--- a/php-hostinger/google-sheets/Mau-lich-chup-AnhGau.xlsx
+++ b/php-hostinger/google-sheets/Mau-lich-chup-AnhGau.xlsx
@@ -330,35 +330,40 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Tên đã ghép trên web (HUY, CƯỜNG…). Lịch thêm trên web tự ghi HUY.</t>
+        <t>Không bắt buộc. Chọn 1: Ô TÔ / Ngoại Cảnh / Nhóm tại Stu / Sản Phẩm.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Lịch thêm trên web tự ghi CƯỜNG.</t>
+        <t>Tên đã ghép trên web (HUY, CƯỜNG…). Lịch thêm trên web tự ghi HUY.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Nam / Nữ / Làm Tóc. Chọn nhiều được nếu bật "Cho phép nhiều lựa chọn" trong cài đặt dropdown.</t>
+        <t>Lịch thêm trên web tự ghi CƯỜNG.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Tiền tip khách cho (nếu có), VD 50000.</t>
+        <t>Không bắt buộc. Chọn 1: Nam / Nữ / Làm Tóc.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Khách hủy: chọn Hủy. Không xóa dòng (xóa dòng không xóa lịch trên web).</t>
+        <t>Tiền tip khách cho (nếu có), VD 50000.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
+        <t>Khách hủy: chọn Hủy. Không xóa dòng (xóa dòng không xóa lịch trên web).</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
         <t>Ghi chú tự do. Team ghi "Giữ 3 tiếng" để khóa đủ giờ.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Cột ẩn: script tự ghi mã lịch. Không sửa, không xóa.</t>
       </text>
@@ -402,35 +407,40 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Tên đã ghép trên web (HUY, CƯỜNG…). Lịch thêm trên web tự ghi HUY.</t>
+        <t>Không bắt buộc. Chọn 1: Ô TÔ / Ngoại Cảnh / Nhóm tại Stu / Sản Phẩm.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Lịch thêm trên web tự ghi CƯỜNG.</t>
+        <t>Tên đã ghép trên web (HUY, CƯỜNG…). Lịch thêm trên web tự ghi HUY.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Nam / Nữ / Làm Tóc. Chọn nhiều được nếu bật "Cho phép nhiều lựa chọn" trong cài đặt dropdown.</t>
+        <t>Lịch thêm trên web tự ghi CƯỜNG.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Tiền tip khách cho (nếu có), VD 50000.</t>
+        <t>Không bắt buộc. Chọn 1: Nam / Nữ / Làm Tóc.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Khách hủy: chọn Hủy. Không xóa dòng (xóa dòng không xóa lịch trên web).</t>
+        <t>Tiền tip khách cho (nếu có), VD 50000.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
+        <t>Khách hủy: chọn Hủy. Không xóa dòng (xóa dòng không xóa lịch trên web).</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
         <t>Ghi chú tự do. Team ghi "Giữ 3 tiếng" để khóa đủ giờ.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Cột ẩn: script tự ghi mã lịch. Không sửa, không xóa.</t>
       </text>
@@ -791,7 +801,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Cột Makeup: Dữ liệu → Xác thực dữ liệu → chọn quy tắc của cột Makeup → Tùy chọn nâng cao → bật "Cho phép nhiều lựa chọn" (để chọn Nam + Nữ…). Có thể chọn kiểu hiển thị dạng "Khối" cho dễ nhìn.</t>
+          <t>Điền lịch từ dòng 2 trở xuống, mỗi khách một dòng. Không sửa dòng tiêu đề (dòng 1) và cột ẩn _AG_BOOKING_ID.</t>
         </is>
       </c>
     </row>
@@ -803,55 +813,65 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Điền lịch từ dòng 2 trở xuống, mỗi khách một dòng. Không sửa dòng tiêu đề (dòng 1) và cột ẩn _AG_BOOKING_ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Bước 5</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
           <t>Menu Anh Gấu Studio → Đồng bộ ngay để kiểm tra. Từ tháng sau, script tự tạo tab tháng mới bằng cách nhân bản tab tháng liền trước khi có lịch thêm trên web.</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Cách điền</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Lịch thêm trên web tự ghi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>dd/mm (VD 05/11). Chỉ ghi ở dòng đầu của mỗi ngày; các dòng sau để trống hoặc gộp ô.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Chèn đúng ngày, đúng thứ tự giờ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Giờ</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -861,19 +881,19 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>dd/mm (VD 05/11). Chỉ ghi ở dòng đầu của mỗi ngày; các dòng sau để trống hoặc gộp ô.</t>
+          <t>HH:mm (VD 10:00, 11:30).</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Chèn đúng ngày, đúng thứ tự giờ</t>
+          <t>Giờ đã chọn</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Giờ</t>
+          <t>Tên khách</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -883,70 +903,66 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>HH:mm (VD 10:00, 11:30).</t>
+          <t>Tên + tiền cọc (VD Chị Lan cọc 200k).</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Giờ đã chọn</t>
+          <t>Tên khách đã nhập</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Tên khách</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+          <t>SĐT</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Tên + tiền cọc (VD Chị Lan cọc 200k).</t>
+          <t>Giữ số 0 đầu.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Tên khách đã nhập</t>
+          <t>SĐT</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>SĐT</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Giữ số 0 đầu.</t>
+          <t>Để trống = 399/699 khách tới chọn (1 tiếng). Couple 999 / 1499 / 2999 = 2 tiếng. Team 349 = theo "Giữ N tiếng" ở Ghi chú.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>SĐT</t>
+          <t>Trống (399/699) hoặc gói đã chọn</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Gói</t>
+          <t>Đặc Biệt</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Để trống = 399/699 khách tới chọn (1 tiếng). Couple 999 / 1499 / 2999 = 2 tiếng. Team 349 = theo "Giữ N tiếng" ở Ghi chú.</t>
+          <t>Chọn 1: Ô TÔ / Ngoại Cảnh / Nhóm tại Stu / Sản Phẩm, hoặc để trống.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Trống (399/699) hoặc gói đã chọn</t>
+          <t>Lựa chọn đã chọn (hoặc trống)</t>
         </is>
       </c>
     </row>
@@ -977,12 +993,12 @@
       <c r="C19" s="8" t="inlineStr"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Nam / Nữ / Làm Tóc, chọn nhiều được.</t>
+          <t>Chọn 1: Nam / Nữ / Làm Tóc, hoặc để trống.</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Lựa chọn đã tick</t>
+          <t>Lựa chọn đã chọn (hoặc trống)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1130,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B1:E1"/>
@@ -1125,7 +1141,6 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1137,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1145,14 +1160,15 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="38" customWidth="1" min="12" max="12"/>
-    <col width="62" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="38" customWidth="1" min="13" max="13"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1183,40 +1199,45 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Đặc Biệt</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>Thợ chính</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Thợ phụ</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Makeup</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>_AG_BOOKING_ID</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Giải thích (chỉ có ở tab Ví dụ)</t>
         </is>
@@ -1240,26 +1261,27 @@
         </is>
       </c>
       <c r="E2" s="14" t="n"/>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>Nữ</t>
         </is>
       </c>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="13" t="n"/>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="13" t="n"/>
+      <c r="O2" s="17" t="inlineStr">
         <is>
           <t>Gói để trống = 399/699, khách tới mới chọn → giữ 1 tiếng (09:00–10:00). Ngày chỉ ghi ở dòng đầu của ngày.</t>
         </is>
@@ -1287,30 +1309,35 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
+          <t>Ngoại Cảnh</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Nữ</t>
         </is>
       </c>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="14" t="n"/>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Chụp áo dài</t>
         </is>
       </c>
-      <c r="L3" s="13" t="n"/>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t>Couple 999 giữ 2 tiếng (10:00–12:00). Ô Ngày trống = cùng ngày với dòng trên.</t>
+      <c r="M3" s="13" t="n"/>
+      <c r="O3" s="17" t="inlineStr">
+        <is>
+          <t>Couple 999 giữ 2 tiếng (10:00–12:00). Ô Ngày trống = cùng ngày với dòng trên. Đặc Biệt chọn 1 hoặc để trống.</t>
         </is>
       </c>
     </row>
@@ -1334,28 +1361,29 @@
           <t>1499</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Làm Tóc</t>
         </is>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="J4" s="15" t="n">
         <v>50000</v>
       </c>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t>Gói 1499 giữ 2 tiếng (13:00–15:00). Cột Tip ghi số tiền khách tip.</t>
         </is>
@@ -1377,30 +1405,31 @@
         </is>
       </c>
       <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>Hủy</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>Khách dời sang tháng sau</t>
         </is>
       </c>
-      <c r="L5" s="13" t="n"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="O5" s="17" t="inlineStr">
         <is>
           <t>Khách hủy: chọn Hủy ở Trạng thái (dòng tự mờ đi). Không xóa dòng. Giờ lẻ 15:30 ghi được.</t>
         </is>
@@ -1430,24 +1459,29 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
+          <t>Nhóm tại Stu</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Giữ 3 tiếng</t>
         </is>
       </c>
-      <c r="L6" s="13" t="n"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="13" t="n"/>
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>Team: dòng đầu ghi "Giữ 3 tiếng" ở Ghi chú → khóa 09:00–12:00 với khách khác.</t>
         </is>
@@ -1471,24 +1505,29 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
+          <t>Nhóm tại Stu</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Nữ</t>
         </is>
       </c>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t>Các thành viên team điền thêm cùng giờ, gói Team 349: không bị báo trùng nhau.</t>
         </is>
@@ -1512,20 +1551,25 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
+          <t>Nhóm tại Stu</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="N8" s="17" t="inlineStr"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="O8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="n"/>
@@ -1549,24 +1593,29 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
+          <t>Ô TÔ</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
           <t>HUY</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>CƯỜNG</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Nam</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Gói 2999 giữ 2 tiếng (13:00–15:00).</t>
         </is>
@@ -1581,10 +1630,11 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="13" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -1595,10 +1645,11 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="13" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -1609,10 +1660,11 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="14" t="n"/>
       <c r="H12" s="14" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="13" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -1623,10 +1675,11 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="13" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -1637,10 +1690,11 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="14" t="n"/>
       <c r="H14" s="14" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="13" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -1651,10 +1705,11 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
       <c r="H15" s="14" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="13" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -1665,10 +1720,11 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="13" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -1679,10 +1735,11 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="13" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -1693,10 +1750,11 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14" t="n"/>
       <c r="H18" s="14" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="13" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -1707,10 +1765,11 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
       <c r="H19" s="14" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="13" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -1721,10 +1780,11 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
       <c r="H20" s="14" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="13" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -1735,10 +1795,11 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
       <c r="H21" s="14" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="14" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="13" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -1749,10 +1810,11 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="14" t="n"/>
       <c r="H22" s="14" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="13" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -1763,10 +1825,11 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
       <c r="H23" s="14" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="14" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="13" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -1777,10 +1840,11 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
       <c r="H24" s="14" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="13" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -1791,10 +1855,11 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14" t="n"/>
       <c r="H25" s="14" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="13" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -1805,10 +1870,11 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="14" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="13" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -1819,10 +1885,11 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="14" t="n"/>
       <c r="H27" s="14" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="14" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="13" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -1833,10 +1900,11 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="13" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -1847,35 +1915,39 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="14" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="13" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K29">
+  <conditionalFormatting sqref="A2:L29">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$J2="Hủy"</formula>
+      <formula>$K2="Hủy"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="E2:E29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn gói trong danh sách (để trống nếu khách chưa chọn 399/699)." type="list" errorStyle="warning">
       <formula1>"399,699,Couple 999,1499,2999,Team 349"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
-      <formula1>"HUY,CƯỜNG,TÍN"</formula1>
+    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Ô TÔ / Ngoại Cảnh / Nhóm tại Stu / Sản Phẩm." type="list" errorStyle="warning">
+      <formula1>"Ô TÔ,Ngoại Cảnh,Nhóm tại Stu,Sản Phẩm"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
       <formula1>"HUY,CƯỜNG,TÍN"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Nam / Nữ / Làm Tóc." type="list" errorStyle="warning">
+    <dataValidation sqref="H2:H29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
+      <formula1>"HUY,CƯỜNG,TÍN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Nam / Nữ / Làm Tóc." type="list" errorStyle="warning">
       <formula1>"Nam,Nữ,Làm Tóc"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chỉ chọn Hủy khi khách hủy." type="list" errorStyle="warning">
+    <dataValidation sqref="K2:K29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chỉ chọn Hủy khi khách hủy." type="list" errorStyle="warning">
       <formula1>"Hủy"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1890,7 +1962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L501"/>
+  <dimension ref="A1:M501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1898,13 +1970,14 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="38" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="38" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1935,35 +2008,40 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Đặc Biệt</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>Thợ chính</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Thợ phụ</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Makeup</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>_AG_BOOKING_ID</t>
         </is>
@@ -1978,10 +2056,11 @@
       <c r="F2" s="14" t="n"/>
       <c r="G2" s="14" t="n"/>
       <c r="H2" s="14" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="13" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -1992,10 +2071,11 @@
       <c r="F3" s="14" t="n"/>
       <c r="G3" s="14" t="n"/>
       <c r="H3" s="14" t="n"/>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="14" t="n"/>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="13" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="13" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -2006,10 +2086,11 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
       <c r="H4" s="14" t="n"/>
-      <c r="I4" s="15" t="n"/>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="13" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -2020,10 +2101,11 @@
       <c r="F5" s="14" t="n"/>
       <c r="G5" s="14" t="n"/>
       <c r="H5" s="14" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="13" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -2034,10 +2116,11 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="14" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="13" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -2048,10 +2131,11 @@
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="14" t="n"/>
       <c r="H7" s="14" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="13" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -2062,10 +2146,11 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="14" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="13" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -2076,10 +2161,11 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="14" t="n"/>
       <c r="H9" s="14" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="13" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -2090,10 +2176,11 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="13" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -2104,10 +2191,11 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="13" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -2118,10 +2206,11 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="14" t="n"/>
       <c r="H12" s="14" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="13" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -2132,10 +2221,11 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="13" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -2146,10 +2236,11 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="14" t="n"/>
       <c r="H14" s="14" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="13" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -2160,10 +2251,11 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
       <c r="H15" s="14" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="13" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -2174,10 +2266,11 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="13" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -2188,10 +2281,11 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="13" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -2202,10 +2296,11 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14" t="n"/>
       <c r="H18" s="14" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="13" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -2216,10 +2311,11 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
       <c r="H19" s="14" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="13" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -2230,10 +2326,11 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
       <c r="H20" s="14" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="13" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -2244,10 +2341,11 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
       <c r="H21" s="14" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="14" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="13" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -2258,10 +2356,11 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="14" t="n"/>
       <c r="H22" s="14" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="13" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -2272,10 +2371,11 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
       <c r="H23" s="14" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="14" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="13" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -2286,10 +2386,11 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
       <c r="H24" s="14" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="13" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -2300,10 +2401,11 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14" t="n"/>
       <c r="H25" s="14" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="13" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -2314,10 +2416,11 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="14" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="13" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -2328,10 +2431,11 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="14" t="n"/>
       <c r="H27" s="14" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="14" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="13" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -2342,10 +2446,11 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="13" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -2356,10 +2461,11 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="14" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="13" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -2370,10 +2476,11 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="14" t="n"/>
       <c r="H30" s="14" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="13" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -2384,10 +2491,11 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="14" t="n"/>
       <c r="H31" s="14" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="13" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -2398,10 +2506,11 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="14" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="13" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -2412,10 +2521,11 @@
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="14" t="n"/>
       <c r="H33" s="14" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="13" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -2426,10 +2536,11 @@
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="14" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="13" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -2440,10 +2551,11 @@
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="13" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="16" t="n"/>
+      <c r="M35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -2454,10 +2566,11 @@
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14" t="n"/>
       <c r="H36" s="14" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="13" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -2468,10 +2581,11 @@
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="14" t="n"/>
       <c r="H37" s="14" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="13" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="16" t="n"/>
+      <c r="M37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -2482,10 +2596,11 @@
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="14" t="n"/>
       <c r="H38" s="14" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="13" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="16" t="n"/>
+      <c r="M38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -2496,10 +2611,11 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="14" t="n"/>
       <c r="H39" s="14" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="14" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="13" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="16" t="n"/>
+      <c r="M39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -2510,10 +2626,11 @@
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="14" t="n"/>
       <c r="H40" s="14" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="13" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="16" t="n"/>
+      <c r="M40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -2524,10 +2641,11 @@
       <c r="F41" s="14" t="n"/>
       <c r="G41" s="14" t="n"/>
       <c r="H41" s="14" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="14" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="13" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="16" t="n"/>
+      <c r="M41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n"/>
@@ -2538,10 +2656,11 @@
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="14" t="n"/>
       <c r="H42" s="14" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="13" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="15" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="16" t="n"/>
+      <c r="M42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n"/>
@@ -2552,10 +2671,11 @@
       <c r="F43" s="14" t="n"/>
       <c r="G43" s="14" t="n"/>
       <c r="H43" s="14" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="13" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="15" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="16" t="n"/>
+      <c r="M43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n"/>
@@ -2566,10 +2686,11 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
       <c r="H44" s="14" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="14" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="13" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="15" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="16" t="n"/>
+      <c r="M44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n"/>
@@ -2580,10 +2701,11 @@
       <c r="F45" s="14" t="n"/>
       <c r="G45" s="14" t="n"/>
       <c r="H45" s="14" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="14" t="n"/>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="13" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="15" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="16" t="n"/>
+      <c r="M45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n"/>
@@ -2594,10 +2716,11 @@
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="14" t="n"/>
       <c r="H46" s="14" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="14" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="13" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="16" t="n"/>
+      <c r="M46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n"/>
@@ -2608,10 +2731,11 @@
       <c r="F47" s="14" t="n"/>
       <c r="G47" s="14" t="n"/>
       <c r="H47" s="14" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="14" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="13" t="n"/>
+      <c r="I47" s="14" t="n"/>
+      <c r="J47" s="15" t="n"/>
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="16" t="n"/>
+      <c r="M47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n"/>
@@ -2622,10 +2746,11 @@
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14" t="n"/>
       <c r="H48" s="14" t="n"/>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="13" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="15" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="16" t="n"/>
+      <c r="M48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n"/>
@@ -2636,10 +2761,11 @@
       <c r="F49" s="14" t="n"/>
       <c r="G49" s="14" t="n"/>
       <c r="H49" s="14" t="n"/>
-      <c r="I49" s="15" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="13" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="15" t="n"/>
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="16" t="n"/>
+      <c r="M49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n"/>
@@ -2650,10 +2776,11 @@
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14" t="n"/>
       <c r="H50" s="14" t="n"/>
-      <c r="I50" s="15" t="n"/>
-      <c r="J50" s="14" t="n"/>
-      <c r="K50" s="16" t="n"/>
-      <c r="L50" s="13" t="n"/>
+      <c r="I50" s="14" t="n"/>
+      <c r="J50" s="15" t="n"/>
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="16" t="n"/>
+      <c r="M50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n"/>
@@ -2664,10 +2791,11 @@
       <c r="F51" s="14" t="n"/>
       <c r="G51" s="14" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="I51" s="15" t="n"/>
-      <c r="J51" s="14" t="n"/>
-      <c r="K51" s="16" t="n"/>
-      <c r="L51" s="13" t="n"/>
+      <c r="I51" s="14" t="n"/>
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="16" t="n"/>
+      <c r="M51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n"/>
@@ -2678,10 +2806,11 @@
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14" t="n"/>
       <c r="H52" s="14" t="n"/>
-      <c r="I52" s="15" t="n"/>
-      <c r="J52" s="14" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="13" t="n"/>
+      <c r="I52" s="14" t="n"/>
+      <c r="J52" s="15" t="n"/>
+      <c r="K52" s="14" t="n"/>
+      <c r="L52" s="16" t="n"/>
+      <c r="M52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n"/>
@@ -2692,10 +2821,11 @@
       <c r="F53" s="14" t="n"/>
       <c r="G53" s="14" t="n"/>
       <c r="H53" s="14" t="n"/>
-      <c r="I53" s="15" t="n"/>
-      <c r="J53" s="14" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="13" t="n"/>
+      <c r="I53" s="14" t="n"/>
+      <c r="J53" s="15" t="n"/>
+      <c r="K53" s="14" t="n"/>
+      <c r="L53" s="16" t="n"/>
+      <c r="M53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n"/>
@@ -2706,10 +2836,11 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="14" t="n"/>
       <c r="H54" s="14" t="n"/>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="14" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="13" t="n"/>
+      <c r="I54" s="14" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="14" t="n"/>
+      <c r="L54" s="16" t="n"/>
+      <c r="M54" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n"/>
@@ -2720,10 +2851,11 @@
       <c r="F55" s="14" t="n"/>
       <c r="G55" s="14" t="n"/>
       <c r="H55" s="14" t="n"/>
-      <c r="I55" s="15" t="n"/>
-      <c r="J55" s="14" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="13" t="n"/>
+      <c r="I55" s="14" t="n"/>
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="14" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n"/>
@@ -2734,10 +2866,11 @@
       <c r="F56" s="14" t="n"/>
       <c r="G56" s="14" t="n"/>
       <c r="H56" s="14" t="n"/>
-      <c r="I56" s="15" t="n"/>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="13" t="n"/>
+      <c r="I56" s="14" t="n"/>
+      <c r="J56" s="15" t="n"/>
+      <c r="K56" s="14" t="n"/>
+      <c r="L56" s="16" t="n"/>
+      <c r="M56" s="13" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n"/>
@@ -2748,10 +2881,11 @@
       <c r="F57" s="14" t="n"/>
       <c r="G57" s="14" t="n"/>
       <c r="H57" s="14" t="n"/>
-      <c r="I57" s="15" t="n"/>
-      <c r="J57" s="14" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="13" t="n"/>
+      <c r="I57" s="14" t="n"/>
+      <c r="J57" s="15" t="n"/>
+      <c r="K57" s="14" t="n"/>
+      <c r="L57" s="16" t="n"/>
+      <c r="M57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n"/>
@@ -2762,10 +2896,11 @@
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="14" t="n"/>
       <c r="H58" s="14" t="n"/>
-      <c r="I58" s="15" t="n"/>
-      <c r="J58" s="14" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="13" t="n"/>
+      <c r="I58" s="14" t="n"/>
+      <c r="J58" s="15" t="n"/>
+      <c r="K58" s="14" t="n"/>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="13" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -2776,10 +2911,11 @@
       <c r="F59" s="14" t="n"/>
       <c r="G59" s="14" t="n"/>
       <c r="H59" s="14" t="n"/>
-      <c r="I59" s="15" t="n"/>
-      <c r="J59" s="14" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="13" t="n"/>
+      <c r="I59" s="14" t="n"/>
+      <c r="J59" s="15" t="n"/>
+      <c r="K59" s="14" t="n"/>
+      <c r="L59" s="16" t="n"/>
+      <c r="M59" s="13" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -2790,10 +2926,11 @@
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="14" t="n"/>
       <c r="H60" s="14" t="n"/>
-      <c r="I60" s="15" t="n"/>
-      <c r="J60" s="14" t="n"/>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="13" t="n"/>
+      <c r="I60" s="14" t="n"/>
+      <c r="J60" s="15" t="n"/>
+      <c r="K60" s="14" t="n"/>
+      <c r="L60" s="16" t="n"/>
+      <c r="M60" s="13" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -2804,10 +2941,11 @@
       <c r="F61" s="14" t="n"/>
       <c r="G61" s="14" t="n"/>
       <c r="H61" s="14" t="n"/>
-      <c r="I61" s="15" t="n"/>
-      <c r="J61" s="14" t="n"/>
-      <c r="K61" s="16" t="n"/>
-      <c r="L61" s="13" t="n"/>
+      <c r="I61" s="14" t="n"/>
+      <c r="J61" s="15" t="n"/>
+      <c r="K61" s="14" t="n"/>
+      <c r="L61" s="16" t="n"/>
+      <c r="M61" s="13" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n"/>
@@ -2818,10 +2956,11 @@
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="14" t="n"/>
       <c r="H62" s="14" t="n"/>
-      <c r="I62" s="15" t="n"/>
-      <c r="J62" s="14" t="n"/>
-      <c r="K62" s="16" t="n"/>
-      <c r="L62" s="13" t="n"/>
+      <c r="I62" s="14" t="n"/>
+      <c r="J62" s="15" t="n"/>
+      <c r="K62" s="14" t="n"/>
+      <c r="L62" s="16" t="n"/>
+      <c r="M62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -2832,10 +2971,11 @@
       <c r="F63" s="14" t="n"/>
       <c r="G63" s="14" t="n"/>
       <c r="H63" s="14" t="n"/>
-      <c r="I63" s="15" t="n"/>
-      <c r="J63" s="14" t="n"/>
-      <c r="K63" s="16" t="n"/>
-      <c r="L63" s="13" t="n"/>
+      <c r="I63" s="14" t="n"/>
+      <c r="J63" s="15" t="n"/>
+      <c r="K63" s="14" t="n"/>
+      <c r="L63" s="16" t="n"/>
+      <c r="M63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -2846,10 +2986,11 @@
       <c r="F64" s="14" t="n"/>
       <c r="G64" s="14" t="n"/>
       <c r="H64" s="14" t="n"/>
-      <c r="I64" s="15" t="n"/>
-      <c r="J64" s="14" t="n"/>
-      <c r="K64" s="16" t="n"/>
-      <c r="L64" s="13" t="n"/>
+      <c r="I64" s="14" t="n"/>
+      <c r="J64" s="15" t="n"/>
+      <c r="K64" s="14" t="n"/>
+      <c r="L64" s="16" t="n"/>
+      <c r="M64" s="13" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -2860,10 +3001,11 @@
       <c r="F65" s="14" t="n"/>
       <c r="G65" s="14" t="n"/>
       <c r="H65" s="14" t="n"/>
-      <c r="I65" s="15" t="n"/>
-      <c r="J65" s="14" t="n"/>
-      <c r="K65" s="16" t="n"/>
-      <c r="L65" s="13" t="n"/>
+      <c r="I65" s="14" t="n"/>
+      <c r="J65" s="15" t="n"/>
+      <c r="K65" s="14" t="n"/>
+      <c r="L65" s="16" t="n"/>
+      <c r="M65" s="13" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n"/>
@@ -2874,10 +3016,11 @@
       <c r="F66" s="14" t="n"/>
       <c r="G66" s="14" t="n"/>
       <c r="H66" s="14" t="n"/>
-      <c r="I66" s="15" t="n"/>
-      <c r="J66" s="14" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="13" t="n"/>
+      <c r="I66" s="14" t="n"/>
+      <c r="J66" s="15" t="n"/>
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="16" t="n"/>
+      <c r="M66" s="13" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -2888,10 +3031,11 @@
       <c r="F67" s="14" t="n"/>
       <c r="G67" s="14" t="n"/>
       <c r="H67" s="14" t="n"/>
-      <c r="I67" s="15" t="n"/>
-      <c r="J67" s="14" t="n"/>
-      <c r="K67" s="16" t="n"/>
-      <c r="L67" s="13" t="n"/>
+      <c r="I67" s="14" t="n"/>
+      <c r="J67" s="15" t="n"/>
+      <c r="K67" s="14" t="n"/>
+      <c r="L67" s="16" t="n"/>
+      <c r="M67" s="13" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -2902,10 +3046,11 @@
       <c r="F68" s="14" t="n"/>
       <c r="G68" s="14" t="n"/>
       <c r="H68" s="14" t="n"/>
-      <c r="I68" s="15" t="n"/>
-      <c r="J68" s="14" t="n"/>
-      <c r="K68" s="16" t="n"/>
-      <c r="L68" s="13" t="n"/>
+      <c r="I68" s="14" t="n"/>
+      <c r="J68" s="15" t="n"/>
+      <c r="K68" s="14" t="n"/>
+      <c r="L68" s="16" t="n"/>
+      <c r="M68" s="13" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -2916,10 +3061,11 @@
       <c r="F69" s="14" t="n"/>
       <c r="G69" s="14" t="n"/>
       <c r="H69" s="14" t="n"/>
-      <c r="I69" s="15" t="n"/>
-      <c r="J69" s="14" t="n"/>
-      <c r="K69" s="16" t="n"/>
-      <c r="L69" s="13" t="n"/>
+      <c r="I69" s="14" t="n"/>
+      <c r="J69" s="15" t="n"/>
+      <c r="K69" s="14" t="n"/>
+      <c r="L69" s="16" t="n"/>
+      <c r="M69" s="13" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n"/>
@@ -2930,10 +3076,11 @@
       <c r="F70" s="14" t="n"/>
       <c r="G70" s="14" t="n"/>
       <c r="H70" s="14" t="n"/>
-      <c r="I70" s="15" t="n"/>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="16" t="n"/>
-      <c r="L70" s="13" t="n"/>
+      <c r="I70" s="14" t="n"/>
+      <c r="J70" s="15" t="n"/>
+      <c r="K70" s="14" t="n"/>
+      <c r="L70" s="16" t="n"/>
+      <c r="M70" s="13" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -2944,10 +3091,11 @@
       <c r="F71" s="14" t="n"/>
       <c r="G71" s="14" t="n"/>
       <c r="H71" s="14" t="n"/>
-      <c r="I71" s="15" t="n"/>
-      <c r="J71" s="14" t="n"/>
-      <c r="K71" s="16" t="n"/>
-      <c r="L71" s="13" t="n"/>
+      <c r="I71" s="14" t="n"/>
+      <c r="J71" s="15" t="n"/>
+      <c r="K71" s="14" t="n"/>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="13" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -2958,10 +3106,11 @@
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="14" t="n"/>
       <c r="H72" s="14" t="n"/>
-      <c r="I72" s="15" t="n"/>
-      <c r="J72" s="14" t="n"/>
-      <c r="K72" s="16" t="n"/>
-      <c r="L72" s="13" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="15" t="n"/>
+      <c r="K72" s="14" t="n"/>
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="13" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -2972,10 +3121,11 @@
       <c r="F73" s="14" t="n"/>
       <c r="G73" s="14" t="n"/>
       <c r="H73" s="14" t="n"/>
-      <c r="I73" s="15" t="n"/>
-      <c r="J73" s="14" t="n"/>
-      <c r="K73" s="16" t="n"/>
-      <c r="L73" s="13" t="n"/>
+      <c r="I73" s="14" t="n"/>
+      <c r="J73" s="15" t="n"/>
+      <c r="K73" s="14" t="n"/>
+      <c r="L73" s="16" t="n"/>
+      <c r="M73" s="13" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n"/>
@@ -2986,10 +3136,11 @@
       <c r="F74" s="14" t="n"/>
       <c r="G74" s="14" t="n"/>
       <c r="H74" s="14" t="n"/>
-      <c r="I74" s="15" t="n"/>
-      <c r="J74" s="14" t="n"/>
-      <c r="K74" s="16" t="n"/>
-      <c r="L74" s="13" t="n"/>
+      <c r="I74" s="14" t="n"/>
+      <c r="J74" s="15" t="n"/>
+      <c r="K74" s="14" t="n"/>
+      <c r="L74" s="16" t="n"/>
+      <c r="M74" s="13" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -3000,10 +3151,11 @@
       <c r="F75" s="14" t="n"/>
       <c r="G75" s="14" t="n"/>
       <c r="H75" s="14" t="n"/>
-      <c r="I75" s="15" t="n"/>
-      <c r="J75" s="14" t="n"/>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="13" t="n"/>
+      <c r="I75" s="14" t="n"/>
+      <c r="J75" s="15" t="n"/>
+      <c r="K75" s="14" t="n"/>
+      <c r="L75" s="16" t="n"/>
+      <c r="M75" s="13" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -3014,10 +3166,11 @@
       <c r="F76" s="14" t="n"/>
       <c r="G76" s="14" t="n"/>
       <c r="H76" s="14" t="n"/>
-      <c r="I76" s="15" t="n"/>
-      <c r="J76" s="14" t="n"/>
-      <c r="K76" s="16" t="n"/>
-      <c r="L76" s="13" t="n"/>
+      <c r="I76" s="14" t="n"/>
+      <c r="J76" s="15" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="16" t="n"/>
+      <c r="M76" s="13" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -3028,10 +3181,11 @@
       <c r="F77" s="14" t="n"/>
       <c r="G77" s="14" t="n"/>
       <c r="H77" s="14" t="n"/>
-      <c r="I77" s="15" t="n"/>
-      <c r="J77" s="14" t="n"/>
-      <c r="K77" s="16" t="n"/>
-      <c r="L77" s="13" t="n"/>
+      <c r="I77" s="14" t="n"/>
+      <c r="J77" s="15" t="n"/>
+      <c r="K77" s="14" t="n"/>
+      <c r="L77" s="16" t="n"/>
+      <c r="M77" s="13" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n"/>
@@ -3042,10 +3196,11 @@
       <c r="F78" s="14" t="n"/>
       <c r="G78" s="14" t="n"/>
       <c r="H78" s="14" t="n"/>
-      <c r="I78" s="15" t="n"/>
-      <c r="J78" s="14" t="n"/>
-      <c r="K78" s="16" t="n"/>
-      <c r="L78" s="13" t="n"/>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="15" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="16" t="n"/>
+      <c r="M78" s="13" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -3056,10 +3211,11 @@
       <c r="F79" s="14" t="n"/>
       <c r="G79" s="14" t="n"/>
       <c r="H79" s="14" t="n"/>
-      <c r="I79" s="15" t="n"/>
-      <c r="J79" s="14" t="n"/>
-      <c r="K79" s="16" t="n"/>
-      <c r="L79" s="13" t="n"/>
+      <c r="I79" s="14" t="n"/>
+      <c r="J79" s="15" t="n"/>
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="16" t="n"/>
+      <c r="M79" s="13" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -3070,10 +3226,11 @@
       <c r="F80" s="14" t="n"/>
       <c r="G80" s="14" t="n"/>
       <c r="H80" s="14" t="n"/>
-      <c r="I80" s="15" t="n"/>
-      <c r="J80" s="14" t="n"/>
-      <c r="K80" s="16" t="n"/>
-      <c r="L80" s="13" t="n"/>
+      <c r="I80" s="14" t="n"/>
+      <c r="J80" s="15" t="n"/>
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="16" t="n"/>
+      <c r="M80" s="13" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -3084,10 +3241,11 @@
       <c r="F81" s="14" t="n"/>
       <c r="G81" s="14" t="n"/>
       <c r="H81" s="14" t="n"/>
-      <c r="I81" s="15" t="n"/>
-      <c r="J81" s="14" t="n"/>
-      <c r="K81" s="16" t="n"/>
-      <c r="L81" s="13" t="n"/>
+      <c r="I81" s="14" t="n"/>
+      <c r="J81" s="15" t="n"/>
+      <c r="K81" s="14" t="n"/>
+      <c r="L81" s="16" t="n"/>
+      <c r="M81" s="13" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n"/>
@@ -3098,10 +3256,11 @@
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="14" t="n"/>
       <c r="H82" s="14" t="n"/>
-      <c r="I82" s="15" t="n"/>
-      <c r="J82" s="14" t="n"/>
-      <c r="K82" s="16" t="n"/>
-      <c r="L82" s="13" t="n"/>
+      <c r="I82" s="14" t="n"/>
+      <c r="J82" s="15" t="n"/>
+      <c r="K82" s="14" t="n"/>
+      <c r="L82" s="16" t="n"/>
+      <c r="M82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -3112,10 +3271,11 @@
       <c r="F83" s="14" t="n"/>
       <c r="G83" s="14" t="n"/>
       <c r="H83" s="14" t="n"/>
-      <c r="I83" s="15" t="n"/>
-      <c r="J83" s="14" t="n"/>
-      <c r="K83" s="16" t="n"/>
-      <c r="L83" s="13" t="n"/>
+      <c r="I83" s="14" t="n"/>
+      <c r="J83" s="15" t="n"/>
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="16" t="n"/>
+      <c r="M83" s="13" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -3126,10 +3286,11 @@
       <c r="F84" s="14" t="n"/>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
-      <c r="I84" s="15" t="n"/>
-      <c r="J84" s="14" t="n"/>
-      <c r="K84" s="16" t="n"/>
-      <c r="L84" s="13" t="n"/>
+      <c r="I84" s="14" t="n"/>
+      <c r="J84" s="15" t="n"/>
+      <c r="K84" s="14" t="n"/>
+      <c r="L84" s="16" t="n"/>
+      <c r="M84" s="13" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -3140,10 +3301,11 @@
       <c r="F85" s="14" t="n"/>
       <c r="G85" s="14" t="n"/>
       <c r="H85" s="14" t="n"/>
-      <c r="I85" s="15" t="n"/>
-      <c r="J85" s="14" t="n"/>
-      <c r="K85" s="16" t="n"/>
-      <c r="L85" s="13" t="n"/>
+      <c r="I85" s="14" t="n"/>
+      <c r="J85" s="15" t="n"/>
+      <c r="K85" s="14" t="n"/>
+      <c r="L85" s="16" t="n"/>
+      <c r="M85" s="13" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n"/>
@@ -3154,10 +3316,11 @@
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="14" t="n"/>
       <c r="H86" s="14" t="n"/>
-      <c r="I86" s="15" t="n"/>
-      <c r="J86" s="14" t="n"/>
-      <c r="K86" s="16" t="n"/>
-      <c r="L86" s="13" t="n"/>
+      <c r="I86" s="14" t="n"/>
+      <c r="J86" s="15" t="n"/>
+      <c r="K86" s="14" t="n"/>
+      <c r="L86" s="16" t="n"/>
+      <c r="M86" s="13" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -3168,10 +3331,11 @@
       <c r="F87" s="14" t="n"/>
       <c r="G87" s="14" t="n"/>
       <c r="H87" s="14" t="n"/>
-      <c r="I87" s="15" t="n"/>
-      <c r="J87" s="14" t="n"/>
-      <c r="K87" s="16" t="n"/>
-      <c r="L87" s="13" t="n"/>
+      <c r="I87" s="14" t="n"/>
+      <c r="J87" s="15" t="n"/>
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="16" t="n"/>
+      <c r="M87" s="13" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -3182,10 +3346,11 @@
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="14" t="n"/>
       <c r="H88" s="14" t="n"/>
-      <c r="I88" s="15" t="n"/>
-      <c r="J88" s="14" t="n"/>
-      <c r="K88" s="16" t="n"/>
-      <c r="L88" s="13" t="n"/>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="15" t="n"/>
+      <c r="K88" s="14" t="n"/>
+      <c r="L88" s="16" t="n"/>
+      <c r="M88" s="13" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -3196,10 +3361,11 @@
       <c r="F89" s="14" t="n"/>
       <c r="G89" s="14" t="n"/>
       <c r="H89" s="14" t="n"/>
-      <c r="I89" s="15" t="n"/>
-      <c r="J89" s="14" t="n"/>
-      <c r="K89" s="16" t="n"/>
-      <c r="L89" s="13" t="n"/>
+      <c r="I89" s="14" t="n"/>
+      <c r="J89" s="15" t="n"/>
+      <c r="K89" s="14" t="n"/>
+      <c r="L89" s="16" t="n"/>
+      <c r="M89" s="13" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -3210,10 +3376,11 @@
       <c r="F90" s="14" t="n"/>
       <c r="G90" s="14" t="n"/>
       <c r="H90" s="14" t="n"/>
-      <c r="I90" s="15" t="n"/>
-      <c r="J90" s="14" t="n"/>
-      <c r="K90" s="16" t="n"/>
-      <c r="L90" s="13" t="n"/>
+      <c r="I90" s="14" t="n"/>
+      <c r="J90" s="15" t="n"/>
+      <c r="K90" s="14" t="n"/>
+      <c r="L90" s="16" t="n"/>
+      <c r="M90" s="13" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n"/>
@@ -3224,10 +3391,11 @@
       <c r="F91" s="14" t="n"/>
       <c r="G91" s="14" t="n"/>
       <c r="H91" s="14" t="n"/>
-      <c r="I91" s="15" t="n"/>
-      <c r="J91" s="14" t="n"/>
-      <c r="K91" s="16" t="n"/>
-      <c r="L91" s="13" t="n"/>
+      <c r="I91" s="14" t="n"/>
+      <c r="J91" s="15" t="n"/>
+      <c r="K91" s="14" t="n"/>
+      <c r="L91" s="16" t="n"/>
+      <c r="M91" s="13" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n"/>
@@ -3238,10 +3406,11 @@
       <c r="F92" s="14" t="n"/>
       <c r="G92" s="14" t="n"/>
       <c r="H92" s="14" t="n"/>
-      <c r="I92" s="15" t="n"/>
-      <c r="J92" s="14" t="n"/>
-      <c r="K92" s="16" t="n"/>
-      <c r="L92" s="13" t="n"/>
+      <c r="I92" s="14" t="n"/>
+      <c r="J92" s="15" t="n"/>
+      <c r="K92" s="14" t="n"/>
+      <c r="L92" s="16" t="n"/>
+      <c r="M92" s="13" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -3252,10 +3421,11 @@
       <c r="F93" s="14" t="n"/>
       <c r="G93" s="14" t="n"/>
       <c r="H93" s="14" t="n"/>
-      <c r="I93" s="15" t="n"/>
-      <c r="J93" s="14" t="n"/>
-      <c r="K93" s="16" t="n"/>
-      <c r="L93" s="13" t="n"/>
+      <c r="I93" s="14" t="n"/>
+      <c r="J93" s="15" t="n"/>
+      <c r="K93" s="14" t="n"/>
+      <c r="L93" s="16" t="n"/>
+      <c r="M93" s="13" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -3266,10 +3436,11 @@
       <c r="F94" s="14" t="n"/>
       <c r="G94" s="14" t="n"/>
       <c r="H94" s="14" t="n"/>
-      <c r="I94" s="15" t="n"/>
-      <c r="J94" s="14" t="n"/>
-      <c r="K94" s="16" t="n"/>
-      <c r="L94" s="13" t="n"/>
+      <c r="I94" s="14" t="n"/>
+      <c r="J94" s="15" t="n"/>
+      <c r="K94" s="14" t="n"/>
+      <c r="L94" s="16" t="n"/>
+      <c r="M94" s="13" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -3280,10 +3451,11 @@
       <c r="F95" s="14" t="n"/>
       <c r="G95" s="14" t="n"/>
       <c r="H95" s="14" t="n"/>
-      <c r="I95" s="15" t="n"/>
-      <c r="J95" s="14" t="n"/>
-      <c r="K95" s="16" t="n"/>
-      <c r="L95" s="13" t="n"/>
+      <c r="I95" s="14" t="n"/>
+      <c r="J95" s="15" t="n"/>
+      <c r="K95" s="14" t="n"/>
+      <c r="L95" s="16" t="n"/>
+      <c r="M95" s="13" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n"/>
@@ -3294,10 +3466,11 @@
       <c r="F96" s="14" t="n"/>
       <c r="G96" s="14" t="n"/>
       <c r="H96" s="14" t="n"/>
-      <c r="I96" s="15" t="n"/>
-      <c r="J96" s="14" t="n"/>
-      <c r="K96" s="16" t="n"/>
-      <c r="L96" s="13" t="n"/>
+      <c r="I96" s="14" t="n"/>
+      <c r="J96" s="15" t="n"/>
+      <c r="K96" s="14" t="n"/>
+      <c r="L96" s="16" t="n"/>
+      <c r="M96" s="13" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -3308,10 +3481,11 @@
       <c r="F97" s="14" t="n"/>
       <c r="G97" s="14" t="n"/>
       <c r="H97" s="14" t="n"/>
-      <c r="I97" s="15" t="n"/>
-      <c r="J97" s="14" t="n"/>
-      <c r="K97" s="16" t="n"/>
-      <c r="L97" s="13" t="n"/>
+      <c r="I97" s="14" t="n"/>
+      <c r="J97" s="15" t="n"/>
+      <c r="K97" s="14" t="n"/>
+      <c r="L97" s="16" t="n"/>
+      <c r="M97" s="13" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -3322,10 +3496,11 @@
       <c r="F98" s="14" t="n"/>
       <c r="G98" s="14" t="n"/>
       <c r="H98" s="14" t="n"/>
-      <c r="I98" s="15" t="n"/>
-      <c r="J98" s="14" t="n"/>
-      <c r="K98" s="16" t="n"/>
-      <c r="L98" s="13" t="n"/>
+      <c r="I98" s="14" t="n"/>
+      <c r="J98" s="15" t="n"/>
+      <c r="K98" s="14" t="n"/>
+      <c r="L98" s="16" t="n"/>
+      <c r="M98" s="13" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -3336,10 +3511,11 @@
       <c r="F99" s="14" t="n"/>
       <c r="G99" s="14" t="n"/>
       <c r="H99" s="14" t="n"/>
-      <c r="I99" s="15" t="n"/>
-      <c r="J99" s="14" t="n"/>
-      <c r="K99" s="16" t="n"/>
-      <c r="L99" s="13" t="n"/>
+      <c r="I99" s="14" t="n"/>
+      <c r="J99" s="15" t="n"/>
+      <c r="K99" s="14" t="n"/>
+      <c r="L99" s="16" t="n"/>
+      <c r="M99" s="13" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n"/>
@@ -3350,10 +3526,11 @@
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="14" t="n"/>
       <c r="H100" s="14" t="n"/>
-      <c r="I100" s="15" t="n"/>
-      <c r="J100" s="14" t="n"/>
-      <c r="K100" s="16" t="n"/>
-      <c r="L100" s="13" t="n"/>
+      <c r="I100" s="14" t="n"/>
+      <c r="J100" s="15" t="n"/>
+      <c r="K100" s="14" t="n"/>
+      <c r="L100" s="16" t="n"/>
+      <c r="M100" s="13" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -3364,10 +3541,11 @@
       <c r="F101" s="14" t="n"/>
       <c r="G101" s="14" t="n"/>
       <c r="H101" s="14" t="n"/>
-      <c r="I101" s="15" t="n"/>
-      <c r="J101" s="14" t="n"/>
-      <c r="K101" s="16" t="n"/>
-      <c r="L101" s="13" t="n"/>
+      <c r="I101" s="14" t="n"/>
+      <c r="J101" s="15" t="n"/>
+      <c r="K101" s="14" t="n"/>
+      <c r="L101" s="16" t="n"/>
+      <c r="M101" s="13" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -3378,10 +3556,11 @@
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="14" t="n"/>
       <c r="H102" s="14" t="n"/>
-      <c r="I102" s="15" t="n"/>
-      <c r="J102" s="14" t="n"/>
-      <c r="K102" s="16" t="n"/>
-      <c r="L102" s="13" t="n"/>
+      <c r="I102" s="14" t="n"/>
+      <c r="J102" s="15" t="n"/>
+      <c r="K102" s="14" t="n"/>
+      <c r="L102" s="16" t="n"/>
+      <c r="M102" s="13" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -3392,10 +3571,11 @@
       <c r="F103" s="14" t="n"/>
       <c r="G103" s="14" t="n"/>
       <c r="H103" s="14" t="n"/>
-      <c r="I103" s="15" t="n"/>
-      <c r="J103" s="14" t="n"/>
-      <c r="K103" s="16" t="n"/>
-      <c r="L103" s="13" t="n"/>
+      <c r="I103" s="14" t="n"/>
+      <c r="J103" s="15" t="n"/>
+      <c r="K103" s="14" t="n"/>
+      <c r="L103" s="16" t="n"/>
+      <c r="M103" s="13" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n"/>
@@ -3406,10 +3586,11 @@
       <c r="F104" s="14" t="n"/>
       <c r="G104" s="14" t="n"/>
       <c r="H104" s="14" t="n"/>
-      <c r="I104" s="15" t="n"/>
-      <c r="J104" s="14" t="n"/>
-      <c r="K104" s="16" t="n"/>
-      <c r="L104" s="13" t="n"/>
+      <c r="I104" s="14" t="n"/>
+      <c r="J104" s="15" t="n"/>
+      <c r="K104" s="14" t="n"/>
+      <c r="L104" s="16" t="n"/>
+      <c r="M104" s="13" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -3420,10 +3601,11 @@
       <c r="F105" s="14" t="n"/>
       <c r="G105" s="14" t="n"/>
       <c r="H105" s="14" t="n"/>
-      <c r="I105" s="15" t="n"/>
-      <c r="J105" s="14" t="n"/>
-      <c r="K105" s="16" t="n"/>
-      <c r="L105" s="13" t="n"/>
+      <c r="I105" s="14" t="n"/>
+      <c r="J105" s="15" t="n"/>
+      <c r="K105" s="14" t="n"/>
+      <c r="L105" s="16" t="n"/>
+      <c r="M105" s="13" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -3434,10 +3616,11 @@
       <c r="F106" s="14" t="n"/>
       <c r="G106" s="14" t="n"/>
       <c r="H106" s="14" t="n"/>
-      <c r="I106" s="15" t="n"/>
-      <c r="J106" s="14" t="n"/>
-      <c r="K106" s="16" t="n"/>
-      <c r="L106" s="13" t="n"/>
+      <c r="I106" s="14" t="n"/>
+      <c r="J106" s="15" t="n"/>
+      <c r="K106" s="14" t="n"/>
+      <c r="L106" s="16" t="n"/>
+      <c r="M106" s="13" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -3448,10 +3631,11 @@
       <c r="F107" s="14" t="n"/>
       <c r="G107" s="14" t="n"/>
       <c r="H107" s="14" t="n"/>
-      <c r="I107" s="15" t="n"/>
-      <c r="J107" s="14" t="n"/>
-      <c r="K107" s="16" t="n"/>
-      <c r="L107" s="13" t="n"/>
+      <c r="I107" s="14" t="n"/>
+      <c r="J107" s="15" t="n"/>
+      <c r="K107" s="14" t="n"/>
+      <c r="L107" s="16" t="n"/>
+      <c r="M107" s="13" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n"/>
@@ -3462,10 +3646,11 @@
       <c r="F108" s="14" t="n"/>
       <c r="G108" s="14" t="n"/>
       <c r="H108" s="14" t="n"/>
-      <c r="I108" s="15" t="n"/>
-      <c r="J108" s="14" t="n"/>
-      <c r="K108" s="16" t="n"/>
-      <c r="L108" s="13" t="n"/>
+      <c r="I108" s="14" t="n"/>
+      <c r="J108" s="15" t="n"/>
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="16" t="n"/>
+      <c r="M108" s="13" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -3476,10 +3661,11 @@
       <c r="F109" s="14" t="n"/>
       <c r="G109" s="14" t="n"/>
       <c r="H109" s="14" t="n"/>
-      <c r="I109" s="15" t="n"/>
-      <c r="J109" s="14" t="n"/>
-      <c r="K109" s="16" t="n"/>
-      <c r="L109" s="13" t="n"/>
+      <c r="I109" s="14" t="n"/>
+      <c r="J109" s="15" t="n"/>
+      <c r="K109" s="14" t="n"/>
+      <c r="L109" s="16" t="n"/>
+      <c r="M109" s="13" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -3490,10 +3676,11 @@
       <c r="F110" s="14" t="n"/>
       <c r="G110" s="14" t="n"/>
       <c r="H110" s="14" t="n"/>
-      <c r="I110" s="15" t="n"/>
-      <c r="J110" s="14" t="n"/>
-      <c r="K110" s="16" t="n"/>
-      <c r="L110" s="13" t="n"/>
+      <c r="I110" s="14" t="n"/>
+      <c r="J110" s="15" t="n"/>
+      <c r="K110" s="14" t="n"/>
+      <c r="L110" s="16" t="n"/>
+      <c r="M110" s="13" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -3504,10 +3691,11 @@
       <c r="F111" s="14" t="n"/>
       <c r="G111" s="14" t="n"/>
       <c r="H111" s="14" t="n"/>
-      <c r="I111" s="15" t="n"/>
-      <c r="J111" s="14" t="n"/>
-      <c r="K111" s="16" t="n"/>
-      <c r="L111" s="13" t="n"/>
+      <c r="I111" s="14" t="n"/>
+      <c r="J111" s="15" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="16" t="n"/>
+      <c r="M111" s="13" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n"/>
@@ -3518,10 +3706,11 @@
       <c r="F112" s="14" t="n"/>
       <c r="G112" s="14" t="n"/>
       <c r="H112" s="14" t="n"/>
-      <c r="I112" s="15" t="n"/>
-      <c r="J112" s="14" t="n"/>
-      <c r="K112" s="16" t="n"/>
-      <c r="L112" s="13" t="n"/>
+      <c r="I112" s="14" t="n"/>
+      <c r="J112" s="15" t="n"/>
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="16" t="n"/>
+      <c r="M112" s="13" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -3532,10 +3721,11 @@
       <c r="F113" s="14" t="n"/>
       <c r="G113" s="14" t="n"/>
       <c r="H113" s="14" t="n"/>
-      <c r="I113" s="15" t="n"/>
-      <c r="J113" s="14" t="n"/>
-      <c r="K113" s="16" t="n"/>
-      <c r="L113" s="13" t="n"/>
+      <c r="I113" s="14" t="n"/>
+      <c r="J113" s="15" t="n"/>
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="16" t="n"/>
+      <c r="M113" s="13" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -3546,10 +3736,11 @@
       <c r="F114" s="14" t="n"/>
       <c r="G114" s="14" t="n"/>
       <c r="H114" s="14" t="n"/>
-      <c r="I114" s="15" t="n"/>
-      <c r="J114" s="14" t="n"/>
-      <c r="K114" s="16" t="n"/>
-      <c r="L114" s="13" t="n"/>
+      <c r="I114" s="14" t="n"/>
+      <c r="J114" s="15" t="n"/>
+      <c r="K114" s="14" t="n"/>
+      <c r="L114" s="16" t="n"/>
+      <c r="M114" s="13" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -3560,10 +3751,11 @@
       <c r="F115" s="14" t="n"/>
       <c r="G115" s="14" t="n"/>
       <c r="H115" s="14" t="n"/>
-      <c r="I115" s="15" t="n"/>
-      <c r="J115" s="14" t="n"/>
-      <c r="K115" s="16" t="n"/>
-      <c r="L115" s="13" t="n"/>
+      <c r="I115" s="14" t="n"/>
+      <c r="J115" s="15" t="n"/>
+      <c r="K115" s="14" t="n"/>
+      <c r="L115" s="16" t="n"/>
+      <c r="M115" s="13" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n"/>
@@ -3574,10 +3766,11 @@
       <c r="F116" s="14" t="n"/>
       <c r="G116" s="14" t="n"/>
       <c r="H116" s="14" t="n"/>
-      <c r="I116" s="15" t="n"/>
-      <c r="J116" s="14" t="n"/>
-      <c r="K116" s="16" t="n"/>
-      <c r="L116" s="13" t="n"/>
+      <c r="I116" s="14" t="n"/>
+      <c r="J116" s="15" t="n"/>
+      <c r="K116" s="14" t="n"/>
+      <c r="L116" s="16" t="n"/>
+      <c r="M116" s="13" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -3588,10 +3781,11 @@
       <c r="F117" s="14" t="n"/>
       <c r="G117" s="14" t="n"/>
       <c r="H117" s="14" t="n"/>
-      <c r="I117" s="15" t="n"/>
-      <c r="J117" s="14" t="n"/>
-      <c r="K117" s="16" t="n"/>
-      <c r="L117" s="13" t="n"/>
+      <c r="I117" s="14" t="n"/>
+      <c r="J117" s="15" t="n"/>
+      <c r="K117" s="14" t="n"/>
+      <c r="L117" s="16" t="n"/>
+      <c r="M117" s="13" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -3602,10 +3796,11 @@
       <c r="F118" s="14" t="n"/>
       <c r="G118" s="14" t="n"/>
       <c r="H118" s="14" t="n"/>
-      <c r="I118" s="15" t="n"/>
-      <c r="J118" s="14" t="n"/>
-      <c r="K118" s="16" t="n"/>
-      <c r="L118" s="13" t="n"/>
+      <c r="I118" s="14" t="n"/>
+      <c r="J118" s="15" t="n"/>
+      <c r="K118" s="14" t="n"/>
+      <c r="L118" s="16" t="n"/>
+      <c r="M118" s="13" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -3616,10 +3811,11 @@
       <c r="F119" s="14" t="n"/>
       <c r="G119" s="14" t="n"/>
       <c r="H119" s="14" t="n"/>
-      <c r="I119" s="15" t="n"/>
-      <c r="J119" s="14" t="n"/>
-      <c r="K119" s="16" t="n"/>
-      <c r="L119" s="13" t="n"/>
+      <c r="I119" s="14" t="n"/>
+      <c r="J119" s="15" t="n"/>
+      <c r="K119" s="14" t="n"/>
+      <c r="L119" s="16" t="n"/>
+      <c r="M119" s="13" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n"/>
@@ -3630,10 +3826,11 @@
       <c r="F120" s="14" t="n"/>
       <c r="G120" s="14" t="n"/>
       <c r="H120" s="14" t="n"/>
-      <c r="I120" s="15" t="n"/>
-      <c r="J120" s="14" t="n"/>
-      <c r="K120" s="16" t="n"/>
-      <c r="L120" s="13" t="n"/>
+      <c r="I120" s="14" t="n"/>
+      <c r="J120" s="15" t="n"/>
+      <c r="K120" s="14" t="n"/>
+      <c r="L120" s="16" t="n"/>
+      <c r="M120" s="13" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -3644,10 +3841,11 @@
       <c r="F121" s="14" t="n"/>
       <c r="G121" s="14" t="n"/>
       <c r="H121" s="14" t="n"/>
-      <c r="I121" s="15" t="n"/>
-      <c r="J121" s="14" t="n"/>
-      <c r="K121" s="16" t="n"/>
-      <c r="L121" s="13" t="n"/>
+      <c r="I121" s="14" t="n"/>
+      <c r="J121" s="15" t="n"/>
+      <c r="K121" s="14" t="n"/>
+      <c r="L121" s="16" t="n"/>
+      <c r="M121" s="13" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -3658,10 +3856,11 @@
       <c r="F122" s="14" t="n"/>
       <c r="G122" s="14" t="n"/>
       <c r="H122" s="14" t="n"/>
-      <c r="I122" s="15" t="n"/>
-      <c r="J122" s="14" t="n"/>
-      <c r="K122" s="16" t="n"/>
-      <c r="L122" s="13" t="n"/>
+      <c r="I122" s="14" t="n"/>
+      <c r="J122" s="15" t="n"/>
+      <c r="K122" s="14" t="n"/>
+      <c r="L122" s="16" t="n"/>
+      <c r="M122" s="13" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -3672,10 +3871,11 @@
       <c r="F123" s="14" t="n"/>
       <c r="G123" s="14" t="n"/>
       <c r="H123" s="14" t="n"/>
-      <c r="I123" s="15" t="n"/>
-      <c r="J123" s="14" t="n"/>
-      <c r="K123" s="16" t="n"/>
-      <c r="L123" s="13" t="n"/>
+      <c r="I123" s="14" t="n"/>
+      <c r="J123" s="15" t="n"/>
+      <c r="K123" s="14" t="n"/>
+      <c r="L123" s="16" t="n"/>
+      <c r="M123" s="13" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -3686,10 +3886,11 @@
       <c r="F124" s="14" t="n"/>
       <c r="G124" s="14" t="n"/>
       <c r="H124" s="14" t="n"/>
-      <c r="I124" s="15" t="n"/>
-      <c r="J124" s="14" t="n"/>
-      <c r="K124" s="16" t="n"/>
-      <c r="L124" s="13" t="n"/>
+      <c r="I124" s="14" t="n"/>
+      <c r="J124" s="15" t="n"/>
+      <c r="K124" s="14" t="n"/>
+      <c r="L124" s="16" t="n"/>
+      <c r="M124" s="13" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="n"/>
@@ -3700,10 +3901,11 @@
       <c r="F125" s="14" t="n"/>
       <c r="G125" s="14" t="n"/>
       <c r="H125" s="14" t="n"/>
-      <c r="I125" s="15" t="n"/>
-      <c r="J125" s="14" t="n"/>
-      <c r="K125" s="16" t="n"/>
-      <c r="L125" s="13" t="n"/>
+      <c r="I125" s="14" t="n"/>
+      <c r="J125" s="15" t="n"/>
+      <c r="K125" s="14" t="n"/>
+      <c r="L125" s="16" t="n"/>
+      <c r="M125" s="13" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n"/>
@@ -3714,10 +3916,11 @@
       <c r="F126" s="14" t="n"/>
       <c r="G126" s="14" t="n"/>
       <c r="H126" s="14" t="n"/>
-      <c r="I126" s="15" t="n"/>
-      <c r="J126" s="14" t="n"/>
-      <c r="K126" s="16" t="n"/>
-      <c r="L126" s="13" t="n"/>
+      <c r="I126" s="14" t="n"/>
+      <c r="J126" s="15" t="n"/>
+      <c r="K126" s="14" t="n"/>
+      <c r="L126" s="16" t="n"/>
+      <c r="M126" s="13" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -3728,10 +3931,11 @@
       <c r="F127" s="14" t="n"/>
       <c r="G127" s="14" t="n"/>
       <c r="H127" s="14" t="n"/>
-      <c r="I127" s="15" t="n"/>
-      <c r="J127" s="14" t="n"/>
-      <c r="K127" s="16" t="n"/>
-      <c r="L127" s="13" t="n"/>
+      <c r="I127" s="14" t="n"/>
+      <c r="J127" s="15" t="n"/>
+      <c r="K127" s="14" t="n"/>
+      <c r="L127" s="16" t="n"/>
+      <c r="M127" s="13" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -3742,10 +3946,11 @@
       <c r="F128" s="14" t="n"/>
       <c r="G128" s="14" t="n"/>
       <c r="H128" s="14" t="n"/>
-      <c r="I128" s="15" t="n"/>
-      <c r="J128" s="14" t="n"/>
-      <c r="K128" s="16" t="n"/>
-      <c r="L128" s="13" t="n"/>
+      <c r="I128" s="14" t="n"/>
+      <c r="J128" s="15" t="n"/>
+      <c r="K128" s="14" t="n"/>
+      <c r="L128" s="16" t="n"/>
+      <c r="M128" s="13" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -3756,10 +3961,11 @@
       <c r="F129" s="14" t="n"/>
       <c r="G129" s="14" t="n"/>
       <c r="H129" s="14" t="n"/>
-      <c r="I129" s="15" t="n"/>
-      <c r="J129" s="14" t="n"/>
-      <c r="K129" s="16" t="n"/>
-      <c r="L129" s="13" t="n"/>
+      <c r="I129" s="14" t="n"/>
+      <c r="J129" s="15" t="n"/>
+      <c r="K129" s="14" t="n"/>
+      <c r="L129" s="16" t="n"/>
+      <c r="M129" s="13" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n"/>
@@ -3770,10 +3976,11 @@
       <c r="F130" s="14" t="n"/>
       <c r="G130" s="14" t="n"/>
       <c r="H130" s="14" t="n"/>
-      <c r="I130" s="15" t="n"/>
-      <c r="J130" s="14" t="n"/>
-      <c r="K130" s="16" t="n"/>
-      <c r="L130" s="13" t="n"/>
+      <c r="I130" s="14" t="n"/>
+      <c r="J130" s="15" t="n"/>
+      <c r="K130" s="14" t="n"/>
+      <c r="L130" s="16" t="n"/>
+      <c r="M130" s="13" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -3784,10 +3991,11 @@
       <c r="F131" s="14" t="n"/>
       <c r="G131" s="14" t="n"/>
       <c r="H131" s="14" t="n"/>
-      <c r="I131" s="15" t="n"/>
-      <c r="J131" s="14" t="n"/>
-      <c r="K131" s="16" t="n"/>
-      <c r="L131" s="13" t="n"/>
+      <c r="I131" s="14" t="n"/>
+      <c r="J131" s="15" t="n"/>
+      <c r="K131" s="14" t="n"/>
+      <c r="L131" s="16" t="n"/>
+      <c r="M131" s="13" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -3798,10 +4006,11 @@
       <c r="F132" s="14" t="n"/>
       <c r="G132" s="14" t="n"/>
       <c r="H132" s="14" t="n"/>
-      <c r="I132" s="15" t="n"/>
-      <c r="J132" s="14" t="n"/>
-      <c r="K132" s="16" t="n"/>
-      <c r="L132" s="13" t="n"/>
+      <c r="I132" s="14" t="n"/>
+      <c r="J132" s="15" t="n"/>
+      <c r="K132" s="14" t="n"/>
+      <c r="L132" s="16" t="n"/>
+      <c r="M132" s="13" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -3812,10 +4021,11 @@
       <c r="F133" s="14" t="n"/>
       <c r="G133" s="14" t="n"/>
       <c r="H133" s="14" t="n"/>
-      <c r="I133" s="15" t="n"/>
-      <c r="J133" s="14" t="n"/>
-      <c r="K133" s="16" t="n"/>
-      <c r="L133" s="13" t="n"/>
+      <c r="I133" s="14" t="n"/>
+      <c r="J133" s="15" t="n"/>
+      <c r="K133" s="14" t="n"/>
+      <c r="L133" s="16" t="n"/>
+      <c r="M133" s="13" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n"/>
@@ -3826,10 +4036,11 @@
       <c r="F134" s="14" t="n"/>
       <c r="G134" s="14" t="n"/>
       <c r="H134" s="14" t="n"/>
-      <c r="I134" s="15" t="n"/>
-      <c r="J134" s="14" t="n"/>
-      <c r="K134" s="16" t="n"/>
-      <c r="L134" s="13" t="n"/>
+      <c r="I134" s="14" t="n"/>
+      <c r="J134" s="15" t="n"/>
+      <c r="K134" s="14" t="n"/>
+      <c r="L134" s="16" t="n"/>
+      <c r="M134" s="13" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -3840,10 +4051,11 @@
       <c r="F135" s="14" t="n"/>
       <c r="G135" s="14" t="n"/>
       <c r="H135" s="14" t="n"/>
-      <c r="I135" s="15" t="n"/>
-      <c r="J135" s="14" t="n"/>
-      <c r="K135" s="16" t="n"/>
-      <c r="L135" s="13" t="n"/>
+      <c r="I135" s="14" t="n"/>
+      <c r="J135" s="15" t="n"/>
+      <c r="K135" s="14" t="n"/>
+      <c r="L135" s="16" t="n"/>
+      <c r="M135" s="13" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -3854,10 +4066,11 @@
       <c r="F136" s="14" t="n"/>
       <c r="G136" s="14" t="n"/>
       <c r="H136" s="14" t="n"/>
-      <c r="I136" s="15" t="n"/>
-      <c r="J136" s="14" t="n"/>
-      <c r="K136" s="16" t="n"/>
-      <c r="L136" s="13" t="n"/>
+      <c r="I136" s="14" t="n"/>
+      <c r="J136" s="15" t="n"/>
+      <c r="K136" s="14" t="n"/>
+      <c r="L136" s="16" t="n"/>
+      <c r="M136" s="13" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -3868,10 +4081,11 @@
       <c r="F137" s="14" t="n"/>
       <c r="G137" s="14" t="n"/>
       <c r="H137" s="14" t="n"/>
-      <c r="I137" s="15" t="n"/>
-      <c r="J137" s="14" t="n"/>
-      <c r="K137" s="16" t="n"/>
-      <c r="L137" s="13" t="n"/>
+      <c r="I137" s="14" t="n"/>
+      <c r="J137" s="15" t="n"/>
+      <c r="K137" s="14" t="n"/>
+      <c r="L137" s="16" t="n"/>
+      <c r="M137" s="13" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n"/>
@@ -3882,10 +4096,11 @@
       <c r="F138" s="14" t="n"/>
       <c r="G138" s="14" t="n"/>
       <c r="H138" s="14" t="n"/>
-      <c r="I138" s="15" t="n"/>
-      <c r="J138" s="14" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="13" t="n"/>
+      <c r="I138" s="14" t="n"/>
+      <c r="J138" s="15" t="n"/>
+      <c r="K138" s="14" t="n"/>
+      <c r="L138" s="16" t="n"/>
+      <c r="M138" s="13" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -3896,10 +4111,11 @@
       <c r="F139" s="14" t="n"/>
       <c r="G139" s="14" t="n"/>
       <c r="H139" s="14" t="n"/>
-      <c r="I139" s="15" t="n"/>
-      <c r="J139" s="14" t="n"/>
-      <c r="K139" s="16" t="n"/>
-      <c r="L139" s="13" t="n"/>
+      <c r="I139" s="14" t="n"/>
+      <c r="J139" s="15" t="n"/>
+      <c r="K139" s="14" t="n"/>
+      <c r="L139" s="16" t="n"/>
+      <c r="M139" s="13" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -3910,10 +4126,11 @@
       <c r="F140" s="14" t="n"/>
       <c r="G140" s="14" t="n"/>
       <c r="H140" s="14" t="n"/>
-      <c r="I140" s="15" t="n"/>
-      <c r="J140" s="14" t="n"/>
-      <c r="K140" s="16" t="n"/>
-      <c r="L140" s="13" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="15" t="n"/>
+      <c r="K140" s="14" t="n"/>
+      <c r="L140" s="16" t="n"/>
+      <c r="M140" s="13" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -3924,10 +4141,11 @@
       <c r="F141" s="14" t="n"/>
       <c r="G141" s="14" t="n"/>
       <c r="H141" s="14" t="n"/>
-      <c r="I141" s="15" t="n"/>
-      <c r="J141" s="14" t="n"/>
-      <c r="K141" s="16" t="n"/>
-      <c r="L141" s="13" t="n"/>
+      <c r="I141" s="14" t="n"/>
+      <c r="J141" s="15" t="n"/>
+      <c r="K141" s="14" t="n"/>
+      <c r="L141" s="16" t="n"/>
+      <c r="M141" s="13" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n"/>
@@ -3938,10 +4156,11 @@
       <c r="F142" s="14" t="n"/>
       <c r="G142" s="14" t="n"/>
       <c r="H142" s="14" t="n"/>
-      <c r="I142" s="15" t="n"/>
-      <c r="J142" s="14" t="n"/>
-      <c r="K142" s="16" t="n"/>
-      <c r="L142" s="13" t="n"/>
+      <c r="I142" s="14" t="n"/>
+      <c r="J142" s="15" t="n"/>
+      <c r="K142" s="14" t="n"/>
+      <c r="L142" s="16" t="n"/>
+      <c r="M142" s="13" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -3952,10 +4171,11 @@
       <c r="F143" s="14" t="n"/>
       <c r="G143" s="14" t="n"/>
       <c r="H143" s="14" t="n"/>
-      <c r="I143" s="15" t="n"/>
-      <c r="J143" s="14" t="n"/>
-      <c r="K143" s="16" t="n"/>
-      <c r="L143" s="13" t="n"/>
+      <c r="I143" s="14" t="n"/>
+      <c r="J143" s="15" t="n"/>
+      <c r="K143" s="14" t="n"/>
+      <c r="L143" s="16" t="n"/>
+      <c r="M143" s="13" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -3966,10 +4186,11 @@
       <c r="F144" s="14" t="n"/>
       <c r="G144" s="14" t="n"/>
       <c r="H144" s="14" t="n"/>
-      <c r="I144" s="15" t="n"/>
-      <c r="J144" s="14" t="n"/>
-      <c r="K144" s="16" t="n"/>
-      <c r="L144" s="13" t="n"/>
+      <c r="I144" s="14" t="n"/>
+      <c r="J144" s="15" t="n"/>
+      <c r="K144" s="14" t="n"/>
+      <c r="L144" s="16" t="n"/>
+      <c r="M144" s="13" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -3980,10 +4201,11 @@
       <c r="F145" s="14" t="n"/>
       <c r="G145" s="14" t="n"/>
       <c r="H145" s="14" t="n"/>
-      <c r="I145" s="15" t="n"/>
-      <c r="J145" s="14" t="n"/>
-      <c r="K145" s="16" t="n"/>
-      <c r="L145" s="13" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="15" t="n"/>
+      <c r="K145" s="14" t="n"/>
+      <c r="L145" s="16" t="n"/>
+      <c r="M145" s="13" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n"/>
@@ -3994,10 +4216,11 @@
       <c r="F146" s="14" t="n"/>
       <c r="G146" s="14" t="n"/>
       <c r="H146" s="14" t="n"/>
-      <c r="I146" s="15" t="n"/>
-      <c r="J146" s="14" t="n"/>
-      <c r="K146" s="16" t="n"/>
-      <c r="L146" s="13" t="n"/>
+      <c r="I146" s="14" t="n"/>
+      <c r="J146" s="15" t="n"/>
+      <c r="K146" s="14" t="n"/>
+      <c r="L146" s="16" t="n"/>
+      <c r="M146" s="13" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -4008,10 +4231,11 @@
       <c r="F147" s="14" t="n"/>
       <c r="G147" s="14" t="n"/>
       <c r="H147" s="14" t="n"/>
-      <c r="I147" s="15" t="n"/>
-      <c r="J147" s="14" t="n"/>
-      <c r="K147" s="16" t="n"/>
-      <c r="L147" s="13" t="n"/>
+      <c r="I147" s="14" t="n"/>
+      <c r="J147" s="15" t="n"/>
+      <c r="K147" s="14" t="n"/>
+      <c r="L147" s="16" t="n"/>
+      <c r="M147" s="13" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -4022,10 +4246,11 @@
       <c r="F148" s="14" t="n"/>
       <c r="G148" s="14" t="n"/>
       <c r="H148" s="14" t="n"/>
-      <c r="I148" s="15" t="n"/>
-      <c r="J148" s="14" t="n"/>
-      <c r="K148" s="16" t="n"/>
-      <c r="L148" s="13" t="n"/>
+      <c r="I148" s="14" t="n"/>
+      <c r="J148" s="15" t="n"/>
+      <c r="K148" s="14" t="n"/>
+      <c r="L148" s="16" t="n"/>
+      <c r="M148" s="13" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -4036,10 +4261,11 @@
       <c r="F149" s="14" t="n"/>
       <c r="G149" s="14" t="n"/>
       <c r="H149" s="14" t="n"/>
-      <c r="I149" s="15" t="n"/>
-      <c r="J149" s="14" t="n"/>
-      <c r="K149" s="16" t="n"/>
-      <c r="L149" s="13" t="n"/>
+      <c r="I149" s="14" t="n"/>
+      <c r="J149" s="15" t="n"/>
+      <c r="K149" s="14" t="n"/>
+      <c r="L149" s="16" t="n"/>
+      <c r="M149" s="13" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="n"/>
@@ -4050,10 +4276,11 @@
       <c r="F150" s="14" t="n"/>
       <c r="G150" s="14" t="n"/>
       <c r="H150" s="14" t="n"/>
-      <c r="I150" s="15" t="n"/>
-      <c r="J150" s="14" t="n"/>
-      <c r="K150" s="16" t="n"/>
-      <c r="L150" s="13" t="n"/>
+      <c r="I150" s="14" t="n"/>
+      <c r="J150" s="15" t="n"/>
+      <c r="K150" s="14" t="n"/>
+      <c r="L150" s="16" t="n"/>
+      <c r="M150" s="13" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -4064,10 +4291,11 @@
       <c r="F151" s="14" t="n"/>
       <c r="G151" s="14" t="n"/>
       <c r="H151" s="14" t="n"/>
-      <c r="I151" s="15" t="n"/>
-      <c r="J151" s="14" t="n"/>
-      <c r="K151" s="16" t="n"/>
-      <c r="L151" s="13" t="n"/>
+      <c r="I151" s="14" t="n"/>
+      <c r="J151" s="15" t="n"/>
+      <c r="K151" s="14" t="n"/>
+      <c r="L151" s="16" t="n"/>
+      <c r="M151" s="13" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -4078,10 +4306,11 @@
       <c r="F152" s="14" t="n"/>
       <c r="G152" s="14" t="n"/>
       <c r="H152" s="14" t="n"/>
-      <c r="I152" s="15" t="n"/>
-      <c r="J152" s="14" t="n"/>
-      <c r="K152" s="16" t="n"/>
-      <c r="L152" s="13" t="n"/>
+      <c r="I152" s="14" t="n"/>
+      <c r="J152" s="15" t="n"/>
+      <c r="K152" s="14" t="n"/>
+      <c r="L152" s="16" t="n"/>
+      <c r="M152" s="13" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -4092,10 +4321,11 @@
       <c r="F153" s="14" t="n"/>
       <c r="G153" s="14" t="n"/>
       <c r="H153" s="14" t="n"/>
-      <c r="I153" s="15" t="n"/>
-      <c r="J153" s="14" t="n"/>
-      <c r="K153" s="16" t="n"/>
-      <c r="L153" s="13" t="n"/>
+      <c r="I153" s="14" t="n"/>
+      <c r="J153" s="15" t="n"/>
+      <c r="K153" s="14" t="n"/>
+      <c r="L153" s="16" t="n"/>
+      <c r="M153" s="13" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n"/>
@@ -4106,10 +4336,11 @@
       <c r="F154" s="14" t="n"/>
       <c r="G154" s="14" t="n"/>
       <c r="H154" s="14" t="n"/>
-      <c r="I154" s="15" t="n"/>
-      <c r="J154" s="14" t="n"/>
-      <c r="K154" s="16" t="n"/>
-      <c r="L154" s="13" t="n"/>
+      <c r="I154" s="14" t="n"/>
+      <c r="J154" s="15" t="n"/>
+      <c r="K154" s="14" t="n"/>
+      <c r="L154" s="16" t="n"/>
+      <c r="M154" s="13" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -4120,10 +4351,11 @@
       <c r="F155" s="14" t="n"/>
       <c r="G155" s="14" t="n"/>
       <c r="H155" s="14" t="n"/>
-      <c r="I155" s="15" t="n"/>
-      <c r="J155" s="14" t="n"/>
-      <c r="K155" s="16" t="n"/>
-      <c r="L155" s="13" t="n"/>
+      <c r="I155" s="14" t="n"/>
+      <c r="J155" s="15" t="n"/>
+      <c r="K155" s="14" t="n"/>
+      <c r="L155" s="16" t="n"/>
+      <c r="M155" s="13" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -4134,10 +4366,11 @@
       <c r="F156" s="14" t="n"/>
       <c r="G156" s="14" t="n"/>
       <c r="H156" s="14" t="n"/>
-      <c r="I156" s="15" t="n"/>
-      <c r="J156" s="14" t="n"/>
-      <c r="K156" s="16" t="n"/>
-      <c r="L156" s="13" t="n"/>
+      <c r="I156" s="14" t="n"/>
+      <c r="J156" s="15" t="n"/>
+      <c r="K156" s="14" t="n"/>
+      <c r="L156" s="16" t="n"/>
+      <c r="M156" s="13" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -4148,10 +4381,11 @@
       <c r="F157" s="14" t="n"/>
       <c r="G157" s="14" t="n"/>
       <c r="H157" s="14" t="n"/>
-      <c r="I157" s="15" t="n"/>
-      <c r="J157" s="14" t="n"/>
-      <c r="K157" s="16" t="n"/>
-      <c r="L157" s="13" t="n"/>
+      <c r="I157" s="14" t="n"/>
+      <c r="J157" s="15" t="n"/>
+      <c r="K157" s="14" t="n"/>
+      <c r="L157" s="16" t="n"/>
+      <c r="M157" s="13" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -4162,10 +4396,11 @@
       <c r="F158" s="14" t="n"/>
       <c r="G158" s="14" t="n"/>
       <c r="H158" s="14" t="n"/>
-      <c r="I158" s="15" t="n"/>
-      <c r="J158" s="14" t="n"/>
-      <c r="K158" s="16" t="n"/>
-      <c r="L158" s="13" t="n"/>
+      <c r="I158" s="14" t="n"/>
+      <c r="J158" s="15" t="n"/>
+      <c r="K158" s="14" t="n"/>
+      <c r="L158" s="16" t="n"/>
+      <c r="M158" s="13" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="n"/>
@@ -4176,10 +4411,11 @@
       <c r="F159" s="14" t="n"/>
       <c r="G159" s="14" t="n"/>
       <c r="H159" s="14" t="n"/>
-      <c r="I159" s="15" t="n"/>
-      <c r="J159" s="14" t="n"/>
-      <c r="K159" s="16" t="n"/>
-      <c r="L159" s="13" t="n"/>
+      <c r="I159" s="14" t="n"/>
+      <c r="J159" s="15" t="n"/>
+      <c r="K159" s="14" t="n"/>
+      <c r="L159" s="16" t="n"/>
+      <c r="M159" s="13" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="n"/>
@@ -4190,10 +4426,11 @@
       <c r="F160" s="14" t="n"/>
       <c r="G160" s="14" t="n"/>
       <c r="H160" s="14" t="n"/>
-      <c r="I160" s="15" t="n"/>
-      <c r="J160" s="14" t="n"/>
-      <c r="K160" s="16" t="n"/>
-      <c r="L160" s="13" t="n"/>
+      <c r="I160" s="14" t="n"/>
+      <c r="J160" s="15" t="n"/>
+      <c r="K160" s="14" t="n"/>
+      <c r="L160" s="16" t="n"/>
+      <c r="M160" s="13" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="n"/>
@@ -4204,10 +4441,11 @@
       <c r="F161" s="14" t="n"/>
       <c r="G161" s="14" t="n"/>
       <c r="H161" s="14" t="n"/>
-      <c r="I161" s="15" t="n"/>
-      <c r="J161" s="14" t="n"/>
-      <c r="K161" s="16" t="n"/>
-      <c r="L161" s="13" t="n"/>
+      <c r="I161" s="14" t="n"/>
+      <c r="J161" s="15" t="n"/>
+      <c r="K161" s="14" t="n"/>
+      <c r="L161" s="16" t="n"/>
+      <c r="M161" s="13" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="n"/>
@@ -4218,10 +4456,11 @@
       <c r="F162" s="14" t="n"/>
       <c r="G162" s="14" t="n"/>
       <c r="H162" s="14" t="n"/>
-      <c r="I162" s="15" t="n"/>
-      <c r="J162" s="14" t="n"/>
-      <c r="K162" s="16" t="n"/>
-      <c r="L162" s="13" t="n"/>
+      <c r="I162" s="14" t="n"/>
+      <c r="J162" s="15" t="n"/>
+      <c r="K162" s="14" t="n"/>
+      <c r="L162" s="16" t="n"/>
+      <c r="M162" s="13" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="n"/>
@@ -4232,10 +4471,11 @@
       <c r="F163" s="14" t="n"/>
       <c r="G163" s="14" t="n"/>
       <c r="H163" s="14" t="n"/>
-      <c r="I163" s="15" t="n"/>
-      <c r="J163" s="14" t="n"/>
-      <c r="K163" s="16" t="n"/>
-      <c r="L163" s="13" t="n"/>
+      <c r="I163" s="14" t="n"/>
+      <c r="J163" s="15" t="n"/>
+      <c r="K163" s="14" t="n"/>
+      <c r="L163" s="16" t="n"/>
+      <c r="M163" s="13" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="n"/>
@@ -4246,10 +4486,11 @@
       <c r="F164" s="14" t="n"/>
       <c r="G164" s="14" t="n"/>
       <c r="H164" s="14" t="n"/>
-      <c r="I164" s="15" t="n"/>
-      <c r="J164" s="14" t="n"/>
-      <c r="K164" s="16" t="n"/>
-      <c r="L164" s="13" t="n"/>
+      <c r="I164" s="14" t="n"/>
+      <c r="J164" s="15" t="n"/>
+      <c r="K164" s="14" t="n"/>
+      <c r="L164" s="16" t="n"/>
+      <c r="M164" s="13" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="n"/>
@@ -4260,10 +4501,11 @@
       <c r="F165" s="14" t="n"/>
       <c r="G165" s="14" t="n"/>
       <c r="H165" s="14" t="n"/>
-      <c r="I165" s="15" t="n"/>
-      <c r="J165" s="14" t="n"/>
-      <c r="K165" s="16" t="n"/>
-      <c r="L165" s="13" t="n"/>
+      <c r="I165" s="14" t="n"/>
+      <c r="J165" s="15" t="n"/>
+      <c r="K165" s="14" t="n"/>
+      <c r="L165" s="16" t="n"/>
+      <c r="M165" s="13" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="n"/>
@@ -4274,10 +4516,11 @@
       <c r="F166" s="14" t="n"/>
       <c r="G166" s="14" t="n"/>
       <c r="H166" s="14" t="n"/>
-      <c r="I166" s="15" t="n"/>
-      <c r="J166" s="14" t="n"/>
-      <c r="K166" s="16" t="n"/>
-      <c r="L166" s="13" t="n"/>
+      <c r="I166" s="14" t="n"/>
+      <c r="J166" s="15" t="n"/>
+      <c r="K166" s="14" t="n"/>
+      <c r="L166" s="16" t="n"/>
+      <c r="M166" s="13" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="n"/>
@@ -4288,10 +4531,11 @@
       <c r="F167" s="14" t="n"/>
       <c r="G167" s="14" t="n"/>
       <c r="H167" s="14" t="n"/>
-      <c r="I167" s="15" t="n"/>
-      <c r="J167" s="14" t="n"/>
-      <c r="K167" s="16" t="n"/>
-      <c r="L167" s="13" t="n"/>
+      <c r="I167" s="14" t="n"/>
+      <c r="J167" s="15" t="n"/>
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="16" t="n"/>
+      <c r="M167" s="13" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="n"/>
@@ -4302,10 +4546,11 @@
       <c r="F168" s="14" t="n"/>
       <c r="G168" s="14" t="n"/>
       <c r="H168" s="14" t="n"/>
-      <c r="I168" s="15" t="n"/>
-      <c r="J168" s="14" t="n"/>
-      <c r="K168" s="16" t="n"/>
-      <c r="L168" s="13" t="n"/>
+      <c r="I168" s="14" t="n"/>
+      <c r="J168" s="15" t="n"/>
+      <c r="K168" s="14" t="n"/>
+      <c r="L168" s="16" t="n"/>
+      <c r="M168" s="13" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="n"/>
@@ -4316,10 +4561,11 @@
       <c r="F169" s="14" t="n"/>
       <c r="G169" s="14" t="n"/>
       <c r="H169" s="14" t="n"/>
-      <c r="I169" s="15" t="n"/>
-      <c r="J169" s="14" t="n"/>
-      <c r="K169" s="16" t="n"/>
-      <c r="L169" s="13" t="n"/>
+      <c r="I169" s="14" t="n"/>
+      <c r="J169" s="15" t="n"/>
+      <c r="K169" s="14" t="n"/>
+      <c r="L169" s="16" t="n"/>
+      <c r="M169" s="13" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="n"/>
@@ -4330,10 +4576,11 @@
       <c r="F170" s="14" t="n"/>
       <c r="G170" s="14" t="n"/>
       <c r="H170" s="14" t="n"/>
-      <c r="I170" s="15" t="n"/>
-      <c r="J170" s="14" t="n"/>
-      <c r="K170" s="16" t="n"/>
-      <c r="L170" s="13" t="n"/>
+      <c r="I170" s="14" t="n"/>
+      <c r="J170" s="15" t="n"/>
+      <c r="K170" s="14" t="n"/>
+      <c r="L170" s="16" t="n"/>
+      <c r="M170" s="13" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="n"/>
@@ -4344,10 +4591,11 @@
       <c r="F171" s="14" t="n"/>
       <c r="G171" s="14" t="n"/>
       <c r="H171" s="14" t="n"/>
-      <c r="I171" s="15" t="n"/>
-      <c r="J171" s="14" t="n"/>
-      <c r="K171" s="16" t="n"/>
-      <c r="L171" s="13" t="n"/>
+      <c r="I171" s="14" t="n"/>
+      <c r="J171" s="15" t="n"/>
+      <c r="K171" s="14" t="n"/>
+      <c r="L171" s="16" t="n"/>
+      <c r="M171" s="13" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="n"/>
@@ -4358,10 +4606,11 @@
       <c r="F172" s="14" t="n"/>
       <c r="G172" s="14" t="n"/>
       <c r="H172" s="14" t="n"/>
-      <c r="I172" s="15" t="n"/>
-      <c r="J172" s="14" t="n"/>
-      <c r="K172" s="16" t="n"/>
-      <c r="L172" s="13" t="n"/>
+      <c r="I172" s="14" t="n"/>
+      <c r="J172" s="15" t="n"/>
+      <c r="K172" s="14" t="n"/>
+      <c r="L172" s="16" t="n"/>
+      <c r="M172" s="13" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="n"/>
@@ -4372,10 +4621,11 @@
       <c r="F173" s="14" t="n"/>
       <c r="G173" s="14" t="n"/>
       <c r="H173" s="14" t="n"/>
-      <c r="I173" s="15" t="n"/>
-      <c r="J173" s="14" t="n"/>
-      <c r="K173" s="16" t="n"/>
-      <c r="L173" s="13" t="n"/>
+      <c r="I173" s="14" t="n"/>
+      <c r="J173" s="15" t="n"/>
+      <c r="K173" s="14" t="n"/>
+      <c r="L173" s="16" t="n"/>
+      <c r="M173" s="13" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n"/>
@@ -4386,10 +4636,11 @@
       <c r="F174" s="14" t="n"/>
       <c r="G174" s="14" t="n"/>
       <c r="H174" s="14" t="n"/>
-      <c r="I174" s="15" t="n"/>
-      <c r="J174" s="14" t="n"/>
-      <c r="K174" s="16" t="n"/>
-      <c r="L174" s="13" t="n"/>
+      <c r="I174" s="14" t="n"/>
+      <c r="J174" s="15" t="n"/>
+      <c r="K174" s="14" t="n"/>
+      <c r="L174" s="16" t="n"/>
+      <c r="M174" s="13" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="n"/>
@@ -4400,10 +4651,11 @@
       <c r="F175" s="14" t="n"/>
       <c r="G175" s="14" t="n"/>
       <c r="H175" s="14" t="n"/>
-      <c r="I175" s="15" t="n"/>
-      <c r="J175" s="14" t="n"/>
-      <c r="K175" s="16" t="n"/>
-      <c r="L175" s="13" t="n"/>
+      <c r="I175" s="14" t="n"/>
+      <c r="J175" s="15" t="n"/>
+      <c r="K175" s="14" t="n"/>
+      <c r="L175" s="16" t="n"/>
+      <c r="M175" s="13" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n"/>
@@ -4414,10 +4666,11 @@
       <c r="F176" s="14" t="n"/>
       <c r="G176" s="14" t="n"/>
       <c r="H176" s="14" t="n"/>
-      <c r="I176" s="15" t="n"/>
-      <c r="J176" s="14" t="n"/>
-      <c r="K176" s="16" t="n"/>
-      <c r="L176" s="13" t="n"/>
+      <c r="I176" s="14" t="n"/>
+      <c r="J176" s="15" t="n"/>
+      <c r="K176" s="14" t="n"/>
+      <c r="L176" s="16" t="n"/>
+      <c r="M176" s="13" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="n"/>
@@ -4428,10 +4681,11 @@
       <c r="F177" s="14" t="n"/>
       <c r="G177" s="14" t="n"/>
       <c r="H177" s="14" t="n"/>
-      <c r="I177" s="15" t="n"/>
-      <c r="J177" s="14" t="n"/>
-      <c r="K177" s="16" t="n"/>
-      <c r="L177" s="13" t="n"/>
+      <c r="I177" s="14" t="n"/>
+      <c r="J177" s="15" t="n"/>
+      <c r="K177" s="14" t="n"/>
+      <c r="L177" s="16" t="n"/>
+      <c r="M177" s="13" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n"/>
@@ -4442,10 +4696,11 @@
       <c r="F178" s="14" t="n"/>
       <c r="G178" s="14" t="n"/>
       <c r="H178" s="14" t="n"/>
-      <c r="I178" s="15" t="n"/>
-      <c r="J178" s="14" t="n"/>
-      <c r="K178" s="16" t="n"/>
-      <c r="L178" s="13" t="n"/>
+      <c r="I178" s="14" t="n"/>
+      <c r="J178" s="15" t="n"/>
+      <c r="K178" s="14" t="n"/>
+      <c r="L178" s="16" t="n"/>
+      <c r="M178" s="13" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="n"/>
@@ -4456,10 +4711,11 @@
       <c r="F179" s="14" t="n"/>
       <c r="G179" s="14" t="n"/>
       <c r="H179" s="14" t="n"/>
-      <c r="I179" s="15" t="n"/>
-      <c r="J179" s="14" t="n"/>
-      <c r="K179" s="16" t="n"/>
-      <c r="L179" s="13" t="n"/>
+      <c r="I179" s="14" t="n"/>
+      <c r="J179" s="15" t="n"/>
+      <c r="K179" s="14" t="n"/>
+      <c r="L179" s="16" t="n"/>
+      <c r="M179" s="13" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n"/>
@@ -4470,10 +4726,11 @@
       <c r="F180" s="14" t="n"/>
       <c r="G180" s="14" t="n"/>
       <c r="H180" s="14" t="n"/>
-      <c r="I180" s="15" t="n"/>
-      <c r="J180" s="14" t="n"/>
-      <c r="K180" s="16" t="n"/>
-      <c r="L180" s="13" t="n"/>
+      <c r="I180" s="14" t="n"/>
+      <c r="J180" s="15" t="n"/>
+      <c r="K180" s="14" t="n"/>
+      <c r="L180" s="16" t="n"/>
+      <c r="M180" s="13" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="n"/>
@@ -4484,10 +4741,11 @@
       <c r="F181" s="14" t="n"/>
       <c r="G181" s="14" t="n"/>
       <c r="H181" s="14" t="n"/>
-      <c r="I181" s="15" t="n"/>
-      <c r="J181" s="14" t="n"/>
-      <c r="K181" s="16" t="n"/>
-      <c r="L181" s="13" t="n"/>
+      <c r="I181" s="14" t="n"/>
+      <c r="J181" s="15" t="n"/>
+      <c r="K181" s="14" t="n"/>
+      <c r="L181" s="16" t="n"/>
+      <c r="M181" s="13" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n"/>
@@ -4498,10 +4756,11 @@
       <c r="F182" s="14" t="n"/>
       <c r="G182" s="14" t="n"/>
       <c r="H182" s="14" t="n"/>
-      <c r="I182" s="15" t="n"/>
-      <c r="J182" s="14" t="n"/>
-      <c r="K182" s="16" t="n"/>
-      <c r="L182" s="13" t="n"/>
+      <c r="I182" s="14" t="n"/>
+      <c r="J182" s="15" t="n"/>
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="16" t="n"/>
+      <c r="M182" s="13" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="n"/>
@@ -4512,10 +4771,11 @@
       <c r="F183" s="14" t="n"/>
       <c r="G183" s="14" t="n"/>
       <c r="H183" s="14" t="n"/>
-      <c r="I183" s="15" t="n"/>
-      <c r="J183" s="14" t="n"/>
-      <c r="K183" s="16" t="n"/>
-      <c r="L183" s="13" t="n"/>
+      <c r="I183" s="14" t="n"/>
+      <c r="J183" s="15" t="n"/>
+      <c r="K183" s="14" t="n"/>
+      <c r="L183" s="16" t="n"/>
+      <c r="M183" s="13" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n"/>
@@ -4526,10 +4786,11 @@
       <c r="F184" s="14" t="n"/>
       <c r="G184" s="14" t="n"/>
       <c r="H184" s="14" t="n"/>
-      <c r="I184" s="15" t="n"/>
-      <c r="J184" s="14" t="n"/>
-      <c r="K184" s="16" t="n"/>
-      <c r="L184" s="13" t="n"/>
+      <c r="I184" s="14" t="n"/>
+      <c r="J184" s="15" t="n"/>
+      <c r="K184" s="14" t="n"/>
+      <c r="L184" s="16" t="n"/>
+      <c r="M184" s="13" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="n"/>
@@ -4540,10 +4801,11 @@
       <c r="F185" s="14" t="n"/>
       <c r="G185" s="14" t="n"/>
       <c r="H185" s="14" t="n"/>
-      <c r="I185" s="15" t="n"/>
-      <c r="J185" s="14" t="n"/>
-      <c r="K185" s="16" t="n"/>
-      <c r="L185" s="13" t="n"/>
+      <c r="I185" s="14" t="n"/>
+      <c r="J185" s="15" t="n"/>
+      <c r="K185" s="14" t="n"/>
+      <c r="L185" s="16" t="n"/>
+      <c r="M185" s="13" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n"/>
@@ -4554,10 +4816,11 @@
       <c r="F186" s="14" t="n"/>
       <c r="G186" s="14" t="n"/>
       <c r="H186" s="14" t="n"/>
-      <c r="I186" s="15" t="n"/>
-      <c r="J186" s="14" t="n"/>
-      <c r="K186" s="16" t="n"/>
-      <c r="L186" s="13" t="n"/>
+      <c r="I186" s="14" t="n"/>
+      <c r="J186" s="15" t="n"/>
+      <c r="K186" s="14" t="n"/>
+      <c r="L186" s="16" t="n"/>
+      <c r="M186" s="13" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="n"/>
@@ -4568,10 +4831,11 @@
       <c r="F187" s="14" t="n"/>
       <c r="G187" s="14" t="n"/>
       <c r="H187" s="14" t="n"/>
-      <c r="I187" s="15" t="n"/>
-      <c r="J187" s="14" t="n"/>
-      <c r="K187" s="16" t="n"/>
-      <c r="L187" s="13" t="n"/>
+      <c r="I187" s="14" t="n"/>
+      <c r="J187" s="15" t="n"/>
+      <c r="K187" s="14" t="n"/>
+      <c r="L187" s="16" t="n"/>
+      <c r="M187" s="13" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n"/>
@@ -4582,10 +4846,11 @@
       <c r="F188" s="14" t="n"/>
       <c r="G188" s="14" t="n"/>
       <c r="H188" s="14" t="n"/>
-      <c r="I188" s="15" t="n"/>
-      <c r="J188" s="14" t="n"/>
-      <c r="K188" s="16" t="n"/>
-      <c r="L188" s="13" t="n"/>
+      <c r="I188" s="14" t="n"/>
+      <c r="J188" s="15" t="n"/>
+      <c r="K188" s="14" t="n"/>
+      <c r="L188" s="16" t="n"/>
+      <c r="M188" s="13" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="n"/>
@@ -4596,10 +4861,11 @@
       <c r="F189" s="14" t="n"/>
       <c r="G189" s="14" t="n"/>
       <c r="H189" s="14" t="n"/>
-      <c r="I189" s="15" t="n"/>
-      <c r="J189" s="14" t="n"/>
-      <c r="K189" s="16" t="n"/>
-      <c r="L189" s="13" t="n"/>
+      <c r="I189" s="14" t="n"/>
+      <c r="J189" s="15" t="n"/>
+      <c r="K189" s="14" t="n"/>
+      <c r="L189" s="16" t="n"/>
+      <c r="M189" s="13" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n"/>
@@ -4610,10 +4876,11 @@
       <c r="F190" s="14" t="n"/>
       <c r="G190" s="14" t="n"/>
       <c r="H190" s="14" t="n"/>
-      <c r="I190" s="15" t="n"/>
-      <c r="J190" s="14" t="n"/>
-      <c r="K190" s="16" t="n"/>
-      <c r="L190" s="13" t="n"/>
+      <c r="I190" s="14" t="n"/>
+      <c r="J190" s="15" t="n"/>
+      <c r="K190" s="14" t="n"/>
+      <c r="L190" s="16" t="n"/>
+      <c r="M190" s="13" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="n"/>
@@ -4624,10 +4891,11 @@
       <c r="F191" s="14" t="n"/>
       <c r="G191" s="14" t="n"/>
       <c r="H191" s="14" t="n"/>
-      <c r="I191" s="15" t="n"/>
-      <c r="J191" s="14" t="n"/>
-      <c r="K191" s="16" t="n"/>
-      <c r="L191" s="13" t="n"/>
+      <c r="I191" s="14" t="n"/>
+      <c r="J191" s="15" t="n"/>
+      <c r="K191" s="14" t="n"/>
+      <c r="L191" s="16" t="n"/>
+      <c r="M191" s="13" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n"/>
@@ -4638,10 +4906,11 @@
       <c r="F192" s="14" t="n"/>
       <c r="G192" s="14" t="n"/>
       <c r="H192" s="14" t="n"/>
-      <c r="I192" s="15" t="n"/>
-      <c r="J192" s="14" t="n"/>
-      <c r="K192" s="16" t="n"/>
-      <c r="L192" s="13" t="n"/>
+      <c r="I192" s="14" t="n"/>
+      <c r="J192" s="15" t="n"/>
+      <c r="K192" s="14" t="n"/>
+      <c r="L192" s="16" t="n"/>
+      <c r="M192" s="13" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="n"/>
@@ -4652,10 +4921,11 @@
       <c r="F193" s="14" t="n"/>
       <c r="G193" s="14" t="n"/>
       <c r="H193" s="14" t="n"/>
-      <c r="I193" s="15" t="n"/>
-      <c r="J193" s="14" t="n"/>
-      <c r="K193" s="16" t="n"/>
-      <c r="L193" s="13" t="n"/>
+      <c r="I193" s="14" t="n"/>
+      <c r="J193" s="15" t="n"/>
+      <c r="K193" s="14" t="n"/>
+      <c r="L193" s="16" t="n"/>
+      <c r="M193" s="13" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n"/>
@@ -4666,10 +4936,11 @@
       <c r="F194" s="14" t="n"/>
       <c r="G194" s="14" t="n"/>
       <c r="H194" s="14" t="n"/>
-      <c r="I194" s="15" t="n"/>
-      <c r="J194" s="14" t="n"/>
-      <c r="K194" s="16" t="n"/>
-      <c r="L194" s="13" t="n"/>
+      <c r="I194" s="14" t="n"/>
+      <c r="J194" s="15" t="n"/>
+      <c r="K194" s="14" t="n"/>
+      <c r="L194" s="16" t="n"/>
+      <c r="M194" s="13" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="n"/>
@@ -4680,10 +4951,11 @@
       <c r="F195" s="14" t="n"/>
       <c r="G195" s="14" t="n"/>
       <c r="H195" s="14" t="n"/>
-      <c r="I195" s="15" t="n"/>
-      <c r="J195" s="14" t="n"/>
-      <c r="K195" s="16" t="n"/>
-      <c r="L195" s="13" t="n"/>
+      <c r="I195" s="14" t="n"/>
+      <c r="J195" s="15" t="n"/>
+      <c r="K195" s="14" t="n"/>
+      <c r="L195" s="16" t="n"/>
+      <c r="M195" s="13" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n"/>
@@ -4694,10 +4966,11 @@
       <c r="F196" s="14" t="n"/>
       <c r="G196" s="14" t="n"/>
       <c r="H196" s="14" t="n"/>
-      <c r="I196" s="15" t="n"/>
-      <c r="J196" s="14" t="n"/>
-      <c r="K196" s="16" t="n"/>
-      <c r="L196" s="13" t="n"/>
+      <c r="I196" s="14" t="n"/>
+      <c r="J196" s="15" t="n"/>
+      <c r="K196" s="14" t="n"/>
+      <c r="L196" s="16" t="n"/>
+      <c r="M196" s="13" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="n"/>
@@ -4708,10 +4981,11 @@
       <c r="F197" s="14" t="n"/>
       <c r="G197" s="14" t="n"/>
       <c r="H197" s="14" t="n"/>
-      <c r="I197" s="15" t="n"/>
-      <c r="J197" s="14" t="n"/>
-      <c r="K197" s="16" t="n"/>
-      <c r="L197" s="13" t="n"/>
+      <c r="I197" s="14" t="n"/>
+      <c r="J197" s="15" t="n"/>
+      <c r="K197" s="14" t="n"/>
+      <c r="L197" s="16" t="n"/>
+      <c r="M197" s="13" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n"/>
@@ -4722,10 +4996,11 @@
       <c r="F198" s="14" t="n"/>
       <c r="G198" s="14" t="n"/>
       <c r="H198" s="14" t="n"/>
-      <c r="I198" s="15" t="n"/>
-      <c r="J198" s="14" t="n"/>
-      <c r="K198" s="16" t="n"/>
-      <c r="L198" s="13" t="n"/>
+      <c r="I198" s="14" t="n"/>
+      <c r="J198" s="15" t="n"/>
+      <c r="K198" s="14" t="n"/>
+      <c r="L198" s="16" t="n"/>
+      <c r="M198" s="13" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="n"/>
@@ -4736,10 +5011,11 @@
       <c r="F199" s="14" t="n"/>
       <c r="G199" s="14" t="n"/>
       <c r="H199" s="14" t="n"/>
-      <c r="I199" s="15" t="n"/>
-      <c r="J199" s="14" t="n"/>
-      <c r="K199" s="16" t="n"/>
-      <c r="L199" s="13" t="n"/>
+      <c r="I199" s="14" t="n"/>
+      <c r="J199" s="15" t="n"/>
+      <c r="K199" s="14" t="n"/>
+      <c r="L199" s="16" t="n"/>
+      <c r="M199" s="13" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n"/>
@@ -4750,10 +5026,11 @@
       <c r="F200" s="14" t="n"/>
       <c r="G200" s="14" t="n"/>
       <c r="H200" s="14" t="n"/>
-      <c r="I200" s="15" t="n"/>
-      <c r="J200" s="14" t="n"/>
-      <c r="K200" s="16" t="n"/>
-      <c r="L200" s="13" t="n"/>
+      <c r="I200" s="14" t="n"/>
+      <c r="J200" s="15" t="n"/>
+      <c r="K200" s="14" t="n"/>
+      <c r="L200" s="16" t="n"/>
+      <c r="M200" s="13" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="n"/>
@@ -4764,10 +5041,11 @@
       <c r="F201" s="14" t="n"/>
       <c r="G201" s="14" t="n"/>
       <c r="H201" s="14" t="n"/>
-      <c r="I201" s="15" t="n"/>
-      <c r="J201" s="14" t="n"/>
-      <c r="K201" s="16" t="n"/>
-      <c r="L201" s="13" t="n"/>
+      <c r="I201" s="14" t="n"/>
+      <c r="J201" s="15" t="n"/>
+      <c r="K201" s="14" t="n"/>
+      <c r="L201" s="16" t="n"/>
+      <c r="M201" s="13" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n"/>
@@ -4778,10 +5056,11 @@
       <c r="F202" s="14" t="n"/>
       <c r="G202" s="14" t="n"/>
       <c r="H202" s="14" t="n"/>
-      <c r="I202" s="15" t="n"/>
-      <c r="J202" s="14" t="n"/>
-      <c r="K202" s="16" t="n"/>
-      <c r="L202" s="13" t="n"/>
+      <c r="I202" s="14" t="n"/>
+      <c r="J202" s="15" t="n"/>
+      <c r="K202" s="14" t="n"/>
+      <c r="L202" s="16" t="n"/>
+      <c r="M202" s="13" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="n"/>
@@ -4792,10 +5071,11 @@
       <c r="F203" s="14" t="n"/>
       <c r="G203" s="14" t="n"/>
       <c r="H203" s="14" t="n"/>
-      <c r="I203" s="15" t="n"/>
-      <c r="J203" s="14" t="n"/>
-      <c r="K203" s="16" t="n"/>
-      <c r="L203" s="13" t="n"/>
+      <c r="I203" s="14" t="n"/>
+      <c r="J203" s="15" t="n"/>
+      <c r="K203" s="14" t="n"/>
+      <c r="L203" s="16" t="n"/>
+      <c r="M203" s="13" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n"/>
@@ -4806,10 +5086,11 @@
       <c r="F204" s="14" t="n"/>
       <c r="G204" s="14" t="n"/>
       <c r="H204" s="14" t="n"/>
-      <c r="I204" s="15" t="n"/>
-      <c r="J204" s="14" t="n"/>
-      <c r="K204" s="16" t="n"/>
-      <c r="L204" s="13" t="n"/>
+      <c r="I204" s="14" t="n"/>
+      <c r="J204" s="15" t="n"/>
+      <c r="K204" s="14" t="n"/>
+      <c r="L204" s="16" t="n"/>
+      <c r="M204" s="13" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="n"/>
@@ -4820,10 +5101,11 @@
       <c r="F205" s="14" t="n"/>
       <c r="G205" s="14" t="n"/>
       <c r="H205" s="14" t="n"/>
-      <c r="I205" s="15" t="n"/>
-      <c r="J205" s="14" t="n"/>
-      <c r="K205" s="16" t="n"/>
-      <c r="L205" s="13" t="n"/>
+      <c r="I205" s="14" t="n"/>
+      <c r="J205" s="15" t="n"/>
+      <c r="K205" s="14" t="n"/>
+      <c r="L205" s="16" t="n"/>
+      <c r="M205" s="13" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="n"/>
@@ -4834,10 +5116,11 @@
       <c r="F206" s="14" t="n"/>
       <c r="G206" s="14" t="n"/>
       <c r="H206" s="14" t="n"/>
-      <c r="I206" s="15" t="n"/>
-      <c r="J206" s="14" t="n"/>
-      <c r="K206" s="16" t="n"/>
-      <c r="L206" s="13" t="n"/>
+      <c r="I206" s="14" t="n"/>
+      <c r="J206" s="15" t="n"/>
+      <c r="K206" s="14" t="n"/>
+      <c r="L206" s="16" t="n"/>
+      <c r="M206" s="13" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="n"/>
@@ -4848,10 +5131,11 @@
       <c r="F207" s="14" t="n"/>
       <c r="G207" s="14" t="n"/>
       <c r="H207" s="14" t="n"/>
-      <c r="I207" s="15" t="n"/>
-      <c r="J207" s="14" t="n"/>
-      <c r="K207" s="16" t="n"/>
-      <c r="L207" s="13" t="n"/>
+      <c r="I207" s="14" t="n"/>
+      <c r="J207" s="15" t="n"/>
+      <c r="K207" s="14" t="n"/>
+      <c r="L207" s="16" t="n"/>
+      <c r="M207" s="13" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="n"/>
@@ -4862,10 +5146,11 @@
       <c r="F208" s="14" t="n"/>
       <c r="G208" s="14" t="n"/>
       <c r="H208" s="14" t="n"/>
-      <c r="I208" s="15" t="n"/>
-      <c r="J208" s="14" t="n"/>
-      <c r="K208" s="16" t="n"/>
-      <c r="L208" s="13" t="n"/>
+      <c r="I208" s="14" t="n"/>
+      <c r="J208" s="15" t="n"/>
+      <c r="K208" s="14" t="n"/>
+      <c r="L208" s="16" t="n"/>
+      <c r="M208" s="13" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="n"/>
@@ -4876,10 +5161,11 @@
       <c r="F209" s="14" t="n"/>
       <c r="G209" s="14" t="n"/>
       <c r="H209" s="14" t="n"/>
-      <c r="I209" s="15" t="n"/>
-      <c r="J209" s="14" t="n"/>
-      <c r="K209" s="16" t="n"/>
-      <c r="L209" s="13" t="n"/>
+      <c r="I209" s="14" t="n"/>
+      <c r="J209" s="15" t="n"/>
+      <c r="K209" s="14" t="n"/>
+      <c r="L209" s="16" t="n"/>
+      <c r="M209" s="13" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="n"/>
@@ -4890,10 +5176,11 @@
       <c r="F210" s="14" t="n"/>
       <c r="G210" s="14" t="n"/>
       <c r="H210" s="14" t="n"/>
-      <c r="I210" s="15" t="n"/>
-      <c r="J210" s="14" t="n"/>
-      <c r="K210" s="16" t="n"/>
-      <c r="L210" s="13" t="n"/>
+      <c r="I210" s="14" t="n"/>
+      <c r="J210" s="15" t="n"/>
+      <c r="K210" s="14" t="n"/>
+      <c r="L210" s="16" t="n"/>
+      <c r="M210" s="13" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="n"/>
@@ -4904,10 +5191,11 @@
       <c r="F211" s="14" t="n"/>
       <c r="G211" s="14" t="n"/>
       <c r="H211" s="14" t="n"/>
-      <c r="I211" s="15" t="n"/>
-      <c r="J211" s="14" t="n"/>
-      <c r="K211" s="16" t="n"/>
-      <c r="L211" s="13" t="n"/>
+      <c r="I211" s="14" t="n"/>
+      <c r="J211" s="15" t="n"/>
+      <c r="K211" s="14" t="n"/>
+      <c r="L211" s="16" t="n"/>
+      <c r="M211" s="13" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="n"/>
@@ -4918,10 +5206,11 @@
       <c r="F212" s="14" t="n"/>
       <c r="G212" s="14" t="n"/>
       <c r="H212" s="14" t="n"/>
-      <c r="I212" s="15" t="n"/>
-      <c r="J212" s="14" t="n"/>
-      <c r="K212" s="16" t="n"/>
-      <c r="L212" s="13" t="n"/>
+      <c r="I212" s="14" t="n"/>
+      <c r="J212" s="15" t="n"/>
+      <c r="K212" s="14" t="n"/>
+      <c r="L212" s="16" t="n"/>
+      <c r="M212" s="13" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="n"/>
@@ -4932,10 +5221,11 @@
       <c r="F213" s="14" t="n"/>
       <c r="G213" s="14" t="n"/>
       <c r="H213" s="14" t="n"/>
-      <c r="I213" s="15" t="n"/>
-      <c r="J213" s="14" t="n"/>
-      <c r="K213" s="16" t="n"/>
-      <c r="L213" s="13" t="n"/>
+      <c r="I213" s="14" t="n"/>
+      <c r="J213" s="15" t="n"/>
+      <c r="K213" s="14" t="n"/>
+      <c r="L213" s="16" t="n"/>
+      <c r="M213" s="13" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="n"/>
@@ -4946,10 +5236,11 @@
       <c r="F214" s="14" t="n"/>
       <c r="G214" s="14" t="n"/>
       <c r="H214" s="14" t="n"/>
-      <c r="I214" s="15" t="n"/>
-      <c r="J214" s="14" t="n"/>
-      <c r="K214" s="16" t="n"/>
-      <c r="L214" s="13" t="n"/>
+      <c r="I214" s="14" t="n"/>
+      <c r="J214" s="15" t="n"/>
+      <c r="K214" s="14" t="n"/>
+      <c r="L214" s="16" t="n"/>
+      <c r="M214" s="13" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="n"/>
@@ -4960,10 +5251,11 @@
       <c r="F215" s="14" t="n"/>
       <c r="G215" s="14" t="n"/>
       <c r="H215" s="14" t="n"/>
-      <c r="I215" s="15" t="n"/>
-      <c r="J215" s="14" t="n"/>
-      <c r="K215" s="16" t="n"/>
-      <c r="L215" s="13" t="n"/>
+      <c r="I215" s="14" t="n"/>
+      <c r="J215" s="15" t="n"/>
+      <c r="K215" s="14" t="n"/>
+      <c r="L215" s="16" t="n"/>
+      <c r="M215" s="13" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="n"/>
@@ -4974,10 +5266,11 @@
       <c r="F216" s="14" t="n"/>
       <c r="G216" s="14" t="n"/>
       <c r="H216" s="14" t="n"/>
-      <c r="I216" s="15" t="n"/>
-      <c r="J216" s="14" t="n"/>
-      <c r="K216" s="16" t="n"/>
-      <c r="L216" s="13" t="n"/>
+      <c r="I216" s="14" t="n"/>
+      <c r="J216" s="15" t="n"/>
+      <c r="K216" s="14" t="n"/>
+      <c r="L216" s="16" t="n"/>
+      <c r="M216" s="13" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="n"/>
@@ -4988,10 +5281,11 @@
       <c r="F217" s="14" t="n"/>
       <c r="G217" s="14" t="n"/>
       <c r="H217" s="14" t="n"/>
-      <c r="I217" s="15" t="n"/>
-      <c r="J217" s="14" t="n"/>
-      <c r="K217" s="16" t="n"/>
-      <c r="L217" s="13" t="n"/>
+      <c r="I217" s="14" t="n"/>
+      <c r="J217" s="15" t="n"/>
+      <c r="K217" s="14" t="n"/>
+      <c r="L217" s="16" t="n"/>
+      <c r="M217" s="13" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="n"/>
@@ -5002,10 +5296,11 @@
       <c r="F218" s="14" t="n"/>
       <c r="G218" s="14" t="n"/>
       <c r="H218" s="14" t="n"/>
-      <c r="I218" s="15" t="n"/>
-      <c r="J218" s="14" t="n"/>
-      <c r="K218" s="16" t="n"/>
-      <c r="L218" s="13" t="n"/>
+      <c r="I218" s="14" t="n"/>
+      <c r="J218" s="15" t="n"/>
+      <c r="K218" s="14" t="n"/>
+      <c r="L218" s="16" t="n"/>
+      <c r="M218" s="13" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="n"/>
@@ -5016,10 +5311,11 @@
       <c r="F219" s="14" t="n"/>
       <c r="G219" s="14" t="n"/>
       <c r="H219" s="14" t="n"/>
-      <c r="I219" s="15" t="n"/>
-      <c r="J219" s="14" t="n"/>
-      <c r="K219" s="16" t="n"/>
-      <c r="L219" s="13" t="n"/>
+      <c r="I219" s="14" t="n"/>
+      <c r="J219" s="15" t="n"/>
+      <c r="K219" s="14" t="n"/>
+      <c r="L219" s="16" t="n"/>
+      <c r="M219" s="13" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="n"/>
@@ -5030,10 +5326,11 @@
       <c r="F220" s="14" t="n"/>
       <c r="G220" s="14" t="n"/>
       <c r="H220" s="14" t="n"/>
-      <c r="I220" s="15" t="n"/>
-      <c r="J220" s="14" t="n"/>
-      <c r="K220" s="16" t="n"/>
-      <c r="L220" s="13" t="n"/>
+      <c r="I220" s="14" t="n"/>
+      <c r="J220" s="15" t="n"/>
+      <c r="K220" s="14" t="n"/>
+      <c r="L220" s="16" t="n"/>
+      <c r="M220" s="13" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="n"/>
@@ -5044,10 +5341,11 @@
       <c r="F221" s="14" t="n"/>
       <c r="G221" s="14" t="n"/>
       <c r="H221" s="14" t="n"/>
-      <c r="I221" s="15" t="n"/>
-      <c r="J221" s="14" t="n"/>
-      <c r="K221" s="16" t="n"/>
-      <c r="L221" s="13" t="n"/>
+      <c r="I221" s="14" t="n"/>
+      <c r="J221" s="15" t="n"/>
+      <c r="K221" s="14" t="n"/>
+      <c r="L221" s="16" t="n"/>
+      <c r="M221" s="13" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="n"/>
@@ -5058,10 +5356,11 @@
       <c r="F222" s="14" t="n"/>
       <c r="G222" s="14" t="n"/>
       <c r="H222" s="14" t="n"/>
-      <c r="I222" s="15" t="n"/>
-      <c r="J222" s="14" t="n"/>
-      <c r="K222" s="16" t="n"/>
-      <c r="L222" s="13" t="n"/>
+      <c r="I222" s="14" t="n"/>
+      <c r="J222" s="15" t="n"/>
+      <c r="K222" s="14" t="n"/>
+      <c r="L222" s="16" t="n"/>
+      <c r="M222" s="13" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="n"/>
@@ -5072,10 +5371,11 @@
       <c r="F223" s="14" t="n"/>
       <c r="G223" s="14" t="n"/>
       <c r="H223" s="14" t="n"/>
-      <c r="I223" s="15" t="n"/>
-      <c r="J223" s="14" t="n"/>
-      <c r="K223" s="16" t="n"/>
-      <c r="L223" s="13" t="n"/>
+      <c r="I223" s="14" t="n"/>
+      <c r="J223" s="15" t="n"/>
+      <c r="K223" s="14" t="n"/>
+      <c r="L223" s="16" t="n"/>
+      <c r="M223" s="13" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="n"/>
@@ -5086,10 +5386,11 @@
       <c r="F224" s="14" t="n"/>
       <c r="G224" s="14" t="n"/>
       <c r="H224" s="14" t="n"/>
-      <c r="I224" s="15" t="n"/>
-      <c r="J224" s="14" t="n"/>
-      <c r="K224" s="16" t="n"/>
-      <c r="L224" s="13" t="n"/>
+      <c r="I224" s="14" t="n"/>
+      <c r="J224" s="15" t="n"/>
+      <c r="K224" s="14" t="n"/>
+      <c r="L224" s="16" t="n"/>
+      <c r="M224" s="13" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="n"/>
@@ -5100,10 +5401,11 @@
       <c r="F225" s="14" t="n"/>
       <c r="G225" s="14" t="n"/>
       <c r="H225" s="14" t="n"/>
-      <c r="I225" s="15" t="n"/>
-      <c r="J225" s="14" t="n"/>
-      <c r="K225" s="16" t="n"/>
-      <c r="L225" s="13" t="n"/>
+      <c r="I225" s="14" t="n"/>
+      <c r="J225" s="15" t="n"/>
+      <c r="K225" s="14" t="n"/>
+      <c r="L225" s="16" t="n"/>
+      <c r="M225" s="13" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="n"/>
@@ -5114,10 +5416,11 @@
       <c r="F226" s="14" t="n"/>
       <c r="G226" s="14" t="n"/>
       <c r="H226" s="14" t="n"/>
-      <c r="I226" s="15" t="n"/>
-      <c r="J226" s="14" t="n"/>
-      <c r="K226" s="16" t="n"/>
-      <c r="L226" s="13" t="n"/>
+      <c r="I226" s="14" t="n"/>
+      <c r="J226" s="15" t="n"/>
+      <c r="K226" s="14" t="n"/>
+      <c r="L226" s="16" t="n"/>
+      <c r="M226" s="13" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="n"/>
@@ -5128,10 +5431,11 @@
       <c r="F227" s="14" t="n"/>
       <c r="G227" s="14" t="n"/>
       <c r="H227" s="14" t="n"/>
-      <c r="I227" s="15" t="n"/>
-      <c r="J227" s="14" t="n"/>
-      <c r="K227" s="16" t="n"/>
-      <c r="L227" s="13" t="n"/>
+      <c r="I227" s="14" t="n"/>
+      <c r="J227" s="15" t="n"/>
+      <c r="K227" s="14" t="n"/>
+      <c r="L227" s="16" t="n"/>
+      <c r="M227" s="13" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="n"/>
@@ -5142,10 +5446,11 @@
       <c r="F228" s="14" t="n"/>
       <c r="G228" s="14" t="n"/>
       <c r="H228" s="14" t="n"/>
-      <c r="I228" s="15" t="n"/>
-      <c r="J228" s="14" t="n"/>
-      <c r="K228" s="16" t="n"/>
-      <c r="L228" s="13" t="n"/>
+      <c r="I228" s="14" t="n"/>
+      <c r="J228" s="15" t="n"/>
+      <c r="K228" s="14" t="n"/>
+      <c r="L228" s="16" t="n"/>
+      <c r="M228" s="13" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="n"/>
@@ -5156,10 +5461,11 @@
       <c r="F229" s="14" t="n"/>
       <c r="G229" s="14" t="n"/>
       <c r="H229" s="14" t="n"/>
-      <c r="I229" s="15" t="n"/>
-      <c r="J229" s="14" t="n"/>
-      <c r="K229" s="16" t="n"/>
-      <c r="L229" s="13" t="n"/>
+      <c r="I229" s="14" t="n"/>
+      <c r="J229" s="15" t="n"/>
+      <c r="K229" s="14" t="n"/>
+      <c r="L229" s="16" t="n"/>
+      <c r="M229" s="13" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="n"/>
@@ -5170,10 +5476,11 @@
       <c r="F230" s="14" t="n"/>
       <c r="G230" s="14" t="n"/>
       <c r="H230" s="14" t="n"/>
-      <c r="I230" s="15" t="n"/>
-      <c r="J230" s="14" t="n"/>
-      <c r="K230" s="16" t="n"/>
-      <c r="L230" s="13" t="n"/>
+      <c r="I230" s="14" t="n"/>
+      <c r="J230" s="15" t="n"/>
+      <c r="K230" s="14" t="n"/>
+      <c r="L230" s="16" t="n"/>
+      <c r="M230" s="13" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="n"/>
@@ -5184,10 +5491,11 @@
       <c r="F231" s="14" t="n"/>
       <c r="G231" s="14" t="n"/>
       <c r="H231" s="14" t="n"/>
-      <c r="I231" s="15" t="n"/>
-      <c r="J231" s="14" t="n"/>
-      <c r="K231" s="16" t="n"/>
-      <c r="L231" s="13" t="n"/>
+      <c r="I231" s="14" t="n"/>
+      <c r="J231" s="15" t="n"/>
+      <c r="K231" s="14" t="n"/>
+      <c r="L231" s="16" t="n"/>
+      <c r="M231" s="13" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="n"/>
@@ -5198,10 +5506,11 @@
       <c r="F232" s="14" t="n"/>
       <c r="G232" s="14" t="n"/>
       <c r="H232" s="14" t="n"/>
-      <c r="I232" s="15" t="n"/>
-      <c r="J232" s="14" t="n"/>
-      <c r="K232" s="16" t="n"/>
-      <c r="L232" s="13" t="n"/>
+      <c r="I232" s="14" t="n"/>
+      <c r="J232" s="15" t="n"/>
+      <c r="K232" s="14" t="n"/>
+      <c r="L232" s="16" t="n"/>
+      <c r="M232" s="13" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="n"/>
@@ -5212,10 +5521,11 @@
       <c r="F233" s="14" t="n"/>
       <c r="G233" s="14" t="n"/>
       <c r="H233" s="14" t="n"/>
-      <c r="I233" s="15" t="n"/>
-      <c r="J233" s="14" t="n"/>
-      <c r="K233" s="16" t="n"/>
-      <c r="L233" s="13" t="n"/>
+      <c r="I233" s="14" t="n"/>
+      <c r="J233" s="15" t="n"/>
+      <c r="K233" s="14" t="n"/>
+      <c r="L233" s="16" t="n"/>
+      <c r="M233" s="13" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="n"/>
@@ -5226,10 +5536,11 @@
       <c r="F234" s="14" t="n"/>
       <c r="G234" s="14" t="n"/>
       <c r="H234" s="14" t="n"/>
-      <c r="I234" s="15" t="n"/>
-      <c r="J234" s="14" t="n"/>
-      <c r="K234" s="16" t="n"/>
-      <c r="L234" s="13" t="n"/>
+      <c r="I234" s="14" t="n"/>
+      <c r="J234" s="15" t="n"/>
+      <c r="K234" s="14" t="n"/>
+      <c r="L234" s="16" t="n"/>
+      <c r="M234" s="13" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="n"/>
@@ -5240,10 +5551,11 @@
       <c r="F235" s="14" t="n"/>
       <c r="G235" s="14" t="n"/>
       <c r="H235" s="14" t="n"/>
-      <c r="I235" s="15" t="n"/>
-      <c r="J235" s="14" t="n"/>
-      <c r="K235" s="16" t="n"/>
-      <c r="L235" s="13" t="n"/>
+      <c r="I235" s="14" t="n"/>
+      <c r="J235" s="15" t="n"/>
+      <c r="K235" s="14" t="n"/>
+      <c r="L235" s="16" t="n"/>
+      <c r="M235" s="13" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="n"/>
@@ -5254,10 +5566,11 @@
       <c r="F236" s="14" t="n"/>
       <c r="G236" s="14" t="n"/>
       <c r="H236" s="14" t="n"/>
-      <c r="I236" s="15" t="n"/>
-      <c r="J236" s="14" t="n"/>
-      <c r="K236" s="16" t="n"/>
-      <c r="L236" s="13" t="n"/>
+      <c r="I236" s="14" t="n"/>
+      <c r="J236" s="15" t="n"/>
+      <c r="K236" s="14" t="n"/>
+      <c r="L236" s="16" t="n"/>
+      <c r="M236" s="13" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="n"/>
@@ -5268,10 +5581,11 @@
       <c r="F237" s="14" t="n"/>
       <c r="G237" s="14" t="n"/>
       <c r="H237" s="14" t="n"/>
-      <c r="I237" s="15" t="n"/>
-      <c r="J237" s="14" t="n"/>
-      <c r="K237" s="16" t="n"/>
-      <c r="L237" s="13" t="n"/>
+      <c r="I237" s="14" t="n"/>
+      <c r="J237" s="15" t="n"/>
+      <c r="K237" s="14" t="n"/>
+      <c r="L237" s="16" t="n"/>
+      <c r="M237" s="13" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="n"/>
@@ -5282,10 +5596,11 @@
       <c r="F238" s="14" t="n"/>
       <c r="G238" s="14" t="n"/>
       <c r="H238" s="14" t="n"/>
-      <c r="I238" s="15" t="n"/>
-      <c r="J238" s="14" t="n"/>
-      <c r="K238" s="16" t="n"/>
-      <c r="L238" s="13" t="n"/>
+      <c r="I238" s="14" t="n"/>
+      <c r="J238" s="15" t="n"/>
+      <c r="K238" s="14" t="n"/>
+      <c r="L238" s="16" t="n"/>
+      <c r="M238" s="13" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="n"/>
@@ -5296,10 +5611,11 @@
       <c r="F239" s="14" t="n"/>
       <c r="G239" s="14" t="n"/>
       <c r="H239" s="14" t="n"/>
-      <c r="I239" s="15" t="n"/>
-      <c r="J239" s="14" t="n"/>
-      <c r="K239" s="16" t="n"/>
-      <c r="L239" s="13" t="n"/>
+      <c r="I239" s="14" t="n"/>
+      <c r="J239" s="15" t="n"/>
+      <c r="K239" s="14" t="n"/>
+      <c r="L239" s="16" t="n"/>
+      <c r="M239" s="13" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="n"/>
@@ -5310,10 +5626,11 @@
       <c r="F240" s="14" t="n"/>
       <c r="G240" s="14" t="n"/>
       <c r="H240" s="14" t="n"/>
-      <c r="I240" s="15" t="n"/>
-      <c r="J240" s="14" t="n"/>
-      <c r="K240" s="16" t="n"/>
-      <c r="L240" s="13" t="n"/>
+      <c r="I240" s="14" t="n"/>
+      <c r="J240" s="15" t="n"/>
+      <c r="K240" s="14" t="n"/>
+      <c r="L240" s="16" t="n"/>
+      <c r="M240" s="13" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="n"/>
@@ -5324,10 +5641,11 @@
       <c r="F241" s="14" t="n"/>
       <c r="G241" s="14" t="n"/>
       <c r="H241" s="14" t="n"/>
-      <c r="I241" s="15" t="n"/>
-      <c r="J241" s="14" t="n"/>
-      <c r="K241" s="16" t="n"/>
-      <c r="L241" s="13" t="n"/>
+      <c r="I241" s="14" t="n"/>
+      <c r="J241" s="15" t="n"/>
+      <c r="K241" s="14" t="n"/>
+      <c r="L241" s="16" t="n"/>
+      <c r="M241" s="13" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="n"/>
@@ -5338,10 +5656,11 @@
       <c r="F242" s="14" t="n"/>
       <c r="G242" s="14" t="n"/>
       <c r="H242" s="14" t="n"/>
-      <c r="I242" s="15" t="n"/>
-      <c r="J242" s="14" t="n"/>
-      <c r="K242" s="16" t="n"/>
-      <c r="L242" s="13" t="n"/>
+      <c r="I242" s="14" t="n"/>
+      <c r="J242" s="15" t="n"/>
+      <c r="K242" s="14" t="n"/>
+      <c r="L242" s="16" t="n"/>
+      <c r="M242" s="13" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="n"/>
@@ -5352,10 +5671,11 @@
       <c r="F243" s="14" t="n"/>
       <c r="G243" s="14" t="n"/>
       <c r="H243" s="14" t="n"/>
-      <c r="I243" s="15" t="n"/>
-      <c r="J243" s="14" t="n"/>
-      <c r="K243" s="16" t="n"/>
-      <c r="L243" s="13" t="n"/>
+      <c r="I243" s="14" t="n"/>
+      <c r="J243" s="15" t="n"/>
+      <c r="K243" s="14" t="n"/>
+      <c r="L243" s="16" t="n"/>
+      <c r="M243" s="13" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="n"/>
@@ -5366,10 +5686,11 @@
       <c r="F244" s="14" t="n"/>
       <c r="G244" s="14" t="n"/>
       <c r="H244" s="14" t="n"/>
-      <c r="I244" s="15" t="n"/>
-      <c r="J244" s="14" t="n"/>
-      <c r="K244" s="16" t="n"/>
-      <c r="L244" s="13" t="n"/>
+      <c r="I244" s="14" t="n"/>
+      <c r="J244" s="15" t="n"/>
+      <c r="K244" s="14" t="n"/>
+      <c r="L244" s="16" t="n"/>
+      <c r="M244" s="13" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="n"/>
@@ -5380,10 +5701,11 @@
       <c r="F245" s="14" t="n"/>
       <c r="G245" s="14" t="n"/>
       <c r="H245" s="14" t="n"/>
-      <c r="I245" s="15" t="n"/>
-      <c r="J245" s="14" t="n"/>
-      <c r="K245" s="16" t="n"/>
-      <c r="L245" s="13" t="n"/>
+      <c r="I245" s="14" t="n"/>
+      <c r="J245" s="15" t="n"/>
+      <c r="K245" s="14" t="n"/>
+      <c r="L245" s="16" t="n"/>
+      <c r="M245" s="13" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="n"/>
@@ -5394,10 +5716,11 @@
       <c r="F246" s="14" t="n"/>
       <c r="G246" s="14" t="n"/>
       <c r="H246" s="14" t="n"/>
-      <c r="I246" s="15" t="n"/>
-      <c r="J246" s="14" t="n"/>
-      <c r="K246" s="16" t="n"/>
-      <c r="L246" s="13" t="n"/>
+      <c r="I246" s="14" t="n"/>
+      <c r="J246" s="15" t="n"/>
+      <c r="K246" s="14" t="n"/>
+      <c r="L246" s="16" t="n"/>
+      <c r="M246" s="13" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="n"/>
@@ -5408,10 +5731,11 @@
       <c r="F247" s="14" t="n"/>
       <c r="G247" s="14" t="n"/>
       <c r="H247" s="14" t="n"/>
-      <c r="I247" s="15" t="n"/>
-      <c r="J247" s="14" t="n"/>
-      <c r="K247" s="16" t="n"/>
-      <c r="L247" s="13" t="n"/>
+      <c r="I247" s="14" t="n"/>
+      <c r="J247" s="15" t="n"/>
+      <c r="K247" s="14" t="n"/>
+      <c r="L247" s="16" t="n"/>
+      <c r="M247" s="13" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="n"/>
@@ -5422,10 +5746,11 @@
       <c r="F248" s="14" t="n"/>
       <c r="G248" s="14" t="n"/>
       <c r="H248" s="14" t="n"/>
-      <c r="I248" s="15" t="n"/>
-      <c r="J248" s="14" t="n"/>
-      <c r="K248" s="16" t="n"/>
-      <c r="L248" s="13" t="n"/>
+      <c r="I248" s="14" t="n"/>
+      <c r="J248" s="15" t="n"/>
+      <c r="K248" s="14" t="n"/>
+      <c r="L248" s="16" t="n"/>
+      <c r="M248" s="13" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="n"/>
@@ -5436,10 +5761,11 @@
       <c r="F249" s="14" t="n"/>
       <c r="G249" s="14" t="n"/>
       <c r="H249" s="14" t="n"/>
-      <c r="I249" s="15" t="n"/>
-      <c r="J249" s="14" t="n"/>
-      <c r="K249" s="16" t="n"/>
-      <c r="L249" s="13" t="n"/>
+      <c r="I249" s="14" t="n"/>
+      <c r="J249" s="15" t="n"/>
+      <c r="K249" s="14" t="n"/>
+      <c r="L249" s="16" t="n"/>
+      <c r="M249" s="13" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="n"/>
@@ -5450,10 +5776,11 @@
       <c r="F250" s="14" t="n"/>
       <c r="G250" s="14" t="n"/>
       <c r="H250" s="14" t="n"/>
-      <c r="I250" s="15" t="n"/>
-      <c r="J250" s="14" t="n"/>
-      <c r="K250" s="16" t="n"/>
-      <c r="L250" s="13" t="n"/>
+      <c r="I250" s="14" t="n"/>
+      <c r="J250" s="15" t="n"/>
+      <c r="K250" s="14" t="n"/>
+      <c r="L250" s="16" t="n"/>
+      <c r="M250" s="13" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="n"/>
@@ -5464,10 +5791,11 @@
       <c r="F251" s="14" t="n"/>
       <c r="G251" s="14" t="n"/>
       <c r="H251" s="14" t="n"/>
-      <c r="I251" s="15" t="n"/>
-      <c r="J251" s="14" t="n"/>
-      <c r="K251" s="16" t="n"/>
-      <c r="L251" s="13" t="n"/>
+      <c r="I251" s="14" t="n"/>
+      <c r="J251" s="15" t="n"/>
+      <c r="K251" s="14" t="n"/>
+      <c r="L251" s="16" t="n"/>
+      <c r="M251" s="13" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="n"/>
@@ -5478,10 +5806,11 @@
       <c r="F252" s="14" t="n"/>
       <c r="G252" s="14" t="n"/>
       <c r="H252" s="14" t="n"/>
-      <c r="I252" s="15" t="n"/>
-      <c r="J252" s="14" t="n"/>
-      <c r="K252" s="16" t="n"/>
-      <c r="L252" s="13" t="n"/>
+      <c r="I252" s="14" t="n"/>
+      <c r="J252" s="15" t="n"/>
+      <c r="K252" s="14" t="n"/>
+      <c r="L252" s="16" t="n"/>
+      <c r="M252" s="13" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="n"/>
@@ -5492,10 +5821,11 @@
       <c r="F253" s="14" t="n"/>
       <c r="G253" s="14" t="n"/>
       <c r="H253" s="14" t="n"/>
-      <c r="I253" s="15" t="n"/>
-      <c r="J253" s="14" t="n"/>
-      <c r="K253" s="16" t="n"/>
-      <c r="L253" s="13" t="n"/>
+      <c r="I253" s="14" t="n"/>
+      <c r="J253" s="15" t="n"/>
+      <c r="K253" s="14" t="n"/>
+      <c r="L253" s="16" t="n"/>
+      <c r="M253" s="13" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="n"/>
@@ -5506,10 +5836,11 @@
       <c r="F254" s="14" t="n"/>
       <c r="G254" s="14" t="n"/>
       <c r="H254" s="14" t="n"/>
-      <c r="I254" s="15" t="n"/>
-      <c r="J254" s="14" t="n"/>
-      <c r="K254" s="16" t="n"/>
-      <c r="L254" s="13" t="n"/>
+      <c r="I254" s="14" t="n"/>
+      <c r="J254" s="15" t="n"/>
+      <c r="K254" s="14" t="n"/>
+      <c r="L254" s="16" t="n"/>
+      <c r="M254" s="13" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="n"/>
@@ -5520,10 +5851,11 @@
       <c r="F255" s="14" t="n"/>
       <c r="G255" s="14" t="n"/>
       <c r="H255" s="14" t="n"/>
-      <c r="I255" s="15" t="n"/>
-      <c r="J255" s="14" t="n"/>
-      <c r="K255" s="16" t="n"/>
-      <c r="L255" s="13" t="n"/>
+      <c r="I255" s="14" t="n"/>
+      <c r="J255" s="15" t="n"/>
+      <c r="K255" s="14" t="n"/>
+      <c r="L255" s="16" t="n"/>
+      <c r="M255" s="13" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="n"/>
@@ -5534,10 +5866,11 @@
       <c r="F256" s="14" t="n"/>
       <c r="G256" s="14" t="n"/>
       <c r="H256" s="14" t="n"/>
-      <c r="I256" s="15" t="n"/>
-      <c r="J256" s="14" t="n"/>
-      <c r="K256" s="16" t="n"/>
-      <c r="L256" s="13" t="n"/>
+      <c r="I256" s="14" t="n"/>
+      <c r="J256" s="15" t="n"/>
+      <c r="K256" s="14" t="n"/>
+      <c r="L256" s="16" t="n"/>
+      <c r="M256" s="13" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="n"/>
@@ -5548,10 +5881,11 @@
       <c r="F257" s="14" t="n"/>
       <c r="G257" s="14" t="n"/>
       <c r="H257" s="14" t="n"/>
-      <c r="I257" s="15" t="n"/>
-      <c r="J257" s="14" t="n"/>
-      <c r="K257" s="16" t="n"/>
-      <c r="L257" s="13" t="n"/>
+      <c r="I257" s="14" t="n"/>
+      <c r="J257" s="15" t="n"/>
+      <c r="K257" s="14" t="n"/>
+      <c r="L257" s="16" t="n"/>
+      <c r="M257" s="13" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="n"/>
@@ -5562,10 +5896,11 @@
       <c r="F258" s="14" t="n"/>
       <c r="G258" s="14" t="n"/>
       <c r="H258" s="14" t="n"/>
-      <c r="I258" s="15" t="n"/>
-      <c r="J258" s="14" t="n"/>
-      <c r="K258" s="16" t="n"/>
-      <c r="L258" s="13" t="n"/>
+      <c r="I258" s="14" t="n"/>
+      <c r="J258" s="15" t="n"/>
+      <c r="K258" s="14" t="n"/>
+      <c r="L258" s="16" t="n"/>
+      <c r="M258" s="13" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="n"/>
@@ -5576,10 +5911,11 @@
       <c r="F259" s="14" t="n"/>
       <c r="G259" s="14" t="n"/>
       <c r="H259" s="14" t="n"/>
-      <c r="I259" s="15" t="n"/>
-      <c r="J259" s="14" t="n"/>
-      <c r="K259" s="16" t="n"/>
-      <c r="L259" s="13" t="n"/>
+      <c r="I259" s="14" t="n"/>
+      <c r="J259" s="15" t="n"/>
+      <c r="K259" s="14" t="n"/>
+      <c r="L259" s="16" t="n"/>
+      <c r="M259" s="13" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="n"/>
@@ -5590,10 +5926,11 @@
       <c r="F260" s="14" t="n"/>
       <c r="G260" s="14" t="n"/>
       <c r="H260" s="14" t="n"/>
-      <c r="I260" s="15" t="n"/>
-      <c r="J260" s="14" t="n"/>
-      <c r="K260" s="16" t="n"/>
-      <c r="L260" s="13" t="n"/>
+      <c r="I260" s="14" t="n"/>
+      <c r="J260" s="15" t="n"/>
+      <c r="K260" s="14" t="n"/>
+      <c r="L260" s="16" t="n"/>
+      <c r="M260" s="13" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="n"/>
@@ -5604,10 +5941,11 @@
       <c r="F261" s="14" t="n"/>
       <c r="G261" s="14" t="n"/>
       <c r="H261" s="14" t="n"/>
-      <c r="I261" s="15" t="n"/>
-      <c r="J261" s="14" t="n"/>
-      <c r="K261" s="16" t="n"/>
-      <c r="L261" s="13" t="n"/>
+      <c r="I261" s="14" t="n"/>
+      <c r="J261" s="15" t="n"/>
+      <c r="K261" s="14" t="n"/>
+      <c r="L261" s="16" t="n"/>
+      <c r="M261" s="13" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="n"/>
@@ -5618,10 +5956,11 @@
       <c r="F262" s="14" t="n"/>
       <c r="G262" s="14" t="n"/>
       <c r="H262" s="14" t="n"/>
-      <c r="I262" s="15" t="n"/>
-      <c r="J262" s="14" t="n"/>
-      <c r="K262" s="16" t="n"/>
-      <c r="L262" s="13" t="n"/>
+      <c r="I262" s="14" t="n"/>
+      <c r="J262" s="15" t="n"/>
+      <c r="K262" s="14" t="n"/>
+      <c r="L262" s="16" t="n"/>
+      <c r="M262" s="13" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="n"/>
@@ -5632,10 +5971,11 @@
       <c r="F263" s="14" t="n"/>
       <c r="G263" s="14" t="n"/>
       <c r="H263" s="14" t="n"/>
-      <c r="I263" s="15" t="n"/>
-      <c r="J263" s="14" t="n"/>
-      <c r="K263" s="16" t="n"/>
-      <c r="L263" s="13" t="n"/>
+      <c r="I263" s="14" t="n"/>
+      <c r="J263" s="15" t="n"/>
+      <c r="K263" s="14" t="n"/>
+      <c r="L263" s="16" t="n"/>
+      <c r="M263" s="13" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="n"/>
@@ -5646,10 +5986,11 @@
       <c r="F264" s="14" t="n"/>
       <c r="G264" s="14" t="n"/>
       <c r="H264" s="14" t="n"/>
-      <c r="I264" s="15" t="n"/>
-      <c r="J264" s="14" t="n"/>
-      <c r="K264" s="16" t="n"/>
-      <c r="L264" s="13" t="n"/>
+      <c r="I264" s="14" t="n"/>
+      <c r="J264" s="15" t="n"/>
+      <c r="K264" s="14" t="n"/>
+      <c r="L264" s="16" t="n"/>
+      <c r="M264" s="13" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="n"/>
@@ -5660,10 +6001,11 @@
       <c r="F265" s="14" t="n"/>
       <c r="G265" s="14" t="n"/>
       <c r="H265" s="14" t="n"/>
-      <c r="I265" s="15" t="n"/>
-      <c r="J265" s="14" t="n"/>
-      <c r="K265" s="16" t="n"/>
-      <c r="L265" s="13" t="n"/>
+      <c r="I265" s="14" t="n"/>
+      <c r="J265" s="15" t="n"/>
+      <c r="K265" s="14" t="n"/>
+      <c r="L265" s="16" t="n"/>
+      <c r="M265" s="13" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="n"/>
@@ -5674,10 +6016,11 @@
       <c r="F266" s="14" t="n"/>
       <c r="G266" s="14" t="n"/>
       <c r="H266" s="14" t="n"/>
-      <c r="I266" s="15" t="n"/>
-      <c r="J266" s="14" t="n"/>
-      <c r="K266" s="16" t="n"/>
-      <c r="L266" s="13" t="n"/>
+      <c r="I266" s="14" t="n"/>
+      <c r="J266" s="15" t="n"/>
+      <c r="K266" s="14" t="n"/>
+      <c r="L266" s="16" t="n"/>
+      <c r="M266" s="13" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="n"/>
@@ -5688,10 +6031,11 @@
       <c r="F267" s="14" t="n"/>
       <c r="G267" s="14" t="n"/>
       <c r="H267" s="14" t="n"/>
-      <c r="I267" s="15" t="n"/>
-      <c r="J267" s="14" t="n"/>
-      <c r="K267" s="16" t="n"/>
-      <c r="L267" s="13" t="n"/>
+      <c r="I267" s="14" t="n"/>
+      <c r="J267" s="15" t="n"/>
+      <c r="K267" s="14" t="n"/>
+      <c r="L267" s="16" t="n"/>
+      <c r="M267" s="13" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="n"/>
@@ -5702,10 +6046,11 @@
       <c r="F268" s="14" t="n"/>
       <c r="G268" s="14" t="n"/>
       <c r="H268" s="14" t="n"/>
-      <c r="I268" s="15" t="n"/>
-      <c r="J268" s="14" t="n"/>
-      <c r="K268" s="16" t="n"/>
-      <c r="L268" s="13" t="n"/>
+      <c r="I268" s="14" t="n"/>
+      <c r="J268" s="15" t="n"/>
+      <c r="K268" s="14" t="n"/>
+      <c r="L268" s="16" t="n"/>
+      <c r="M268" s="13" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="n"/>
@@ -5716,10 +6061,11 @@
       <c r="F269" s="14" t="n"/>
       <c r="G269" s="14" t="n"/>
       <c r="H269" s="14" t="n"/>
-      <c r="I269" s="15" t="n"/>
-      <c r="J269" s="14" t="n"/>
-      <c r="K269" s="16" t="n"/>
-      <c r="L269" s="13" t="n"/>
+      <c r="I269" s="14" t="n"/>
+      <c r="J269" s="15" t="n"/>
+      <c r="K269" s="14" t="n"/>
+      <c r="L269" s="16" t="n"/>
+      <c r="M269" s="13" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="n"/>
@@ -5730,10 +6076,11 @@
       <c r="F270" s="14" t="n"/>
       <c r="G270" s="14" t="n"/>
       <c r="H270" s="14" t="n"/>
-      <c r="I270" s="15" t="n"/>
-      <c r="J270" s="14" t="n"/>
-      <c r="K270" s="16" t="n"/>
-      <c r="L270" s="13" t="n"/>
+      <c r="I270" s="14" t="n"/>
+      <c r="J270" s="15" t="n"/>
+      <c r="K270" s="14" t="n"/>
+      <c r="L270" s="16" t="n"/>
+      <c r="M270" s="13" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="n"/>
@@ -5744,10 +6091,11 @@
       <c r="F271" s="14" t="n"/>
       <c r="G271" s="14" t="n"/>
       <c r="H271" s="14" t="n"/>
-      <c r="I271" s="15" t="n"/>
-      <c r="J271" s="14" t="n"/>
-      <c r="K271" s="16" t="n"/>
-      <c r="L271" s="13" t="n"/>
+      <c r="I271" s="14" t="n"/>
+      <c r="J271" s="15" t="n"/>
+      <c r="K271" s="14" t="n"/>
+      <c r="L271" s="16" t="n"/>
+      <c r="M271" s="13" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="n"/>
@@ -5758,10 +6106,11 @@
       <c r="F272" s="14" t="n"/>
       <c r="G272" s="14" t="n"/>
       <c r="H272" s="14" t="n"/>
-      <c r="I272" s="15" t="n"/>
-      <c r="J272" s="14" t="n"/>
-      <c r="K272" s="16" t="n"/>
-      <c r="L272" s="13" t="n"/>
+      <c r="I272" s="14" t="n"/>
+      <c r="J272" s="15" t="n"/>
+      <c r="K272" s="14" t="n"/>
+      <c r="L272" s="16" t="n"/>
+      <c r="M272" s="13" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="n"/>
@@ -5772,10 +6121,11 @@
       <c r="F273" s="14" t="n"/>
       <c r="G273" s="14" t="n"/>
       <c r="H273" s="14" t="n"/>
-      <c r="I273" s="15" t="n"/>
-      <c r="J273" s="14" t="n"/>
-      <c r="K273" s="16" t="n"/>
-      <c r="L273" s="13" t="n"/>
+      <c r="I273" s="14" t="n"/>
+      <c r="J273" s="15" t="n"/>
+      <c r="K273" s="14" t="n"/>
+      <c r="L273" s="16" t="n"/>
+      <c r="M273" s="13" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="n"/>
@@ -5786,10 +6136,11 @@
       <c r="F274" s="14" t="n"/>
       <c r="G274" s="14" t="n"/>
       <c r="H274" s="14" t="n"/>
-      <c r="I274" s="15" t="n"/>
-      <c r="J274" s="14" t="n"/>
-      <c r="K274" s="16" t="n"/>
-      <c r="L274" s="13" t="n"/>
+      <c r="I274" s="14" t="n"/>
+      <c r="J274" s="15" t="n"/>
+      <c r="K274" s="14" t="n"/>
+      <c r="L274" s="16" t="n"/>
+      <c r="M274" s="13" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="n"/>
@@ -5800,10 +6151,11 @@
       <c r="F275" s="14" t="n"/>
       <c r="G275" s="14" t="n"/>
       <c r="H275" s="14" t="n"/>
-      <c r="I275" s="15" t="n"/>
-      <c r="J275" s="14" t="n"/>
-      <c r="K275" s="16" t="n"/>
-      <c r="L275" s="13" t="n"/>
+      <c r="I275" s="14" t="n"/>
+      <c r="J275" s="15" t="n"/>
+      <c r="K275" s="14" t="n"/>
+      <c r="L275" s="16" t="n"/>
+      <c r="M275" s="13" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="n"/>
@@ -5814,10 +6166,11 @@
       <c r="F276" s="14" t="n"/>
       <c r="G276" s="14" t="n"/>
       <c r="H276" s="14" t="n"/>
-      <c r="I276" s="15" t="n"/>
-      <c r="J276" s="14" t="n"/>
-      <c r="K276" s="16" t="n"/>
-      <c r="L276" s="13" t="n"/>
+      <c r="I276" s="14" t="n"/>
+      <c r="J276" s="15" t="n"/>
+      <c r="K276" s="14" t="n"/>
+      <c r="L276" s="16" t="n"/>
+      <c r="M276" s="13" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="n"/>
@@ -5828,10 +6181,11 @@
       <c r="F277" s="14" t="n"/>
       <c r="G277" s="14" t="n"/>
       <c r="H277" s="14" t="n"/>
-      <c r="I277" s="15" t="n"/>
-      <c r="J277" s="14" t="n"/>
-      <c r="K277" s="16" t="n"/>
-      <c r="L277" s="13" t="n"/>
+      <c r="I277" s="14" t="n"/>
+      <c r="J277" s="15" t="n"/>
+      <c r="K277" s="14" t="n"/>
+      <c r="L277" s="16" t="n"/>
+      <c r="M277" s="13" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="n"/>
@@ -5842,10 +6196,11 @@
       <c r="F278" s="14" t="n"/>
       <c r="G278" s="14" t="n"/>
       <c r="H278" s="14" t="n"/>
-      <c r="I278" s="15" t="n"/>
-      <c r="J278" s="14" t="n"/>
-      <c r="K278" s="16" t="n"/>
-      <c r="L278" s="13" t="n"/>
+      <c r="I278" s="14" t="n"/>
+      <c r="J278" s="15" t="n"/>
+      <c r="K278" s="14" t="n"/>
+      <c r="L278" s="16" t="n"/>
+      <c r="M278" s="13" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="n"/>
@@ -5856,10 +6211,11 @@
       <c r="F279" s="14" t="n"/>
       <c r="G279" s="14" t="n"/>
       <c r="H279" s="14" t="n"/>
-      <c r="I279" s="15" t="n"/>
-      <c r="J279" s="14" t="n"/>
-      <c r="K279" s="16" t="n"/>
-      <c r="L279" s="13" t="n"/>
+      <c r="I279" s="14" t="n"/>
+      <c r="J279" s="15" t="n"/>
+      <c r="K279" s="14" t="n"/>
+      <c r="L279" s="16" t="n"/>
+      <c r="M279" s="13" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="n"/>
@@ -5870,10 +6226,11 @@
       <c r="F280" s="14" t="n"/>
       <c r="G280" s="14" t="n"/>
       <c r="H280" s="14" t="n"/>
-      <c r="I280" s="15" t="n"/>
-      <c r="J280" s="14" t="n"/>
-      <c r="K280" s="16" t="n"/>
-      <c r="L280" s="13" t="n"/>
+      <c r="I280" s="14" t="n"/>
+      <c r="J280" s="15" t="n"/>
+      <c r="K280" s="14" t="n"/>
+      <c r="L280" s="16" t="n"/>
+      <c r="M280" s="13" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="n"/>
@@ -5884,10 +6241,11 @@
       <c r="F281" s="14" t="n"/>
       <c r="G281" s="14" t="n"/>
       <c r="H281" s="14" t="n"/>
-      <c r="I281" s="15" t="n"/>
-      <c r="J281" s="14" t="n"/>
-      <c r="K281" s="16" t="n"/>
-      <c r="L281" s="13" t="n"/>
+      <c r="I281" s="14" t="n"/>
+      <c r="J281" s="15" t="n"/>
+      <c r="K281" s="14" t="n"/>
+      <c r="L281" s="16" t="n"/>
+      <c r="M281" s="13" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="n"/>
@@ -5898,10 +6256,11 @@
       <c r="F282" s="14" t="n"/>
       <c r="G282" s="14" t="n"/>
       <c r="H282" s="14" t="n"/>
-      <c r="I282" s="15" t="n"/>
-      <c r="J282" s="14" t="n"/>
-      <c r="K282" s="16" t="n"/>
-      <c r="L282" s="13" t="n"/>
+      <c r="I282" s="14" t="n"/>
+      <c r="J282" s="15" t="n"/>
+      <c r="K282" s="14" t="n"/>
+      <c r="L282" s="16" t="n"/>
+      <c r="M282" s="13" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="n"/>
@@ -5912,10 +6271,11 @@
       <c r="F283" s="14" t="n"/>
       <c r="G283" s="14" t="n"/>
       <c r="H283" s="14" t="n"/>
-      <c r="I283" s="15" t="n"/>
-      <c r="J283" s="14" t="n"/>
-      <c r="K283" s="16" t="n"/>
-      <c r="L283" s="13" t="n"/>
+      <c r="I283" s="14" t="n"/>
+      <c r="J283" s="15" t="n"/>
+      <c r="K283" s="14" t="n"/>
+      <c r="L283" s="16" t="n"/>
+      <c r="M283" s="13" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="n"/>
@@ -5926,10 +6286,11 @@
       <c r="F284" s="14" t="n"/>
       <c r="G284" s="14" t="n"/>
       <c r="H284" s="14" t="n"/>
-      <c r="I284" s="15" t="n"/>
-      <c r="J284" s="14" t="n"/>
-      <c r="K284" s="16" t="n"/>
-      <c r="L284" s="13" t="n"/>
+      <c r="I284" s="14" t="n"/>
+      <c r="J284" s="15" t="n"/>
+      <c r="K284" s="14" t="n"/>
+      <c r="L284" s="16" t="n"/>
+      <c r="M284" s="13" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="n"/>
@@ -5940,10 +6301,11 @@
       <c r="F285" s="14" t="n"/>
       <c r="G285" s="14" t="n"/>
       <c r="H285" s="14" t="n"/>
-      <c r="I285" s="15" t="n"/>
-      <c r="J285" s="14" t="n"/>
-      <c r="K285" s="16" t="n"/>
-      <c r="L285" s="13" t="n"/>
+      <c r="I285" s="14" t="n"/>
+      <c r="J285" s="15" t="n"/>
+      <c r="K285" s="14" t="n"/>
+      <c r="L285" s="16" t="n"/>
+      <c r="M285" s="13" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="n"/>
@@ -5954,10 +6316,11 @@
       <c r="F286" s="14" t="n"/>
       <c r="G286" s="14" t="n"/>
       <c r="H286" s="14" t="n"/>
-      <c r="I286" s="15" t="n"/>
-      <c r="J286" s="14" t="n"/>
-      <c r="K286" s="16" t="n"/>
-      <c r="L286" s="13" t="n"/>
+      <c r="I286" s="14" t="n"/>
+      <c r="J286" s="15" t="n"/>
+      <c r="K286" s="14" t="n"/>
+      <c r="L286" s="16" t="n"/>
+      <c r="M286" s="13" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="n"/>
@@ -5968,10 +6331,11 @@
       <c r="F287" s="14" t="n"/>
       <c r="G287" s="14" t="n"/>
       <c r="H287" s="14" t="n"/>
-      <c r="I287" s="15" t="n"/>
-      <c r="J287" s="14" t="n"/>
-      <c r="K287" s="16" t="n"/>
-      <c r="L287" s="13" t="n"/>
+      <c r="I287" s="14" t="n"/>
+      <c r="J287" s="15" t="n"/>
+      <c r="K287" s="14" t="n"/>
+      <c r="L287" s="16" t="n"/>
+      <c r="M287" s="13" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="n"/>
@@ -5982,10 +6346,11 @@
       <c r="F288" s="14" t="n"/>
       <c r="G288" s="14" t="n"/>
       <c r="H288" s="14" t="n"/>
-      <c r="I288" s="15" t="n"/>
-      <c r="J288" s="14" t="n"/>
-      <c r="K288" s="16" t="n"/>
-      <c r="L288" s="13" t="n"/>
+      <c r="I288" s="14" t="n"/>
+      <c r="J288" s="15" t="n"/>
+      <c r="K288" s="14" t="n"/>
+      <c r="L288" s="16" t="n"/>
+      <c r="M288" s="13" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="n"/>
@@ -5996,10 +6361,11 @@
       <c r="F289" s="14" t="n"/>
       <c r="G289" s="14" t="n"/>
       <c r="H289" s="14" t="n"/>
-      <c r="I289" s="15" t="n"/>
-      <c r="J289" s="14" t="n"/>
-      <c r="K289" s="16" t="n"/>
-      <c r="L289" s="13" t="n"/>
+      <c r="I289" s="14" t="n"/>
+      <c r="J289" s="15" t="n"/>
+      <c r="K289" s="14" t="n"/>
+      <c r="L289" s="16" t="n"/>
+      <c r="M289" s="13" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="n"/>
@@ -6010,10 +6376,11 @@
       <c r="F290" s="14" t="n"/>
       <c r="G290" s="14" t="n"/>
       <c r="H290" s="14" t="n"/>
-      <c r="I290" s="15" t="n"/>
-      <c r="J290" s="14" t="n"/>
-      <c r="K290" s="16" t="n"/>
-      <c r="L290" s="13" t="n"/>
+      <c r="I290" s="14" t="n"/>
+      <c r="J290" s="15" t="n"/>
+      <c r="K290" s="14" t="n"/>
+      <c r="L290" s="16" t="n"/>
+      <c r="M290" s="13" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="n"/>
@@ -6024,10 +6391,11 @@
       <c r="F291" s="14" t="n"/>
       <c r="G291" s="14" t="n"/>
       <c r="H291" s="14" t="n"/>
-      <c r="I291" s="15" t="n"/>
-      <c r="J291" s="14" t="n"/>
-      <c r="K291" s="16" t="n"/>
-      <c r="L291" s="13" t="n"/>
+      <c r="I291" s="14" t="n"/>
+      <c r="J291" s="15" t="n"/>
+      <c r="K291" s="14" t="n"/>
+      <c r="L291" s="16" t="n"/>
+      <c r="M291" s="13" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="n"/>
@@ -6038,10 +6406,11 @@
       <c r="F292" s="14" t="n"/>
       <c r="G292" s="14" t="n"/>
       <c r="H292" s="14" t="n"/>
-      <c r="I292" s="15" t="n"/>
-      <c r="J292" s="14" t="n"/>
-      <c r="K292" s="16" t="n"/>
-      <c r="L292" s="13" t="n"/>
+      <c r="I292" s="14" t="n"/>
+      <c r="J292" s="15" t="n"/>
+      <c r="K292" s="14" t="n"/>
+      <c r="L292" s="16" t="n"/>
+      <c r="M292" s="13" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="n"/>
@@ -6052,10 +6421,11 @@
       <c r="F293" s="14" t="n"/>
       <c r="G293" s="14" t="n"/>
       <c r="H293" s="14" t="n"/>
-      <c r="I293" s="15" t="n"/>
-      <c r="J293" s="14" t="n"/>
-      <c r="K293" s="16" t="n"/>
-      <c r="L293" s="13" t="n"/>
+      <c r="I293" s="14" t="n"/>
+      <c r="J293" s="15" t="n"/>
+      <c r="K293" s="14" t="n"/>
+      <c r="L293" s="16" t="n"/>
+      <c r="M293" s="13" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="n"/>
@@ -6066,10 +6436,11 @@
       <c r="F294" s="14" t="n"/>
       <c r="G294" s="14" t="n"/>
       <c r="H294" s="14" t="n"/>
-      <c r="I294" s="15" t="n"/>
-      <c r="J294" s="14" t="n"/>
-      <c r="K294" s="16" t="n"/>
-      <c r="L294" s="13" t="n"/>
+      <c r="I294" s="14" t="n"/>
+      <c r="J294" s="15" t="n"/>
+      <c r="K294" s="14" t="n"/>
+      <c r="L294" s="16" t="n"/>
+      <c r="M294" s="13" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="n"/>
@@ -6080,10 +6451,11 @@
       <c r="F295" s="14" t="n"/>
       <c r="G295" s="14" t="n"/>
       <c r="H295" s="14" t="n"/>
-      <c r="I295" s="15" t="n"/>
-      <c r="J295" s="14" t="n"/>
-      <c r="K295" s="16" t="n"/>
-      <c r="L295" s="13" t="n"/>
+      <c r="I295" s="14" t="n"/>
+      <c r="J295" s="15" t="n"/>
+      <c r="K295" s="14" t="n"/>
+      <c r="L295" s="16" t="n"/>
+      <c r="M295" s="13" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="n"/>
@@ -6094,10 +6466,11 @@
       <c r="F296" s="14" t="n"/>
       <c r="G296" s="14" t="n"/>
       <c r="H296" s="14" t="n"/>
-      <c r="I296" s="15" t="n"/>
-      <c r="J296" s="14" t="n"/>
-      <c r="K296" s="16" t="n"/>
-      <c r="L296" s="13" t="n"/>
+      <c r="I296" s="14" t="n"/>
+      <c r="J296" s="15" t="n"/>
+      <c r="K296" s="14" t="n"/>
+      <c r="L296" s="16" t="n"/>
+      <c r="M296" s="13" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="n"/>
@@ -6108,10 +6481,11 @@
       <c r="F297" s="14" t="n"/>
       <c r="G297" s="14" t="n"/>
       <c r="H297" s="14" t="n"/>
-      <c r="I297" s="15" t="n"/>
-      <c r="J297" s="14" t="n"/>
-      <c r="K297" s="16" t="n"/>
-      <c r="L297" s="13" t="n"/>
+      <c r="I297" s="14" t="n"/>
+      <c r="J297" s="15" t="n"/>
+      <c r="K297" s="14" t="n"/>
+      <c r="L297" s="16" t="n"/>
+      <c r="M297" s="13" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="n"/>
@@ -6122,10 +6496,11 @@
       <c r="F298" s="14" t="n"/>
       <c r="G298" s="14" t="n"/>
       <c r="H298" s="14" t="n"/>
-      <c r="I298" s="15" t="n"/>
-      <c r="J298" s="14" t="n"/>
-      <c r="K298" s="16" t="n"/>
-      <c r="L298" s="13" t="n"/>
+      <c r="I298" s="14" t="n"/>
+      <c r="J298" s="15" t="n"/>
+      <c r="K298" s="14" t="n"/>
+      <c r="L298" s="16" t="n"/>
+      <c r="M298" s="13" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="n"/>
@@ -6136,10 +6511,11 @@
       <c r="F299" s="14" t="n"/>
       <c r="G299" s="14" t="n"/>
       <c r="H299" s="14" t="n"/>
-      <c r="I299" s="15" t="n"/>
-      <c r="J299" s="14" t="n"/>
-      <c r="K299" s="16" t="n"/>
-      <c r="L299" s="13" t="n"/>
+      <c r="I299" s="14" t="n"/>
+      <c r="J299" s="15" t="n"/>
+      <c r="K299" s="14" t="n"/>
+      <c r="L299" s="16" t="n"/>
+      <c r="M299" s="13" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="n"/>
@@ -6150,10 +6526,11 @@
       <c r="F300" s="14" t="n"/>
       <c r="G300" s="14" t="n"/>
       <c r="H300" s="14" t="n"/>
-      <c r="I300" s="15" t="n"/>
-      <c r="J300" s="14" t="n"/>
-      <c r="K300" s="16" t="n"/>
-      <c r="L300" s="13" t="n"/>
+      <c r="I300" s="14" t="n"/>
+      <c r="J300" s="15" t="n"/>
+      <c r="K300" s="14" t="n"/>
+      <c r="L300" s="16" t="n"/>
+      <c r="M300" s="13" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="n"/>
@@ -6164,10 +6541,11 @@
       <c r="F301" s="14" t="n"/>
       <c r="G301" s="14" t="n"/>
       <c r="H301" s="14" t="n"/>
-      <c r="I301" s="15" t="n"/>
-      <c r="J301" s="14" t="n"/>
-      <c r="K301" s="16" t="n"/>
-      <c r="L301" s="13" t="n"/>
+      <c r="I301" s="14" t="n"/>
+      <c r="J301" s="15" t="n"/>
+      <c r="K301" s="14" t="n"/>
+      <c r="L301" s="16" t="n"/>
+      <c r="M301" s="13" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="n"/>
@@ -6178,10 +6556,11 @@
       <c r="F302" s="14" t="n"/>
       <c r="G302" s="14" t="n"/>
       <c r="H302" s="14" t="n"/>
-      <c r="I302" s="15" t="n"/>
-      <c r="J302" s="14" t="n"/>
-      <c r="K302" s="16" t="n"/>
-      <c r="L302" s="13" t="n"/>
+      <c r="I302" s="14" t="n"/>
+      <c r="J302" s="15" t="n"/>
+      <c r="K302" s="14" t="n"/>
+      <c r="L302" s="16" t="n"/>
+      <c r="M302" s="13" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="n"/>
@@ -6192,10 +6571,11 @@
       <c r="F303" s="14" t="n"/>
       <c r="G303" s="14" t="n"/>
       <c r="H303" s="14" t="n"/>
-      <c r="I303" s="15" t="n"/>
-      <c r="J303" s="14" t="n"/>
-      <c r="K303" s="16" t="n"/>
-      <c r="L303" s="13" t="n"/>
+      <c r="I303" s="14" t="n"/>
+      <c r="J303" s="15" t="n"/>
+      <c r="K303" s="14" t="n"/>
+      <c r="L303" s="16" t="n"/>
+      <c r="M303" s="13" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="n"/>
@@ -6206,10 +6586,11 @@
       <c r="F304" s="14" t="n"/>
       <c r="G304" s="14" t="n"/>
       <c r="H304" s="14" t="n"/>
-      <c r="I304" s="15" t="n"/>
-      <c r="J304" s="14" t="n"/>
-      <c r="K304" s="16" t="n"/>
-      <c r="L304" s="13" t="n"/>
+      <c r="I304" s="14" t="n"/>
+      <c r="J304" s="15" t="n"/>
+      <c r="K304" s="14" t="n"/>
+      <c r="L304" s="16" t="n"/>
+      <c r="M304" s="13" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="n"/>
@@ -6220,10 +6601,11 @@
       <c r="F305" s="14" t="n"/>
       <c r="G305" s="14" t="n"/>
       <c r="H305" s="14" t="n"/>
-      <c r="I305" s="15" t="n"/>
-      <c r="J305" s="14" t="n"/>
-      <c r="K305" s="16" t="n"/>
-      <c r="L305" s="13" t="n"/>
+      <c r="I305" s="14" t="n"/>
+      <c r="J305" s="15" t="n"/>
+      <c r="K305" s="14" t="n"/>
+      <c r="L305" s="16" t="n"/>
+      <c r="M305" s="13" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="n"/>
@@ -6234,10 +6616,11 @@
       <c r="F306" s="14" t="n"/>
       <c r="G306" s="14" t="n"/>
       <c r="H306" s="14" t="n"/>
-      <c r="I306" s="15" t="n"/>
-      <c r="J306" s="14" t="n"/>
-      <c r="K306" s="16" t="n"/>
-      <c r="L306" s="13" t="n"/>
+      <c r="I306" s="14" t="n"/>
+      <c r="J306" s="15" t="n"/>
+      <c r="K306" s="14" t="n"/>
+      <c r="L306" s="16" t="n"/>
+      <c r="M306" s="13" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="n"/>
@@ -6248,10 +6631,11 @@
       <c r="F307" s="14" t="n"/>
       <c r="G307" s="14" t="n"/>
       <c r="H307" s="14" t="n"/>
-      <c r="I307" s="15" t="n"/>
-      <c r="J307" s="14" t="n"/>
-      <c r="K307" s="16" t="n"/>
-      <c r="L307" s="13" t="n"/>
+      <c r="I307" s="14" t="n"/>
+      <c r="J307" s="15" t="n"/>
+      <c r="K307" s="14" t="n"/>
+      <c r="L307" s="16" t="n"/>
+      <c r="M307" s="13" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="n"/>
@@ -6262,10 +6646,11 @@
       <c r="F308" s="14" t="n"/>
       <c r="G308" s="14" t="n"/>
       <c r="H308" s="14" t="n"/>
-      <c r="I308" s="15" t="n"/>
-      <c r="J308" s="14" t="n"/>
-      <c r="K308" s="16" t="n"/>
-      <c r="L308" s="13" t="n"/>
+      <c r="I308" s="14" t="n"/>
+      <c r="J308" s="15" t="n"/>
+      <c r="K308" s="14" t="n"/>
+      <c r="L308" s="16" t="n"/>
+      <c r="M308" s="13" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="n"/>
@@ -6276,10 +6661,11 @@
       <c r="F309" s="14" t="n"/>
       <c r="G309" s="14" t="n"/>
       <c r="H309" s="14" t="n"/>
-      <c r="I309" s="15" t="n"/>
-      <c r="J309" s="14" t="n"/>
-      <c r="K309" s="16" t="n"/>
-      <c r="L309" s="13" t="n"/>
+      <c r="I309" s="14" t="n"/>
+      <c r="J309" s="15" t="n"/>
+      <c r="K309" s="14" t="n"/>
+      <c r="L309" s="16" t="n"/>
+      <c r="M309" s="13" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="n"/>
@@ -6290,10 +6676,11 @@
       <c r="F310" s="14" t="n"/>
       <c r="G310" s="14" t="n"/>
       <c r="H310" s="14" t="n"/>
-      <c r="I310" s="15" t="n"/>
-      <c r="J310" s="14" t="n"/>
-      <c r="K310" s="16" t="n"/>
-      <c r="L310" s="13" t="n"/>
+      <c r="I310" s="14" t="n"/>
+      <c r="J310" s="15" t="n"/>
+      <c r="K310" s="14" t="n"/>
+      <c r="L310" s="16" t="n"/>
+      <c r="M310" s="13" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="n"/>
@@ -6304,10 +6691,11 @@
       <c r="F311" s="14" t="n"/>
       <c r="G311" s="14" t="n"/>
       <c r="H311" s="14" t="n"/>
-      <c r="I311" s="15" t="n"/>
-      <c r="J311" s="14" t="n"/>
-      <c r="K311" s="16" t="n"/>
-      <c r="L311" s="13" t="n"/>
+      <c r="I311" s="14" t="n"/>
+      <c r="J311" s="15" t="n"/>
+      <c r="K311" s="14" t="n"/>
+      <c r="L311" s="16" t="n"/>
+      <c r="M311" s="13" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="n"/>
@@ -6318,10 +6706,11 @@
       <c r="F312" s="14" t="n"/>
       <c r="G312" s="14" t="n"/>
       <c r="H312" s="14" t="n"/>
-      <c r="I312" s="15" t="n"/>
-      <c r="J312" s="14" t="n"/>
-      <c r="K312" s="16" t="n"/>
-      <c r="L312" s="13" t="n"/>
+      <c r="I312" s="14" t="n"/>
+      <c r="J312" s="15" t="n"/>
+      <c r="K312" s="14" t="n"/>
+      <c r="L312" s="16" t="n"/>
+      <c r="M312" s="13" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="n"/>
@@ -6332,10 +6721,11 @@
       <c r="F313" s="14" t="n"/>
       <c r="G313" s="14" t="n"/>
       <c r="H313" s="14" t="n"/>
-      <c r="I313" s="15" t="n"/>
-      <c r="J313" s="14" t="n"/>
-      <c r="K313" s="16" t="n"/>
-      <c r="L313" s="13" t="n"/>
+      <c r="I313" s="14" t="n"/>
+      <c r="J313" s="15" t="n"/>
+      <c r="K313" s="14" t="n"/>
+      <c r="L313" s="16" t="n"/>
+      <c r="M313" s="13" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="11" t="n"/>
@@ -6346,10 +6736,11 @@
       <c r="F314" s="14" t="n"/>
       <c r="G314" s="14" t="n"/>
       <c r="H314" s="14" t="n"/>
-      <c r="I314" s="15" t="n"/>
-      <c r="J314" s="14" t="n"/>
-      <c r="K314" s="16" t="n"/>
-      <c r="L314" s="13" t="n"/>
+      <c r="I314" s="14" t="n"/>
+      <c r="J314" s="15" t="n"/>
+      <c r="K314" s="14" t="n"/>
+      <c r="L314" s="16" t="n"/>
+      <c r="M314" s="13" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="11" t="n"/>
@@ -6360,10 +6751,11 @@
       <c r="F315" s="14" t="n"/>
       <c r="G315" s="14" t="n"/>
       <c r="H315" s="14" t="n"/>
-      <c r="I315" s="15" t="n"/>
-      <c r="J315" s="14" t="n"/>
-      <c r="K315" s="16" t="n"/>
-      <c r="L315" s="13" t="n"/>
+      <c r="I315" s="14" t="n"/>
+      <c r="J315" s="15" t="n"/>
+      <c r="K315" s="14" t="n"/>
+      <c r="L315" s="16" t="n"/>
+      <c r="M315" s="13" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="11" t="n"/>
@@ -6374,10 +6766,11 @@
       <c r="F316" s="14" t="n"/>
       <c r="G316" s="14" t="n"/>
       <c r="H316" s="14" t="n"/>
-      <c r="I316" s="15" t="n"/>
-      <c r="J316" s="14" t="n"/>
-      <c r="K316" s="16" t="n"/>
-      <c r="L316" s="13" t="n"/>
+      <c r="I316" s="14" t="n"/>
+      <c r="J316" s="15" t="n"/>
+      <c r="K316" s="14" t="n"/>
+      <c r="L316" s="16" t="n"/>
+      <c r="M316" s="13" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="11" t="n"/>
@@ -6388,10 +6781,11 @@
       <c r="F317" s="14" t="n"/>
       <c r="G317" s="14" t="n"/>
       <c r="H317" s="14" t="n"/>
-      <c r="I317" s="15" t="n"/>
-      <c r="J317" s="14" t="n"/>
-      <c r="K317" s="16" t="n"/>
-      <c r="L317" s="13" t="n"/>
+      <c r="I317" s="14" t="n"/>
+      <c r="J317" s="15" t="n"/>
+      <c r="K317" s="14" t="n"/>
+      <c r="L317" s="16" t="n"/>
+      <c r="M317" s="13" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="11" t="n"/>
@@ -6402,10 +6796,11 @@
       <c r="F318" s="14" t="n"/>
       <c r="G318" s="14" t="n"/>
       <c r="H318" s="14" t="n"/>
-      <c r="I318" s="15" t="n"/>
-      <c r="J318" s="14" t="n"/>
-      <c r="K318" s="16" t="n"/>
-      <c r="L318" s="13" t="n"/>
+      <c r="I318" s="14" t="n"/>
+      <c r="J318" s="15" t="n"/>
+      <c r="K318" s="14" t="n"/>
+      <c r="L318" s="16" t="n"/>
+      <c r="M318" s="13" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="11" t="n"/>
@@ -6416,10 +6811,11 @@
       <c r="F319" s="14" t="n"/>
       <c r="G319" s="14" t="n"/>
       <c r="H319" s="14" t="n"/>
-      <c r="I319" s="15" t="n"/>
-      <c r="J319" s="14" t="n"/>
-      <c r="K319" s="16" t="n"/>
-      <c r="L319" s="13" t="n"/>
+      <c r="I319" s="14" t="n"/>
+      <c r="J319" s="15" t="n"/>
+      <c r="K319" s="14" t="n"/>
+      <c r="L319" s="16" t="n"/>
+      <c r="M319" s="13" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="11" t="n"/>
@@ -6430,10 +6826,11 @@
       <c r="F320" s="14" t="n"/>
       <c r="G320" s="14" t="n"/>
       <c r="H320" s="14" t="n"/>
-      <c r="I320" s="15" t="n"/>
-      <c r="J320" s="14" t="n"/>
-      <c r="K320" s="16" t="n"/>
-      <c r="L320" s="13" t="n"/>
+      <c r="I320" s="14" t="n"/>
+      <c r="J320" s="15" t="n"/>
+      <c r="K320" s="14" t="n"/>
+      <c r="L320" s="16" t="n"/>
+      <c r="M320" s="13" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="n"/>
@@ -6444,10 +6841,11 @@
       <c r="F321" s="14" t="n"/>
       <c r="G321" s="14" t="n"/>
       <c r="H321" s="14" t="n"/>
-      <c r="I321" s="15" t="n"/>
-      <c r="J321" s="14" t="n"/>
-      <c r="K321" s="16" t="n"/>
-      <c r="L321" s="13" t="n"/>
+      <c r="I321" s="14" t="n"/>
+      <c r="J321" s="15" t="n"/>
+      <c r="K321" s="14" t="n"/>
+      <c r="L321" s="16" t="n"/>
+      <c r="M321" s="13" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="11" t="n"/>
@@ -6458,10 +6856,11 @@
       <c r="F322" s="14" t="n"/>
       <c r="G322" s="14" t="n"/>
       <c r="H322" s="14" t="n"/>
-      <c r="I322" s="15" t="n"/>
-      <c r="J322" s="14" t="n"/>
-      <c r="K322" s="16" t="n"/>
-      <c r="L322" s="13" t="n"/>
+      <c r="I322" s="14" t="n"/>
+      <c r="J322" s="15" t="n"/>
+      <c r="K322" s="14" t="n"/>
+      <c r="L322" s="16" t="n"/>
+      <c r="M322" s="13" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="11" t="n"/>
@@ -6472,10 +6871,11 @@
       <c r="F323" s="14" t="n"/>
       <c r="G323" s="14" t="n"/>
       <c r="H323" s="14" t="n"/>
-      <c r="I323" s="15" t="n"/>
-      <c r="J323" s="14" t="n"/>
-      <c r="K323" s="16" t="n"/>
-      <c r="L323" s="13" t="n"/>
+      <c r="I323" s="14" t="n"/>
+      <c r="J323" s="15" t="n"/>
+      <c r="K323" s="14" t="n"/>
+      <c r="L323" s="16" t="n"/>
+      <c r="M323" s="13" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="11" t="n"/>
@@ -6486,10 +6886,11 @@
       <c r="F324" s="14" t="n"/>
       <c r="G324" s="14" t="n"/>
       <c r="H324" s="14" t="n"/>
-      <c r="I324" s="15" t="n"/>
-      <c r="J324" s="14" t="n"/>
-      <c r="K324" s="16" t="n"/>
-      <c r="L324" s="13" t="n"/>
+      <c r="I324" s="14" t="n"/>
+      <c r="J324" s="15" t="n"/>
+      <c r="K324" s="14" t="n"/>
+      <c r="L324" s="16" t="n"/>
+      <c r="M324" s="13" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="11" t="n"/>
@@ -6500,10 +6901,11 @@
       <c r="F325" s="14" t="n"/>
       <c r="G325" s="14" t="n"/>
       <c r="H325" s="14" t="n"/>
-      <c r="I325" s="15" t="n"/>
-      <c r="J325" s="14" t="n"/>
-      <c r="K325" s="16" t="n"/>
-      <c r="L325" s="13" t="n"/>
+      <c r="I325" s="14" t="n"/>
+      <c r="J325" s="15" t="n"/>
+      <c r="K325" s="14" t="n"/>
+      <c r="L325" s="16" t="n"/>
+      <c r="M325" s="13" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="11" t="n"/>
@@ -6514,10 +6916,11 @@
       <c r="F326" s="14" t="n"/>
       <c r="G326" s="14" t="n"/>
       <c r="H326" s="14" t="n"/>
-      <c r="I326" s="15" t="n"/>
-      <c r="J326" s="14" t="n"/>
-      <c r="K326" s="16" t="n"/>
-      <c r="L326" s="13" t="n"/>
+      <c r="I326" s="14" t="n"/>
+      <c r="J326" s="15" t="n"/>
+      <c r="K326" s="14" t="n"/>
+      <c r="L326" s="16" t="n"/>
+      <c r="M326" s="13" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="11" t="n"/>
@@ -6528,10 +6931,11 @@
       <c r="F327" s="14" t="n"/>
       <c r="G327" s="14" t="n"/>
       <c r="H327" s="14" t="n"/>
-      <c r="I327" s="15" t="n"/>
-      <c r="J327" s="14" t="n"/>
-      <c r="K327" s="16" t="n"/>
-      <c r="L327" s="13" t="n"/>
+      <c r="I327" s="14" t="n"/>
+      <c r="J327" s="15" t="n"/>
+      <c r="K327" s="14" t="n"/>
+      <c r="L327" s="16" t="n"/>
+      <c r="M327" s="13" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="11" t="n"/>
@@ -6542,10 +6946,11 @@
       <c r="F328" s="14" t="n"/>
       <c r="G328" s="14" t="n"/>
       <c r="H328" s="14" t="n"/>
-      <c r="I328" s="15" t="n"/>
-      <c r="J328" s="14" t="n"/>
-      <c r="K328" s="16" t="n"/>
-      <c r="L328" s="13" t="n"/>
+      <c r="I328" s="14" t="n"/>
+      <c r="J328" s="15" t="n"/>
+      <c r="K328" s="14" t="n"/>
+      <c r="L328" s="16" t="n"/>
+      <c r="M328" s="13" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="n"/>
@@ -6556,10 +6961,11 @@
       <c r="F329" s="14" t="n"/>
       <c r="G329" s="14" t="n"/>
       <c r="H329" s="14" t="n"/>
-      <c r="I329" s="15" t="n"/>
-      <c r="J329" s="14" t="n"/>
-      <c r="K329" s="16" t="n"/>
-      <c r="L329" s="13" t="n"/>
+      <c r="I329" s="14" t="n"/>
+      <c r="J329" s="15" t="n"/>
+      <c r="K329" s="14" t="n"/>
+      <c r="L329" s="16" t="n"/>
+      <c r="M329" s="13" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="11" t="n"/>
@@ -6570,10 +6976,11 @@
       <c r="F330" s="14" t="n"/>
       <c r="G330" s="14" t="n"/>
       <c r="H330" s="14" t="n"/>
-      <c r="I330" s="15" t="n"/>
-      <c r="J330" s="14" t="n"/>
-      <c r="K330" s="16" t="n"/>
-      <c r="L330" s="13" t="n"/>
+      <c r="I330" s="14" t="n"/>
+      <c r="J330" s="15" t="n"/>
+      <c r="K330" s="14" t="n"/>
+      <c r="L330" s="16" t="n"/>
+      <c r="M330" s="13" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="11" t="n"/>
@@ -6584,10 +6991,11 @@
       <c r="F331" s="14" t="n"/>
       <c r="G331" s="14" t="n"/>
       <c r="H331" s="14" t="n"/>
-      <c r="I331" s="15" t="n"/>
-      <c r="J331" s="14" t="n"/>
-      <c r="K331" s="16" t="n"/>
-      <c r="L331" s="13" t="n"/>
+      <c r="I331" s="14" t="n"/>
+      <c r="J331" s="15" t="n"/>
+      <c r="K331" s="14" t="n"/>
+      <c r="L331" s="16" t="n"/>
+      <c r="M331" s="13" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="11" t="n"/>
@@ -6598,10 +7006,11 @@
       <c r="F332" s="14" t="n"/>
       <c r="G332" s="14" t="n"/>
       <c r="H332" s="14" t="n"/>
-      <c r="I332" s="15" t="n"/>
-      <c r="J332" s="14" t="n"/>
-      <c r="K332" s="16" t="n"/>
-      <c r="L332" s="13" t="n"/>
+      <c r="I332" s="14" t="n"/>
+      <c r="J332" s="15" t="n"/>
+      <c r="K332" s="14" t="n"/>
+      <c r="L332" s="16" t="n"/>
+      <c r="M332" s="13" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="11" t="n"/>
@@ -6612,10 +7021,11 @@
       <c r="F333" s="14" t="n"/>
       <c r="G333" s="14" t="n"/>
       <c r="H333" s="14" t="n"/>
-      <c r="I333" s="15" t="n"/>
-      <c r="J333" s="14" t="n"/>
-      <c r="K333" s="16" t="n"/>
-      <c r="L333" s="13" t="n"/>
+      <c r="I333" s="14" t="n"/>
+      <c r="J333" s="15" t="n"/>
+      <c r="K333" s="14" t="n"/>
+      <c r="L333" s="16" t="n"/>
+      <c r="M333" s="13" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="11" t="n"/>
@@ -6626,10 +7036,11 @@
       <c r="F334" s="14" t="n"/>
       <c r="G334" s="14" t="n"/>
       <c r="H334" s="14" t="n"/>
-      <c r="I334" s="15" t="n"/>
-      <c r="J334" s="14" t="n"/>
-      <c r="K334" s="16" t="n"/>
-      <c r="L334" s="13" t="n"/>
+      <c r="I334" s="14" t="n"/>
+      <c r="J334" s="15" t="n"/>
+      <c r="K334" s="14" t="n"/>
+      <c r="L334" s="16" t="n"/>
+      <c r="M334" s="13" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="11" t="n"/>
@@ -6640,10 +7051,11 @@
       <c r="F335" s="14" t="n"/>
       <c r="G335" s="14" t="n"/>
       <c r="H335" s="14" t="n"/>
-      <c r="I335" s="15" t="n"/>
-      <c r="J335" s="14" t="n"/>
-      <c r="K335" s="16" t="n"/>
-      <c r="L335" s="13" t="n"/>
+      <c r="I335" s="14" t="n"/>
+      <c r="J335" s="15" t="n"/>
+      <c r="K335" s="14" t="n"/>
+      <c r="L335" s="16" t="n"/>
+      <c r="M335" s="13" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="11" t="n"/>
@@ -6654,10 +7066,11 @@
       <c r="F336" s="14" t="n"/>
       <c r="G336" s="14" t="n"/>
       <c r="H336" s="14" t="n"/>
-      <c r="I336" s="15" t="n"/>
-      <c r="J336" s="14" t="n"/>
-      <c r="K336" s="16" t="n"/>
-      <c r="L336" s="13" t="n"/>
+      <c r="I336" s="14" t="n"/>
+      <c r="J336" s="15" t="n"/>
+      <c r="K336" s="14" t="n"/>
+      <c r="L336" s="16" t="n"/>
+      <c r="M336" s="13" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="n"/>
@@ -6668,10 +7081,11 @@
       <c r="F337" s="14" t="n"/>
       <c r="G337" s="14" t="n"/>
       <c r="H337" s="14" t="n"/>
-      <c r="I337" s="15" t="n"/>
-      <c r="J337" s="14" t="n"/>
-      <c r="K337" s="16" t="n"/>
-      <c r="L337" s="13" t="n"/>
+      <c r="I337" s="14" t="n"/>
+      <c r="J337" s="15" t="n"/>
+      <c r="K337" s="14" t="n"/>
+      <c r="L337" s="16" t="n"/>
+      <c r="M337" s="13" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="11" t="n"/>
@@ -6682,10 +7096,11 @@
       <c r="F338" s="14" t="n"/>
       <c r="G338" s="14" t="n"/>
       <c r="H338" s="14" t="n"/>
-      <c r="I338" s="15" t="n"/>
-      <c r="J338" s="14" t="n"/>
-      <c r="K338" s="16" t="n"/>
-      <c r="L338" s="13" t="n"/>
+      <c r="I338" s="14" t="n"/>
+      <c r="J338" s="15" t="n"/>
+      <c r="K338" s="14" t="n"/>
+      <c r="L338" s="16" t="n"/>
+      <c r="M338" s="13" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="n"/>
@@ -6696,10 +7111,11 @@
       <c r="F339" s="14" t="n"/>
       <c r="G339" s="14" t="n"/>
       <c r="H339" s="14" t="n"/>
-      <c r="I339" s="15" t="n"/>
-      <c r="J339" s="14" t="n"/>
-      <c r="K339" s="16" t="n"/>
-      <c r="L339" s="13" t="n"/>
+      <c r="I339" s="14" t="n"/>
+      <c r="J339" s="15" t="n"/>
+      <c r="K339" s="14" t="n"/>
+      <c r="L339" s="16" t="n"/>
+      <c r="M339" s="13" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="n"/>
@@ -6710,10 +7126,11 @@
       <c r="F340" s="14" t="n"/>
       <c r="G340" s="14" t="n"/>
       <c r="H340" s="14" t="n"/>
-      <c r="I340" s="15" t="n"/>
-      <c r="J340" s="14" t="n"/>
-      <c r="K340" s="16" t="n"/>
-      <c r="L340" s="13" t="n"/>
+      <c r="I340" s="14" t="n"/>
+      <c r="J340" s="15" t="n"/>
+      <c r="K340" s="14" t="n"/>
+      <c r="L340" s="16" t="n"/>
+      <c r="M340" s="13" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="n"/>
@@ -6724,10 +7141,11 @@
       <c r="F341" s="14" t="n"/>
       <c r="G341" s="14" t="n"/>
       <c r="H341" s="14" t="n"/>
-      <c r="I341" s="15" t="n"/>
-      <c r="J341" s="14" t="n"/>
-      <c r="K341" s="16" t="n"/>
-      <c r="L341" s="13" t="n"/>
+      <c r="I341" s="14" t="n"/>
+      <c r="J341" s="15" t="n"/>
+      <c r="K341" s="14" t="n"/>
+      <c r="L341" s="16" t="n"/>
+      <c r="M341" s="13" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="11" t="n"/>
@@ -6738,10 +7156,11 @@
       <c r="F342" s="14" t="n"/>
       <c r="G342" s="14" t="n"/>
       <c r="H342" s="14" t="n"/>
-      <c r="I342" s="15" t="n"/>
-      <c r="J342" s="14" t="n"/>
-      <c r="K342" s="16" t="n"/>
-      <c r="L342" s="13" t="n"/>
+      <c r="I342" s="14" t="n"/>
+      <c r="J342" s="15" t="n"/>
+      <c r="K342" s="14" t="n"/>
+      <c r="L342" s="16" t="n"/>
+      <c r="M342" s="13" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="11" t="n"/>
@@ -6752,10 +7171,11 @@
       <c r="F343" s="14" t="n"/>
       <c r="G343" s="14" t="n"/>
       <c r="H343" s="14" t="n"/>
-      <c r="I343" s="15" t="n"/>
-      <c r="J343" s="14" t="n"/>
-      <c r="K343" s="16" t="n"/>
-      <c r="L343" s="13" t="n"/>
+      <c r="I343" s="14" t="n"/>
+      <c r="J343" s="15" t="n"/>
+      <c r="K343" s="14" t="n"/>
+      <c r="L343" s="16" t="n"/>
+      <c r="M343" s="13" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="11" t="n"/>
@@ -6766,10 +7186,11 @@
       <c r="F344" s="14" t="n"/>
       <c r="G344" s="14" t="n"/>
       <c r="H344" s="14" t="n"/>
-      <c r="I344" s="15" t="n"/>
-      <c r="J344" s="14" t="n"/>
-      <c r="K344" s="16" t="n"/>
-      <c r="L344" s="13" t="n"/>
+      <c r="I344" s="14" t="n"/>
+      <c r="J344" s="15" t="n"/>
+      <c r="K344" s="14" t="n"/>
+      <c r="L344" s="16" t="n"/>
+      <c r="M344" s="13" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="n"/>
@@ -6780,10 +7201,11 @@
       <c r="F345" s="14" t="n"/>
       <c r="G345" s="14" t="n"/>
       <c r="H345" s="14" t="n"/>
-      <c r="I345" s="15" t="n"/>
-      <c r="J345" s="14" t="n"/>
-      <c r="K345" s="16" t="n"/>
-      <c r="L345" s="13" t="n"/>
+      <c r="I345" s="14" t="n"/>
+      <c r="J345" s="15" t="n"/>
+      <c r="K345" s="14" t="n"/>
+      <c r="L345" s="16" t="n"/>
+      <c r="M345" s="13" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="n"/>
@@ -6794,10 +7216,11 @@
       <c r="F346" s="14" t="n"/>
       <c r="G346" s="14" t="n"/>
       <c r="H346" s="14" t="n"/>
-      <c r="I346" s="15" t="n"/>
-      <c r="J346" s="14" t="n"/>
-      <c r="K346" s="16" t="n"/>
-      <c r="L346" s="13" t="n"/>
+      <c r="I346" s="14" t="n"/>
+      <c r="J346" s="15" t="n"/>
+      <c r="K346" s="14" t="n"/>
+      <c r="L346" s="16" t="n"/>
+      <c r="M346" s="13" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="11" t="n"/>
@@ -6808,10 +7231,11 @@
       <c r="F347" s="14" t="n"/>
       <c r="G347" s="14" t="n"/>
       <c r="H347" s="14" t="n"/>
-      <c r="I347" s="15" t="n"/>
-      <c r="J347" s="14" t="n"/>
-      <c r="K347" s="16" t="n"/>
-      <c r="L347" s="13" t="n"/>
+      <c r="I347" s="14" t="n"/>
+      <c r="J347" s="15" t="n"/>
+      <c r="K347" s="14" t="n"/>
+      <c r="L347" s="16" t="n"/>
+      <c r="M347" s="13" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="11" t="n"/>
@@ -6822,10 +7246,11 @@
       <c r="F348" s="14" t="n"/>
       <c r="G348" s="14" t="n"/>
       <c r="H348" s="14" t="n"/>
-      <c r="I348" s="15" t="n"/>
-      <c r="J348" s="14" t="n"/>
-      <c r="K348" s="16" t="n"/>
-      <c r="L348" s="13" t="n"/>
+      <c r="I348" s="14" t="n"/>
+      <c r="J348" s="15" t="n"/>
+      <c r="K348" s="14" t="n"/>
+      <c r="L348" s="16" t="n"/>
+      <c r="M348" s="13" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="11" t="n"/>
@@ -6836,10 +7261,11 @@
       <c r="F349" s="14" t="n"/>
       <c r="G349" s="14" t="n"/>
       <c r="H349" s="14" t="n"/>
-      <c r="I349" s="15" t="n"/>
-      <c r="J349" s="14" t="n"/>
-      <c r="K349" s="16" t="n"/>
-      <c r="L349" s="13" t="n"/>
+      <c r="I349" s="14" t="n"/>
+      <c r="J349" s="15" t="n"/>
+      <c r="K349" s="14" t="n"/>
+      <c r="L349" s="16" t="n"/>
+      <c r="M349" s="13" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="11" t="n"/>
@@ -6850,10 +7276,11 @@
       <c r="F350" s="14" t="n"/>
       <c r="G350" s="14" t="n"/>
       <c r="H350" s="14" t="n"/>
-      <c r="I350" s="15" t="n"/>
-      <c r="J350" s="14" t="n"/>
-      <c r="K350" s="16" t="n"/>
-      <c r="L350" s="13" t="n"/>
+      <c r="I350" s="14" t="n"/>
+      <c r="J350" s="15" t="n"/>
+      <c r="K350" s="14" t="n"/>
+      <c r="L350" s="16" t="n"/>
+      <c r="M350" s="13" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="11" t="n"/>
@@ -6864,10 +7291,11 @@
       <c r="F351" s="14" t="n"/>
       <c r="G351" s="14" t="n"/>
       <c r="H351" s="14" t="n"/>
-      <c r="I351" s="15" t="n"/>
-      <c r="J351" s="14" t="n"/>
-      <c r="K351" s="16" t="n"/>
-      <c r="L351" s="13" t="n"/>
+      <c r="I351" s="14" t="n"/>
+      <c r="J351" s="15" t="n"/>
+      <c r="K351" s="14" t="n"/>
+      <c r="L351" s="16" t="n"/>
+      <c r="M351" s="13" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="11" t="n"/>
@@ -6878,10 +7306,11 @@
       <c r="F352" s="14" t="n"/>
       <c r="G352" s="14" t="n"/>
       <c r="H352" s="14" t="n"/>
-      <c r="I352" s="15" t="n"/>
-      <c r="J352" s="14" t="n"/>
-      <c r="K352" s="16" t="n"/>
-      <c r="L352" s="13" t="n"/>
+      <c r="I352" s="14" t="n"/>
+      <c r="J352" s="15" t="n"/>
+      <c r="K352" s="14" t="n"/>
+      <c r="L352" s="16" t="n"/>
+      <c r="M352" s="13" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="11" t="n"/>
@@ -6892,10 +7321,11 @@
       <c r="F353" s="14" t="n"/>
       <c r="G353" s="14" t="n"/>
       <c r="H353" s="14" t="n"/>
-      <c r="I353" s="15" t="n"/>
-      <c r="J353" s="14" t="n"/>
-      <c r="K353" s="16" t="n"/>
-      <c r="L353" s="13" t="n"/>
+      <c r="I353" s="14" t="n"/>
+      <c r="J353" s="15" t="n"/>
+      <c r="K353" s="14" t="n"/>
+      <c r="L353" s="16" t="n"/>
+      <c r="M353" s="13" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="11" t="n"/>
@@ -6906,10 +7336,11 @@
       <c r="F354" s="14" t="n"/>
       <c r="G354" s="14" t="n"/>
       <c r="H354" s="14" t="n"/>
-      <c r="I354" s="15" t="n"/>
-      <c r="J354" s="14" t="n"/>
-      <c r="K354" s="16" t="n"/>
-      <c r="L354" s="13" t="n"/>
+      <c r="I354" s="14" t="n"/>
+      <c r="J354" s="15" t="n"/>
+      <c r="K354" s="14" t="n"/>
+      <c r="L354" s="16" t="n"/>
+      <c r="M354" s="13" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="11" t="n"/>
@@ -6920,10 +7351,11 @@
       <c r="F355" s="14" t="n"/>
       <c r="G355" s="14" t="n"/>
       <c r="H355" s="14" t="n"/>
-      <c r="I355" s="15" t="n"/>
-      <c r="J355" s="14" t="n"/>
-      <c r="K355" s="16" t="n"/>
-      <c r="L355" s="13" t="n"/>
+      <c r="I355" s="14" t="n"/>
+      <c r="J355" s="15" t="n"/>
+      <c r="K355" s="14" t="n"/>
+      <c r="L355" s="16" t="n"/>
+      <c r="M355" s="13" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="11" t="n"/>
@@ -6934,10 +7366,11 @@
       <c r="F356" s="14" t="n"/>
       <c r="G356" s="14" t="n"/>
       <c r="H356" s="14" t="n"/>
-      <c r="I356" s="15" t="n"/>
-      <c r="J356" s="14" t="n"/>
-      <c r="K356" s="16" t="n"/>
-      <c r="L356" s="13" t="n"/>
+      <c r="I356" s="14" t="n"/>
+      <c r="J356" s="15" t="n"/>
+      <c r="K356" s="14" t="n"/>
+      <c r="L356" s="16" t="n"/>
+      <c r="M356" s="13" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="11" t="n"/>
@@ -6948,10 +7381,11 @@
       <c r="F357" s="14" t="n"/>
       <c r="G357" s="14" t="n"/>
       <c r="H357" s="14" t="n"/>
-      <c r="I357" s="15" t="n"/>
-      <c r="J357" s="14" t="n"/>
-      <c r="K357" s="16" t="n"/>
-      <c r="L357" s="13" t="n"/>
+      <c r="I357" s="14" t="n"/>
+      <c r="J357" s="15" t="n"/>
+      <c r="K357" s="14" t="n"/>
+      <c r="L357" s="16" t="n"/>
+      <c r="M357" s="13" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="n"/>
@@ -6962,10 +7396,11 @@
       <c r="F358" s="14" t="n"/>
       <c r="G358" s="14" t="n"/>
       <c r="H358" s="14" t="n"/>
-      <c r="I358" s="15" t="n"/>
-      <c r="J358" s="14" t="n"/>
-      <c r="K358" s="16" t="n"/>
-      <c r="L358" s="13" t="n"/>
+      <c r="I358" s="14" t="n"/>
+      <c r="J358" s="15" t="n"/>
+      <c r="K358" s="14" t="n"/>
+      <c r="L358" s="16" t="n"/>
+      <c r="M358" s="13" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="11" t="n"/>
@@ -6976,10 +7411,11 @@
       <c r="F359" s="14" t="n"/>
       <c r="G359" s="14" t="n"/>
       <c r="H359" s="14" t="n"/>
-      <c r="I359" s="15" t="n"/>
-      <c r="J359" s="14" t="n"/>
-      <c r="K359" s="16" t="n"/>
-      <c r="L359" s="13" t="n"/>
+      <c r="I359" s="14" t="n"/>
+      <c r="J359" s="15" t="n"/>
+      <c r="K359" s="14" t="n"/>
+      <c r="L359" s="16" t="n"/>
+      <c r="M359" s="13" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="11" t="n"/>
@@ -6990,10 +7426,11 @@
       <c r="F360" s="14" t="n"/>
       <c r="G360" s="14" t="n"/>
       <c r="H360" s="14" t="n"/>
-      <c r="I360" s="15" t="n"/>
-      <c r="J360" s="14" t="n"/>
-      <c r="K360" s="16" t="n"/>
-      <c r="L360" s="13" t="n"/>
+      <c r="I360" s="14" t="n"/>
+      <c r="J360" s="15" t="n"/>
+      <c r="K360" s="14" t="n"/>
+      <c r="L360" s="16" t="n"/>
+      <c r="M360" s="13" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="11" t="n"/>
@@ -7004,10 +7441,11 @@
       <c r="F361" s="14" t="n"/>
       <c r="G361" s="14" t="n"/>
       <c r="H361" s="14" t="n"/>
-      <c r="I361" s="15" t="n"/>
-      <c r="J361" s="14" t="n"/>
-      <c r="K361" s="16" t="n"/>
-      <c r="L361" s="13" t="n"/>
+      <c r="I361" s="14" t="n"/>
+      <c r="J361" s="15" t="n"/>
+      <c r="K361" s="14" t="n"/>
+      <c r="L361" s="16" t="n"/>
+      <c r="M361" s="13" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="11" t="n"/>
@@ -7018,10 +7456,11 @@
       <c r="F362" s="14" t="n"/>
       <c r="G362" s="14" t="n"/>
       <c r="H362" s="14" t="n"/>
-      <c r="I362" s="15" t="n"/>
-      <c r="J362" s="14" t="n"/>
-      <c r="K362" s="16" t="n"/>
-      <c r="L362" s="13" t="n"/>
+      <c r="I362" s="14" t="n"/>
+      <c r="J362" s="15" t="n"/>
+      <c r="K362" s="14" t="n"/>
+      <c r="L362" s="16" t="n"/>
+      <c r="M362" s="13" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="11" t="n"/>
@@ -7032,10 +7471,11 @@
       <c r="F363" s="14" t="n"/>
       <c r="G363" s="14" t="n"/>
       <c r="H363" s="14" t="n"/>
-      <c r="I363" s="15" t="n"/>
-      <c r="J363" s="14" t="n"/>
-      <c r="K363" s="16" t="n"/>
-      <c r="L363" s="13" t="n"/>
+      <c r="I363" s="14" t="n"/>
+      <c r="J363" s="15" t="n"/>
+      <c r="K363" s="14" t="n"/>
+      <c r="L363" s="16" t="n"/>
+      <c r="M363" s="13" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="11" t="n"/>
@@ -7046,10 +7486,11 @@
       <c r="F364" s="14" t="n"/>
       <c r="G364" s="14" t="n"/>
       <c r="H364" s="14" t="n"/>
-      <c r="I364" s="15" t="n"/>
-      <c r="J364" s="14" t="n"/>
-      <c r="K364" s="16" t="n"/>
-      <c r="L364" s="13" t="n"/>
+      <c r="I364" s="14" t="n"/>
+      <c r="J364" s="15" t="n"/>
+      <c r="K364" s="14" t="n"/>
+      <c r="L364" s="16" t="n"/>
+      <c r="M364" s="13" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="11" t="n"/>
@@ -7060,10 +7501,11 @@
       <c r="F365" s="14" t="n"/>
       <c r="G365" s="14" t="n"/>
       <c r="H365" s="14" t="n"/>
-      <c r="I365" s="15" t="n"/>
-      <c r="J365" s="14" t="n"/>
-      <c r="K365" s="16" t="n"/>
-      <c r="L365" s="13" t="n"/>
+      <c r="I365" s="14" t="n"/>
+      <c r="J365" s="15" t="n"/>
+      <c r="K365" s="14" t="n"/>
+      <c r="L365" s="16" t="n"/>
+      <c r="M365" s="13" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="n"/>
@@ -7074,10 +7516,11 @@
       <c r="F366" s="14" t="n"/>
       <c r="G366" s="14" t="n"/>
       <c r="H366" s="14" t="n"/>
-      <c r="I366" s="15" t="n"/>
-      <c r="J366" s="14" t="n"/>
-      <c r="K366" s="16" t="n"/>
-      <c r="L366" s="13" t="n"/>
+      <c r="I366" s="14" t="n"/>
+      <c r="J366" s="15" t="n"/>
+      <c r="K366" s="14" t="n"/>
+      <c r="L366" s="16" t="n"/>
+      <c r="M366" s="13" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="11" t="n"/>
@@ -7088,10 +7531,11 @@
       <c r="F367" s="14" t="n"/>
       <c r="G367" s="14" t="n"/>
       <c r="H367" s="14" t="n"/>
-      <c r="I367" s="15" t="n"/>
-      <c r="J367" s="14" t="n"/>
-      <c r="K367" s="16" t="n"/>
-      <c r="L367" s="13" t="n"/>
+      <c r="I367" s="14" t="n"/>
+      <c r="J367" s="15" t="n"/>
+      <c r="K367" s="14" t="n"/>
+      <c r="L367" s="16" t="n"/>
+      <c r="M367" s="13" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="11" t="n"/>
@@ -7102,10 +7546,11 @@
       <c r="F368" s="14" t="n"/>
       <c r="G368" s="14" t="n"/>
       <c r="H368" s="14" t="n"/>
-      <c r="I368" s="15" t="n"/>
-      <c r="J368" s="14" t="n"/>
-      <c r="K368" s="16" t="n"/>
-      <c r="L368" s="13" t="n"/>
+      <c r="I368" s="14" t="n"/>
+      <c r="J368" s="15" t="n"/>
+      <c r="K368" s="14" t="n"/>
+      <c r="L368" s="16" t="n"/>
+      <c r="M368" s="13" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="11" t="n"/>
@@ -7116,10 +7561,11 @@
       <c r="F369" s="14" t="n"/>
       <c r="G369" s="14" t="n"/>
       <c r="H369" s="14" t="n"/>
-      <c r="I369" s="15" t="n"/>
-      <c r="J369" s="14" t="n"/>
-      <c r="K369" s="16" t="n"/>
-      <c r="L369" s="13" t="n"/>
+      <c r="I369" s="14" t="n"/>
+      <c r="J369" s="15" t="n"/>
+      <c r="K369" s="14" t="n"/>
+      <c r="L369" s="16" t="n"/>
+      <c r="M369" s="13" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="11" t="n"/>
@@ -7130,10 +7576,11 @@
       <c r="F370" s="14" t="n"/>
       <c r="G370" s="14" t="n"/>
       <c r="H370" s="14" t="n"/>
-      <c r="I370" s="15" t="n"/>
-      <c r="J370" s="14" t="n"/>
-      <c r="K370" s="16" t="n"/>
-      <c r="L370" s="13" t="n"/>
+      <c r="I370" s="14" t="n"/>
+      <c r="J370" s="15" t="n"/>
+      <c r="K370" s="14" t="n"/>
+      <c r="L370" s="16" t="n"/>
+      <c r="M370" s="13" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="11" t="n"/>
@@ -7144,10 +7591,11 @@
       <c r="F371" s="14" t="n"/>
       <c r="G371" s="14" t="n"/>
       <c r="H371" s="14" t="n"/>
-      <c r="I371" s="15" t="n"/>
-      <c r="J371" s="14" t="n"/>
-      <c r="K371" s="16" t="n"/>
-      <c r="L371" s="13" t="n"/>
+      <c r="I371" s="14" t="n"/>
+      <c r="J371" s="15" t="n"/>
+      <c r="K371" s="14" t="n"/>
+      <c r="L371" s="16" t="n"/>
+      <c r="M371" s="13" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="11" t="n"/>
@@ -7158,10 +7606,11 @@
       <c r="F372" s="14" t="n"/>
       <c r="G372" s="14" t="n"/>
       <c r="H372" s="14" t="n"/>
-      <c r="I372" s="15" t="n"/>
-      <c r="J372" s="14" t="n"/>
-      <c r="K372" s="16" t="n"/>
-      <c r="L372" s="13" t="n"/>
+      <c r="I372" s="14" t="n"/>
+      <c r="J372" s="15" t="n"/>
+      <c r="K372" s="14" t="n"/>
+      <c r="L372" s="16" t="n"/>
+      <c r="M372" s="13" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="11" t="n"/>
@@ -7172,10 +7621,11 @@
       <c r="F373" s="14" t="n"/>
       <c r="G373" s="14" t="n"/>
       <c r="H373" s="14" t="n"/>
-      <c r="I373" s="15" t="n"/>
-      <c r="J373" s="14" t="n"/>
-      <c r="K373" s="16" t="n"/>
-      <c r="L373" s="13" t="n"/>
+      <c r="I373" s="14" t="n"/>
+      <c r="J373" s="15" t="n"/>
+      <c r="K373" s="14" t="n"/>
+      <c r="L373" s="16" t="n"/>
+      <c r="M373" s="13" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="11" t="n"/>
@@ -7186,10 +7636,11 @@
       <c r="F374" s="14" t="n"/>
       <c r="G374" s="14" t="n"/>
       <c r="H374" s="14" t="n"/>
-      <c r="I374" s="15" t="n"/>
-      <c r="J374" s="14" t="n"/>
-      <c r="K374" s="16" t="n"/>
-      <c r="L374" s="13" t="n"/>
+      <c r="I374" s="14" t="n"/>
+      <c r="J374" s="15" t="n"/>
+      <c r="K374" s="14" t="n"/>
+      <c r="L374" s="16" t="n"/>
+      <c r="M374" s="13" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="11" t="n"/>
@@ -7200,10 +7651,11 @@
       <c r="F375" s="14" t="n"/>
       <c r="G375" s="14" t="n"/>
       <c r="H375" s="14" t="n"/>
-      <c r="I375" s="15" t="n"/>
-      <c r="J375" s="14" t="n"/>
-      <c r="K375" s="16" t="n"/>
-      <c r="L375" s="13" t="n"/>
+      <c r="I375" s="14" t="n"/>
+      <c r="J375" s="15" t="n"/>
+      <c r="K375" s="14" t="n"/>
+      <c r="L375" s="16" t="n"/>
+      <c r="M375" s="13" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="11" t="n"/>
@@ -7214,10 +7666,11 @@
       <c r="F376" s="14" t="n"/>
       <c r="G376" s="14" t="n"/>
       <c r="H376" s="14" t="n"/>
-      <c r="I376" s="15" t="n"/>
-      <c r="J376" s="14" t="n"/>
-      <c r="K376" s="16" t="n"/>
-      <c r="L376" s="13" t="n"/>
+      <c r="I376" s="14" t="n"/>
+      <c r="J376" s="15" t="n"/>
+      <c r="K376" s="14" t="n"/>
+      <c r="L376" s="16" t="n"/>
+      <c r="M376" s="13" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="11" t="n"/>
@@ -7228,10 +7681,11 @@
       <c r="F377" s="14" t="n"/>
       <c r="G377" s="14" t="n"/>
       <c r="H377" s="14" t="n"/>
-      <c r="I377" s="15" t="n"/>
-      <c r="J377" s="14" t="n"/>
-      <c r="K377" s="16" t="n"/>
-      <c r="L377" s="13" t="n"/>
+      <c r="I377" s="14" t="n"/>
+      <c r="J377" s="15" t="n"/>
+      <c r="K377" s="14" t="n"/>
+      <c r="L377" s="16" t="n"/>
+      <c r="M377" s="13" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="11" t="n"/>
@@ -7242,10 +7696,11 @@
       <c r="F378" s="14" t="n"/>
       <c r="G378" s="14" t="n"/>
       <c r="H378" s="14" t="n"/>
-      <c r="I378" s="15" t="n"/>
-      <c r="J378" s="14" t="n"/>
-      <c r="K378" s="16" t="n"/>
-      <c r="L378" s="13" t="n"/>
+      <c r="I378" s="14" t="n"/>
+      <c r="J378" s="15" t="n"/>
+      <c r="K378" s="14" t="n"/>
+      <c r="L378" s="16" t="n"/>
+      <c r="M378" s="13" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="n"/>
@@ -7256,10 +7711,11 @@
       <c r="F379" s="14" t="n"/>
       <c r="G379" s="14" t="n"/>
       <c r="H379" s="14" t="n"/>
-      <c r="I379" s="15" t="n"/>
-      <c r="J379" s="14" t="n"/>
-      <c r="K379" s="16" t="n"/>
-      <c r="L379" s="13" t="n"/>
+      <c r="I379" s="14" t="n"/>
+      <c r="J379" s="15" t="n"/>
+      <c r="K379" s="14" t="n"/>
+      <c r="L379" s="16" t="n"/>
+      <c r="M379" s="13" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="11" t="n"/>
@@ -7270,10 +7726,11 @@
       <c r="F380" s="14" t="n"/>
       <c r="G380" s="14" t="n"/>
       <c r="H380" s="14" t="n"/>
-      <c r="I380" s="15" t="n"/>
-      <c r="J380" s="14" t="n"/>
-      <c r="K380" s="16" t="n"/>
-      <c r="L380" s="13" t="n"/>
+      <c r="I380" s="14" t="n"/>
+      <c r="J380" s="15" t="n"/>
+      <c r="K380" s="14" t="n"/>
+      <c r="L380" s="16" t="n"/>
+      <c r="M380" s="13" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="11" t="n"/>
@@ -7284,10 +7741,11 @@
       <c r="F381" s="14" t="n"/>
       <c r="G381" s="14" t="n"/>
       <c r="H381" s="14" t="n"/>
-      <c r="I381" s="15" t="n"/>
-      <c r="J381" s="14" t="n"/>
-      <c r="K381" s="16" t="n"/>
-      <c r="L381" s="13" t="n"/>
+      <c r="I381" s="14" t="n"/>
+      <c r="J381" s="15" t="n"/>
+      <c r="K381" s="14" t="n"/>
+      <c r="L381" s="16" t="n"/>
+      <c r="M381" s="13" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="11" t="n"/>
@@ -7298,10 +7756,11 @@
       <c r="F382" s="14" t="n"/>
       <c r="G382" s="14" t="n"/>
       <c r="H382" s="14" t="n"/>
-      <c r="I382" s="15" t="n"/>
-      <c r="J382" s="14" t="n"/>
-      <c r="K382" s="16" t="n"/>
-      <c r="L382" s="13" t="n"/>
+      <c r="I382" s="14" t="n"/>
+      <c r="J382" s="15" t="n"/>
+      <c r="K382" s="14" t="n"/>
+      <c r="L382" s="16" t="n"/>
+      <c r="M382" s="13" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="11" t="n"/>
@@ -7312,10 +7771,11 @@
       <c r="F383" s="14" t="n"/>
       <c r="G383" s="14" t="n"/>
       <c r="H383" s="14" t="n"/>
-      <c r="I383" s="15" t="n"/>
-      <c r="J383" s="14" t="n"/>
-      <c r="K383" s="16" t="n"/>
-      <c r="L383" s="13" t="n"/>
+      <c r="I383" s="14" t="n"/>
+      <c r="J383" s="15" t="n"/>
+      <c r="K383" s="14" t="n"/>
+      <c r="L383" s="16" t="n"/>
+      <c r="M383" s="13" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="11" t="n"/>
@@ -7326,10 +7786,11 @@
       <c r="F384" s="14" t="n"/>
       <c r="G384" s="14" t="n"/>
       <c r="H384" s="14" t="n"/>
-      <c r="I384" s="15" t="n"/>
-      <c r="J384" s="14" t="n"/>
-      <c r="K384" s="16" t="n"/>
-      <c r="L384" s="13" t="n"/>
+      <c r="I384" s="14" t="n"/>
+      <c r="J384" s="15" t="n"/>
+      <c r="K384" s="14" t="n"/>
+      <c r="L384" s="16" t="n"/>
+      <c r="M384" s="13" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="11" t="n"/>
@@ -7340,10 +7801,11 @@
       <c r="F385" s="14" t="n"/>
       <c r="G385" s="14" t="n"/>
       <c r="H385" s="14" t="n"/>
-      <c r="I385" s="15" t="n"/>
-      <c r="J385" s="14" t="n"/>
-      <c r="K385" s="16" t="n"/>
-      <c r="L385" s="13" t="n"/>
+      <c r="I385" s="14" t="n"/>
+      <c r="J385" s="15" t="n"/>
+      <c r="K385" s="14" t="n"/>
+      <c r="L385" s="16" t="n"/>
+      <c r="M385" s="13" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="11" t="n"/>
@@ -7354,10 +7816,11 @@
       <c r="F386" s="14" t="n"/>
       <c r="G386" s="14" t="n"/>
       <c r="H386" s="14" t="n"/>
-      <c r="I386" s="15" t="n"/>
-      <c r="J386" s="14" t="n"/>
-      <c r="K386" s="16" t="n"/>
-      <c r="L386" s="13" t="n"/>
+      <c r="I386" s="14" t="n"/>
+      <c r="J386" s="15" t="n"/>
+      <c r="K386" s="14" t="n"/>
+      <c r="L386" s="16" t="n"/>
+      <c r="M386" s="13" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="11" t="n"/>
@@ -7368,10 +7831,11 @@
       <c r="F387" s="14" t="n"/>
       <c r="G387" s="14" t="n"/>
       <c r="H387" s="14" t="n"/>
-      <c r="I387" s="15" t="n"/>
-      <c r="J387" s="14" t="n"/>
-      <c r="K387" s="16" t="n"/>
-      <c r="L387" s="13" t="n"/>
+      <c r="I387" s="14" t="n"/>
+      <c r="J387" s="15" t="n"/>
+      <c r="K387" s="14" t="n"/>
+      <c r="L387" s="16" t="n"/>
+      <c r="M387" s="13" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="11" t="n"/>
@@ -7382,10 +7846,11 @@
       <c r="F388" s="14" t="n"/>
       <c r="G388" s="14" t="n"/>
       <c r="H388" s="14" t="n"/>
-      <c r="I388" s="15" t="n"/>
-      <c r="J388" s="14" t="n"/>
-      <c r="K388" s="16" t="n"/>
-      <c r="L388" s="13" t="n"/>
+      <c r="I388" s="14" t="n"/>
+      <c r="J388" s="15" t="n"/>
+      <c r="K388" s="14" t="n"/>
+      <c r="L388" s="16" t="n"/>
+      <c r="M388" s="13" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="11" t="n"/>
@@ -7396,10 +7861,11 @@
       <c r="F389" s="14" t="n"/>
       <c r="G389" s="14" t="n"/>
       <c r="H389" s="14" t="n"/>
-      <c r="I389" s="15" t="n"/>
-      <c r="J389" s="14" t="n"/>
-      <c r="K389" s="16" t="n"/>
-      <c r="L389" s="13" t="n"/>
+      <c r="I389" s="14" t="n"/>
+      <c r="J389" s="15" t="n"/>
+      <c r="K389" s="14" t="n"/>
+      <c r="L389" s="16" t="n"/>
+      <c r="M389" s="13" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="11" t="n"/>
@@ -7410,10 +7876,11 @@
       <c r="F390" s="14" t="n"/>
       <c r="G390" s="14" t="n"/>
       <c r="H390" s="14" t="n"/>
-      <c r="I390" s="15" t="n"/>
-      <c r="J390" s="14" t="n"/>
-      <c r="K390" s="16" t="n"/>
-      <c r="L390" s="13" t="n"/>
+      <c r="I390" s="14" t="n"/>
+      <c r="J390" s="15" t="n"/>
+      <c r="K390" s="14" t="n"/>
+      <c r="L390" s="16" t="n"/>
+      <c r="M390" s="13" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="11" t="n"/>
@@ -7424,10 +7891,11 @@
       <c r="F391" s="14" t="n"/>
       <c r="G391" s="14" t="n"/>
       <c r="H391" s="14" t="n"/>
-      <c r="I391" s="15" t="n"/>
-      <c r="J391" s="14" t="n"/>
-      <c r="K391" s="16" t="n"/>
-      <c r="L391" s="13" t="n"/>
+      <c r="I391" s="14" t="n"/>
+      <c r="J391" s="15" t="n"/>
+      <c r="K391" s="14" t="n"/>
+      <c r="L391" s="16" t="n"/>
+      <c r="M391" s="13" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="n"/>
@@ -7438,10 +7906,11 @@
       <c r="F392" s="14" t="n"/>
       <c r="G392" s="14" t="n"/>
       <c r="H392" s="14" t="n"/>
-      <c r="I392" s="15" t="n"/>
-      <c r="J392" s="14" t="n"/>
-      <c r="K392" s="16" t="n"/>
-      <c r="L392" s="13" t="n"/>
+      <c r="I392" s="14" t="n"/>
+      <c r="J392" s="15" t="n"/>
+      <c r="K392" s="14" t="n"/>
+      <c r="L392" s="16" t="n"/>
+      <c r="M392" s="13" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="11" t="n"/>
@@ -7452,10 +7921,11 @@
       <c r="F393" s="14" t="n"/>
       <c r="G393" s="14" t="n"/>
       <c r="H393" s="14" t="n"/>
-      <c r="I393" s="15" t="n"/>
-      <c r="J393" s="14" t="n"/>
-      <c r="K393" s="16" t="n"/>
-      <c r="L393" s="13" t="n"/>
+      <c r="I393" s="14" t="n"/>
+      <c r="J393" s="15" t="n"/>
+      <c r="K393" s="14" t="n"/>
+      <c r="L393" s="16" t="n"/>
+      <c r="M393" s="13" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="11" t="n"/>
@@ -7466,10 +7936,11 @@
       <c r="F394" s="14" t="n"/>
       <c r="G394" s="14" t="n"/>
       <c r="H394" s="14" t="n"/>
-      <c r="I394" s="15" t="n"/>
-      <c r="J394" s="14" t="n"/>
-      <c r="K394" s="16" t="n"/>
-      <c r="L394" s="13" t="n"/>
+      <c r="I394" s="14" t="n"/>
+      <c r="J394" s="15" t="n"/>
+      <c r="K394" s="14" t="n"/>
+      <c r="L394" s="16" t="n"/>
+      <c r="M394" s="13" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="11" t="n"/>
@@ -7480,10 +7951,11 @@
       <c r="F395" s="14" t="n"/>
       <c r="G395" s="14" t="n"/>
       <c r="H395" s="14" t="n"/>
-      <c r="I395" s="15" t="n"/>
-      <c r="J395" s="14" t="n"/>
-      <c r="K395" s="16" t="n"/>
-      <c r="L395" s="13" t="n"/>
+      <c r="I395" s="14" t="n"/>
+      <c r="J395" s="15" t="n"/>
+      <c r="K395" s="14" t="n"/>
+      <c r="L395" s="16" t="n"/>
+      <c r="M395" s="13" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="11" t="n"/>
@@ -7494,10 +7966,11 @@
       <c r="F396" s="14" t="n"/>
       <c r="G396" s="14" t="n"/>
       <c r="H396" s="14" t="n"/>
-      <c r="I396" s="15" t="n"/>
-      <c r="J396" s="14" t="n"/>
-      <c r="K396" s="16" t="n"/>
-      <c r="L396" s="13" t="n"/>
+      <c r="I396" s="14" t="n"/>
+      <c r="J396" s="15" t="n"/>
+      <c r="K396" s="14" t="n"/>
+      <c r="L396" s="16" t="n"/>
+      <c r="M396" s="13" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="11" t="n"/>
@@ -7508,10 +7981,11 @@
       <c r="F397" s="14" t="n"/>
       <c r="G397" s="14" t="n"/>
       <c r="H397" s="14" t="n"/>
-      <c r="I397" s="15" t="n"/>
-      <c r="J397" s="14" t="n"/>
-      <c r="K397" s="16" t="n"/>
-      <c r="L397" s="13" t="n"/>
+      <c r="I397" s="14" t="n"/>
+      <c r="J397" s="15" t="n"/>
+      <c r="K397" s="14" t="n"/>
+      <c r="L397" s="16" t="n"/>
+      <c r="M397" s="13" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="11" t="n"/>
@@ -7522,10 +7996,11 @@
       <c r="F398" s="14" t="n"/>
       <c r="G398" s="14" t="n"/>
       <c r="H398" s="14" t="n"/>
-      <c r="I398" s="15" t="n"/>
-      <c r="J398" s="14" t="n"/>
-      <c r="K398" s="16" t="n"/>
-      <c r="L398" s="13" t="n"/>
+      <c r="I398" s="14" t="n"/>
+      <c r="J398" s="15" t="n"/>
+      <c r="K398" s="14" t="n"/>
+      <c r="L398" s="16" t="n"/>
+      <c r="M398" s="13" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="11" t="n"/>
@@ -7536,10 +8011,11 @@
       <c r="F399" s="14" t="n"/>
       <c r="G399" s="14" t="n"/>
       <c r="H399" s="14" t="n"/>
-      <c r="I399" s="15" t="n"/>
-      <c r="J399" s="14" t="n"/>
-      <c r="K399" s="16" t="n"/>
-      <c r="L399" s="13" t="n"/>
+      <c r="I399" s="14" t="n"/>
+      <c r="J399" s="15" t="n"/>
+      <c r="K399" s="14" t="n"/>
+      <c r="L399" s="16" t="n"/>
+      <c r="M399" s="13" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="11" t="n"/>
@@ -7550,10 +8026,11 @@
       <c r="F400" s="14" t="n"/>
       <c r="G400" s="14" t="n"/>
       <c r="H400" s="14" t="n"/>
-      <c r="I400" s="15" t="n"/>
-      <c r="J400" s="14" t="n"/>
-      <c r="K400" s="16" t="n"/>
-      <c r="L400" s="13" t="n"/>
+      <c r="I400" s="14" t="n"/>
+      <c r="J400" s="15" t="n"/>
+      <c r="K400" s="14" t="n"/>
+      <c r="L400" s="16" t="n"/>
+      <c r="M400" s="13" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="11" t="n"/>
@@ -7564,10 +8041,11 @@
       <c r="F401" s="14" t="n"/>
       <c r="G401" s="14" t="n"/>
       <c r="H401" s="14" t="n"/>
-      <c r="I401" s="15" t="n"/>
-      <c r="J401" s="14" t="n"/>
-      <c r="K401" s="16" t="n"/>
-      <c r="L401" s="13" t="n"/>
+      <c r="I401" s="14" t="n"/>
+      <c r="J401" s="15" t="n"/>
+      <c r="K401" s="14" t="n"/>
+      <c r="L401" s="16" t="n"/>
+      <c r="M401" s="13" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="11" t="n"/>
@@ -7578,10 +8056,11 @@
       <c r="F402" s="14" t="n"/>
       <c r="G402" s="14" t="n"/>
       <c r="H402" s="14" t="n"/>
-      <c r="I402" s="15" t="n"/>
-      <c r="J402" s="14" t="n"/>
-      <c r="K402" s="16" t="n"/>
-      <c r="L402" s="13" t="n"/>
+      <c r="I402" s="14" t="n"/>
+      <c r="J402" s="15" t="n"/>
+      <c r="K402" s="14" t="n"/>
+      <c r="L402" s="16" t="n"/>
+      <c r="M402" s="13" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="11" t="n"/>
@@ -7592,10 +8071,11 @@
       <c r="F403" s="14" t="n"/>
       <c r="G403" s="14" t="n"/>
       <c r="H403" s="14" t="n"/>
-      <c r="I403" s="15" t="n"/>
-      <c r="J403" s="14" t="n"/>
-      <c r="K403" s="16" t="n"/>
-      <c r="L403" s="13" t="n"/>
+      <c r="I403" s="14" t="n"/>
+      <c r="J403" s="15" t="n"/>
+      <c r="K403" s="14" t="n"/>
+      <c r="L403" s="16" t="n"/>
+      <c r="M403" s="13" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="11" t="n"/>
@@ -7606,10 +8086,11 @@
       <c r="F404" s="14" t="n"/>
       <c r="G404" s="14" t="n"/>
       <c r="H404" s="14" t="n"/>
-      <c r="I404" s="15" t="n"/>
-      <c r="J404" s="14" t="n"/>
-      <c r="K404" s="16" t="n"/>
-      <c r="L404" s="13" t="n"/>
+      <c r="I404" s="14" t="n"/>
+      <c r="J404" s="15" t="n"/>
+      <c r="K404" s="14" t="n"/>
+      <c r="L404" s="16" t="n"/>
+      <c r="M404" s="13" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="11" t="n"/>
@@ -7620,10 +8101,11 @@
       <c r="F405" s="14" t="n"/>
       <c r="G405" s="14" t="n"/>
       <c r="H405" s="14" t="n"/>
-      <c r="I405" s="15" t="n"/>
-      <c r="J405" s="14" t="n"/>
-      <c r="K405" s="16" t="n"/>
-      <c r="L405" s="13" t="n"/>
+      <c r="I405" s="14" t="n"/>
+      <c r="J405" s="15" t="n"/>
+      <c r="K405" s="14" t="n"/>
+      <c r="L405" s="16" t="n"/>
+      <c r="M405" s="13" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="11" t="n"/>
@@ -7634,10 +8116,11 @@
       <c r="F406" s="14" t="n"/>
       <c r="G406" s="14" t="n"/>
       <c r="H406" s="14" t="n"/>
-      <c r="I406" s="15" t="n"/>
-      <c r="J406" s="14" t="n"/>
-      <c r="K406" s="16" t="n"/>
-      <c r="L406" s="13" t="n"/>
+      <c r="I406" s="14" t="n"/>
+      <c r="J406" s="15" t="n"/>
+      <c r="K406" s="14" t="n"/>
+      <c r="L406" s="16" t="n"/>
+      <c r="M406" s="13" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="11" t="n"/>
@@ -7648,10 +8131,11 @@
       <c r="F407" s="14" t="n"/>
       <c r="G407" s="14" t="n"/>
       <c r="H407" s="14" t="n"/>
-      <c r="I407" s="15" t="n"/>
-      <c r="J407" s="14" t="n"/>
-      <c r="K407" s="16" t="n"/>
-      <c r="L407" s="13" t="n"/>
+      <c r="I407" s="14" t="n"/>
+      <c r="J407" s="15" t="n"/>
+      <c r="K407" s="14" t="n"/>
+      <c r="L407" s="16" t="n"/>
+      <c r="M407" s="13" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="11" t="n"/>
@@ -7662,10 +8146,11 @@
       <c r="F408" s="14" t="n"/>
       <c r="G408" s="14" t="n"/>
       <c r="H408" s="14" t="n"/>
-      <c r="I408" s="15" t="n"/>
-      <c r="J408" s="14" t="n"/>
-      <c r="K408" s="16" t="n"/>
-      <c r="L408" s="13" t="n"/>
+      <c r="I408" s="14" t="n"/>
+      <c r="J408" s="15" t="n"/>
+      <c r="K408" s="14" t="n"/>
+      <c r="L408" s="16" t="n"/>
+      <c r="M408" s="13" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="11" t="n"/>
@@ -7676,10 +8161,11 @@
       <c r="F409" s="14" t="n"/>
       <c r="G409" s="14" t="n"/>
       <c r="H409" s="14" t="n"/>
-      <c r="I409" s="15" t="n"/>
-      <c r="J409" s="14" t="n"/>
-      <c r="K409" s="16" t="n"/>
-      <c r="L409" s="13" t="n"/>
+      <c r="I409" s="14" t="n"/>
+      <c r="J409" s="15" t="n"/>
+      <c r="K409" s="14" t="n"/>
+      <c r="L409" s="16" t="n"/>
+      <c r="M409" s="13" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="11" t="n"/>
@@ -7690,10 +8176,11 @@
       <c r="F410" s="14" t="n"/>
       <c r="G410" s="14" t="n"/>
       <c r="H410" s="14" t="n"/>
-      <c r="I410" s="15" t="n"/>
-      <c r="J410" s="14" t="n"/>
-      <c r="K410" s="16" t="n"/>
-      <c r="L410" s="13" t="n"/>
+      <c r="I410" s="14" t="n"/>
+      <c r="J410" s="15" t="n"/>
+      <c r="K410" s="14" t="n"/>
+      <c r="L410" s="16" t="n"/>
+      <c r="M410" s="13" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="11" t="n"/>
@@ -7704,10 +8191,11 @@
       <c r="F411" s="14" t="n"/>
       <c r="G411" s="14" t="n"/>
       <c r="H411" s="14" t="n"/>
-      <c r="I411" s="15" t="n"/>
-      <c r="J411" s="14" t="n"/>
-      <c r="K411" s="16" t="n"/>
-      <c r="L411" s="13" t="n"/>
+      <c r="I411" s="14" t="n"/>
+      <c r="J411" s="15" t="n"/>
+      <c r="K411" s="14" t="n"/>
+      <c r="L411" s="16" t="n"/>
+      <c r="M411" s="13" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="11" t="n"/>
@@ -7718,10 +8206,11 @@
       <c r="F412" s="14" t="n"/>
       <c r="G412" s="14" t="n"/>
       <c r="H412" s="14" t="n"/>
-      <c r="I412" s="15" t="n"/>
-      <c r="J412" s="14" t="n"/>
-      <c r="K412" s="16" t="n"/>
-      <c r="L412" s="13" t="n"/>
+      <c r="I412" s="14" t="n"/>
+      <c r="J412" s="15" t="n"/>
+      <c r="K412" s="14" t="n"/>
+      <c r="L412" s="16" t="n"/>
+      <c r="M412" s="13" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="11" t="n"/>
@@ -7732,10 +8221,11 @@
       <c r="F413" s="14" t="n"/>
       <c r="G413" s="14" t="n"/>
       <c r="H413" s="14" t="n"/>
-      <c r="I413" s="15" t="n"/>
-      <c r="J413" s="14" t="n"/>
-      <c r="K413" s="16" t="n"/>
-      <c r="L413" s="13" t="n"/>
+      <c r="I413" s="14" t="n"/>
+      <c r="J413" s="15" t="n"/>
+      <c r="K413" s="14" t="n"/>
+      <c r="L413" s="16" t="n"/>
+      <c r="M413" s="13" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="11" t="n"/>
@@ -7746,10 +8236,11 @@
       <c r="F414" s="14" t="n"/>
       <c r="G414" s="14" t="n"/>
       <c r="H414" s="14" t="n"/>
-      <c r="I414" s="15" t="n"/>
-      <c r="J414" s="14" t="n"/>
-      <c r="K414" s="16" t="n"/>
-      <c r="L414" s="13" t="n"/>
+      <c r="I414" s="14" t="n"/>
+      <c r="J414" s="15" t="n"/>
+      <c r="K414" s="14" t="n"/>
+      <c r="L414" s="16" t="n"/>
+      <c r="M414" s="13" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="11" t="n"/>
@@ -7760,10 +8251,11 @@
       <c r="F415" s="14" t="n"/>
       <c r="G415" s="14" t="n"/>
       <c r="H415" s="14" t="n"/>
-      <c r="I415" s="15" t="n"/>
-      <c r="J415" s="14" t="n"/>
-      <c r="K415" s="16" t="n"/>
-      <c r="L415" s="13" t="n"/>
+      <c r="I415" s="14" t="n"/>
+      <c r="J415" s="15" t="n"/>
+      <c r="K415" s="14" t="n"/>
+      <c r="L415" s="16" t="n"/>
+      <c r="M415" s="13" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="11" t="n"/>
@@ -7774,10 +8266,11 @@
       <c r="F416" s="14" t="n"/>
       <c r="G416" s="14" t="n"/>
       <c r="H416" s="14" t="n"/>
-      <c r="I416" s="15" t="n"/>
-      <c r="J416" s="14" t="n"/>
-      <c r="K416" s="16" t="n"/>
-      <c r="L416" s="13" t="n"/>
+      <c r="I416" s="14" t="n"/>
+      <c r="J416" s="15" t="n"/>
+      <c r="K416" s="14" t="n"/>
+      <c r="L416" s="16" t="n"/>
+      <c r="M416" s="13" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="11" t="n"/>
@@ -7788,10 +8281,11 @@
       <c r="F417" s="14" t="n"/>
       <c r="G417" s="14" t="n"/>
       <c r="H417" s="14" t="n"/>
-      <c r="I417" s="15" t="n"/>
-      <c r="J417" s="14" t="n"/>
-      <c r="K417" s="16" t="n"/>
-      <c r="L417" s="13" t="n"/>
+      <c r="I417" s="14" t="n"/>
+      <c r="J417" s="15" t="n"/>
+      <c r="K417" s="14" t="n"/>
+      <c r="L417" s="16" t="n"/>
+      <c r="M417" s="13" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="11" t="n"/>
@@ -7802,10 +8296,11 @@
       <c r="F418" s="14" t="n"/>
       <c r="G418" s="14" t="n"/>
       <c r="H418" s="14" t="n"/>
-      <c r="I418" s="15" t="n"/>
-      <c r="J418" s="14" t="n"/>
-      <c r="K418" s="16" t="n"/>
-      <c r="L418" s="13" t="n"/>
+      <c r="I418" s="14" t="n"/>
+      <c r="J418" s="15" t="n"/>
+      <c r="K418" s="14" t="n"/>
+      <c r="L418" s="16" t="n"/>
+      <c r="M418" s="13" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="11" t="n"/>
@@ -7816,10 +8311,11 @@
       <c r="F419" s="14" t="n"/>
       <c r="G419" s="14" t="n"/>
       <c r="H419" s="14" t="n"/>
-      <c r="I419" s="15" t="n"/>
-      <c r="J419" s="14" t="n"/>
-      <c r="K419" s="16" t="n"/>
-      <c r="L419" s="13" t="n"/>
+      <c r="I419" s="14" t="n"/>
+      <c r="J419" s="15" t="n"/>
+      <c r="K419" s="14" t="n"/>
+      <c r="L419" s="16" t="n"/>
+      <c r="M419" s="13" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="11" t="n"/>
@@ -7830,10 +8326,11 @@
       <c r="F420" s="14" t="n"/>
       <c r="G420" s="14" t="n"/>
       <c r="H420" s="14" t="n"/>
-      <c r="I420" s="15" t="n"/>
-      <c r="J420" s="14" t="n"/>
-      <c r="K420" s="16" t="n"/>
-      <c r="L420" s="13" t="n"/>
+      <c r="I420" s="14" t="n"/>
+      <c r="J420" s="15" t="n"/>
+      <c r="K420" s="14" t="n"/>
+      <c r="L420" s="16" t="n"/>
+      <c r="M420" s="13" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="11" t="n"/>
@@ -7844,10 +8341,11 @@
       <c r="F421" s="14" t="n"/>
       <c r="G421" s="14" t="n"/>
       <c r="H421" s="14" t="n"/>
-      <c r="I421" s="15" t="n"/>
-      <c r="J421" s="14" t="n"/>
-      <c r="K421" s="16" t="n"/>
-      <c r="L421" s="13" t="n"/>
+      <c r="I421" s="14" t="n"/>
+      <c r="J421" s="15" t="n"/>
+      <c r="K421" s="14" t="n"/>
+      <c r="L421" s="16" t="n"/>
+      <c r="M421" s="13" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="11" t="n"/>
@@ -7858,10 +8356,11 @@
       <c r="F422" s="14" t="n"/>
       <c r="G422" s="14" t="n"/>
       <c r="H422" s="14" t="n"/>
-      <c r="I422" s="15" t="n"/>
-      <c r="J422" s="14" t="n"/>
-      <c r="K422" s="16" t="n"/>
-      <c r="L422" s="13" t="n"/>
+      <c r="I422" s="14" t="n"/>
+      <c r="J422" s="15" t="n"/>
+      <c r="K422" s="14" t="n"/>
+      <c r="L422" s="16" t="n"/>
+      <c r="M422" s="13" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="11" t="n"/>
@@ -7872,10 +8371,11 @@
       <c r="F423" s="14" t="n"/>
       <c r="G423" s="14" t="n"/>
       <c r="H423" s="14" t="n"/>
-      <c r="I423" s="15" t="n"/>
-      <c r="J423" s="14" t="n"/>
-      <c r="K423" s="16" t="n"/>
-      <c r="L423" s="13" t="n"/>
+      <c r="I423" s="14" t="n"/>
+      <c r="J423" s="15" t="n"/>
+      <c r="K423" s="14" t="n"/>
+      <c r="L423" s="16" t="n"/>
+      <c r="M423" s="13" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="11" t="n"/>
@@ -7886,10 +8386,11 @@
       <c r="F424" s="14" t="n"/>
       <c r="G424" s="14" t="n"/>
       <c r="H424" s="14" t="n"/>
-      <c r="I424" s="15" t="n"/>
-      <c r="J424" s="14" t="n"/>
-      <c r="K424" s="16" t="n"/>
-      <c r="L424" s="13" t="n"/>
+      <c r="I424" s="14" t="n"/>
+      <c r="J424" s="15" t="n"/>
+      <c r="K424" s="14" t="n"/>
+      <c r="L424" s="16" t="n"/>
+      <c r="M424" s="13" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="11" t="n"/>
@@ -7900,10 +8401,11 @@
       <c r="F425" s="14" t="n"/>
       <c r="G425" s="14" t="n"/>
       <c r="H425" s="14" t="n"/>
-      <c r="I425" s="15" t="n"/>
-      <c r="J425" s="14" t="n"/>
-      <c r="K425" s="16" t="n"/>
-      <c r="L425" s="13" t="n"/>
+      <c r="I425" s="14" t="n"/>
+      <c r="J425" s="15" t="n"/>
+      <c r="K425" s="14" t="n"/>
+      <c r="L425" s="16" t="n"/>
+      <c r="M425" s="13" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="11" t="n"/>
@@ -7914,10 +8416,11 @@
       <c r="F426" s="14" t="n"/>
       <c r="G426" s="14" t="n"/>
       <c r="H426" s="14" t="n"/>
-      <c r="I426" s="15" t="n"/>
-      <c r="J426" s="14" t="n"/>
-      <c r="K426" s="16" t="n"/>
-      <c r="L426" s="13" t="n"/>
+      <c r="I426" s="14" t="n"/>
+      <c r="J426" s="15" t="n"/>
+      <c r="K426" s="14" t="n"/>
+      <c r="L426" s="16" t="n"/>
+      <c r="M426" s="13" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="11" t="n"/>
@@ -7928,10 +8431,11 @@
       <c r="F427" s="14" t="n"/>
       <c r="G427" s="14" t="n"/>
       <c r="H427" s="14" t="n"/>
-      <c r="I427" s="15" t="n"/>
-      <c r="J427" s="14" t="n"/>
-      <c r="K427" s="16" t="n"/>
-      <c r="L427" s="13" t="n"/>
+      <c r="I427" s="14" t="n"/>
+      <c r="J427" s="15" t="n"/>
+      <c r="K427" s="14" t="n"/>
+      <c r="L427" s="16" t="n"/>
+      <c r="M427" s="13" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="11" t="n"/>
@@ -7942,10 +8446,11 @@
       <c r="F428" s="14" t="n"/>
       <c r="G428" s="14" t="n"/>
       <c r="H428" s="14" t="n"/>
-      <c r="I428" s="15" t="n"/>
-      <c r="J428" s="14" t="n"/>
-      <c r="K428" s="16" t="n"/>
-      <c r="L428" s="13" t="n"/>
+      <c r="I428" s="14" t="n"/>
+      <c r="J428" s="15" t="n"/>
+      <c r="K428" s="14" t="n"/>
+      <c r="L428" s="16" t="n"/>
+      <c r="M428" s="13" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="11" t="n"/>
@@ -7956,10 +8461,11 @@
       <c r="F429" s="14" t="n"/>
       <c r="G429" s="14" t="n"/>
       <c r="H429" s="14" t="n"/>
-      <c r="I429" s="15" t="n"/>
-      <c r="J429" s="14" t="n"/>
-      <c r="K429" s="16" t="n"/>
-      <c r="L429" s="13" t="n"/>
+      <c r="I429" s="14" t="n"/>
+      <c r="J429" s="15" t="n"/>
+      <c r="K429" s="14" t="n"/>
+      <c r="L429" s="16" t="n"/>
+      <c r="M429" s="13" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="11" t="n"/>
@@ -7970,10 +8476,11 @@
       <c r="F430" s="14" t="n"/>
       <c r="G430" s="14" t="n"/>
       <c r="H430" s="14" t="n"/>
-      <c r="I430" s="15" t="n"/>
-      <c r="J430" s="14" t="n"/>
-      <c r="K430" s="16" t="n"/>
-      <c r="L430" s="13" t="n"/>
+      <c r="I430" s="14" t="n"/>
+      <c r="J430" s="15" t="n"/>
+      <c r="K430" s="14" t="n"/>
+      <c r="L430" s="16" t="n"/>
+      <c r="M430" s="13" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="11" t="n"/>
@@ -7984,10 +8491,11 @@
       <c r="F431" s="14" t="n"/>
       <c r="G431" s="14" t="n"/>
       <c r="H431" s="14" t="n"/>
-      <c r="I431" s="15" t="n"/>
-      <c r="J431" s="14" t="n"/>
-      <c r="K431" s="16" t="n"/>
-      <c r="L431" s="13" t="n"/>
+      <c r="I431" s="14" t="n"/>
+      <c r="J431" s="15" t="n"/>
+      <c r="K431" s="14" t="n"/>
+      <c r="L431" s="16" t="n"/>
+      <c r="M431" s="13" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="11" t="n"/>
@@ -7998,10 +8506,11 @@
       <c r="F432" s="14" t="n"/>
       <c r="G432" s="14" t="n"/>
       <c r="H432" s="14" t="n"/>
-      <c r="I432" s="15" t="n"/>
-      <c r="J432" s="14" t="n"/>
-      <c r="K432" s="16" t="n"/>
-      <c r="L432" s="13" t="n"/>
+      <c r="I432" s="14" t="n"/>
+      <c r="J432" s="15" t="n"/>
+      <c r="K432" s="14" t="n"/>
+      <c r="L432" s="16" t="n"/>
+      <c r="M432" s="13" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="11" t="n"/>
@@ -8012,10 +8521,11 @@
       <c r="F433" s="14" t="n"/>
       <c r="G433" s="14" t="n"/>
       <c r="H433" s="14" t="n"/>
-      <c r="I433" s="15" t="n"/>
-      <c r="J433" s="14" t="n"/>
-      <c r="K433" s="16" t="n"/>
-      <c r="L433" s="13" t="n"/>
+      <c r="I433" s="14" t="n"/>
+      <c r="J433" s="15" t="n"/>
+      <c r="K433" s="14" t="n"/>
+      <c r="L433" s="16" t="n"/>
+      <c r="M433" s="13" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="11" t="n"/>
@@ -8026,10 +8536,11 @@
       <c r="F434" s="14" t="n"/>
       <c r="G434" s="14" t="n"/>
       <c r="H434" s="14" t="n"/>
-      <c r="I434" s="15" t="n"/>
-      <c r="J434" s="14" t="n"/>
-      <c r="K434" s="16" t="n"/>
-      <c r="L434" s="13" t="n"/>
+      <c r="I434" s="14" t="n"/>
+      <c r="J434" s="15" t="n"/>
+      <c r="K434" s="14" t="n"/>
+      <c r="L434" s="16" t="n"/>
+      <c r="M434" s="13" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="11" t="n"/>
@@ -8040,10 +8551,11 @@
       <c r="F435" s="14" t="n"/>
       <c r="G435" s="14" t="n"/>
       <c r="H435" s="14" t="n"/>
-      <c r="I435" s="15" t="n"/>
-      <c r="J435" s="14" t="n"/>
-      <c r="K435" s="16" t="n"/>
-      <c r="L435" s="13" t="n"/>
+      <c r="I435" s="14" t="n"/>
+      <c r="J435" s="15" t="n"/>
+      <c r="K435" s="14" t="n"/>
+      <c r="L435" s="16" t="n"/>
+      <c r="M435" s="13" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="11" t="n"/>
@@ -8054,10 +8566,11 @@
       <c r="F436" s="14" t="n"/>
       <c r="G436" s="14" t="n"/>
       <c r="H436" s="14" t="n"/>
-      <c r="I436" s="15" t="n"/>
-      <c r="J436" s="14" t="n"/>
-      <c r="K436" s="16" t="n"/>
-      <c r="L436" s="13" t="n"/>
+      <c r="I436" s="14" t="n"/>
+      <c r="J436" s="15" t="n"/>
+      <c r="K436" s="14" t="n"/>
+      <c r="L436" s="16" t="n"/>
+      <c r="M436" s="13" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="11" t="n"/>
@@ -8068,10 +8581,11 @@
       <c r="F437" s="14" t="n"/>
       <c r="G437" s="14" t="n"/>
       <c r="H437" s="14" t="n"/>
-      <c r="I437" s="15" t="n"/>
-      <c r="J437" s="14" t="n"/>
-      <c r="K437" s="16" t="n"/>
-      <c r="L437" s="13" t="n"/>
+      <c r="I437" s="14" t="n"/>
+      <c r="J437" s="15" t="n"/>
+      <c r="K437" s="14" t="n"/>
+      <c r="L437" s="16" t="n"/>
+      <c r="M437" s="13" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="11" t="n"/>
@@ -8082,10 +8596,11 @@
       <c r="F438" s="14" t="n"/>
       <c r="G438" s="14" t="n"/>
       <c r="H438" s="14" t="n"/>
-      <c r="I438" s="15" t="n"/>
-      <c r="J438" s="14" t="n"/>
-      <c r="K438" s="16" t="n"/>
-      <c r="L438" s="13" t="n"/>
+      <c r="I438" s="14" t="n"/>
+      <c r="J438" s="15" t="n"/>
+      <c r="K438" s="14" t="n"/>
+      <c r="L438" s="16" t="n"/>
+      <c r="M438" s="13" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="11" t="n"/>
@@ -8096,10 +8611,11 @@
       <c r="F439" s="14" t="n"/>
       <c r="G439" s="14" t="n"/>
       <c r="H439" s="14" t="n"/>
-      <c r="I439" s="15" t="n"/>
-      <c r="J439" s="14" t="n"/>
-      <c r="K439" s="16" t="n"/>
-      <c r="L439" s="13" t="n"/>
+      <c r="I439" s="14" t="n"/>
+      <c r="J439" s="15" t="n"/>
+      <c r="K439" s="14" t="n"/>
+      <c r="L439" s="16" t="n"/>
+      <c r="M439" s="13" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="11" t="n"/>
@@ -8110,10 +8626,11 @@
       <c r="F440" s="14" t="n"/>
       <c r="G440" s="14" t="n"/>
       <c r="H440" s="14" t="n"/>
-      <c r="I440" s="15" t="n"/>
-      <c r="J440" s="14" t="n"/>
-      <c r="K440" s="16" t="n"/>
-      <c r="L440" s="13" t="n"/>
+      <c r="I440" s="14" t="n"/>
+      <c r="J440" s="15" t="n"/>
+      <c r="K440" s="14" t="n"/>
+      <c r="L440" s="16" t="n"/>
+      <c r="M440" s="13" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="11" t="n"/>
@@ -8124,10 +8641,11 @@
       <c r="F441" s="14" t="n"/>
       <c r="G441" s="14" t="n"/>
       <c r="H441" s="14" t="n"/>
-      <c r="I441" s="15" t="n"/>
-      <c r="J441" s="14" t="n"/>
-      <c r="K441" s="16" t="n"/>
-      <c r="L441" s="13" t="n"/>
+      <c r="I441" s="14" t="n"/>
+      <c r="J441" s="15" t="n"/>
+      <c r="K441" s="14" t="n"/>
+      <c r="L441" s="16" t="n"/>
+      <c r="M441" s="13" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="11" t="n"/>
@@ -8138,10 +8656,11 @@
       <c r="F442" s="14" t="n"/>
       <c r="G442" s="14" t="n"/>
       <c r="H442" s="14" t="n"/>
-      <c r="I442" s="15" t="n"/>
-      <c r="J442" s="14" t="n"/>
-      <c r="K442" s="16" t="n"/>
-      <c r="L442" s="13" t="n"/>
+      <c r="I442" s="14" t="n"/>
+      <c r="J442" s="15" t="n"/>
+      <c r="K442" s="14" t="n"/>
+      <c r="L442" s="16" t="n"/>
+      <c r="M442" s="13" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="11" t="n"/>
@@ -8152,10 +8671,11 @@
       <c r="F443" s="14" t="n"/>
       <c r="G443" s="14" t="n"/>
       <c r="H443" s="14" t="n"/>
-      <c r="I443" s="15" t="n"/>
-      <c r="J443" s="14" t="n"/>
-      <c r="K443" s="16" t="n"/>
-      <c r="L443" s="13" t="n"/>
+      <c r="I443" s="14" t="n"/>
+      <c r="J443" s="15" t="n"/>
+      <c r="K443" s="14" t="n"/>
+      <c r="L443" s="16" t="n"/>
+      <c r="M443" s="13" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="11" t="n"/>
@@ -8166,10 +8686,11 @@
       <c r="F444" s="14" t="n"/>
       <c r="G444" s="14" t="n"/>
       <c r="H444" s="14" t="n"/>
-      <c r="I444" s="15" t="n"/>
-      <c r="J444" s="14" t="n"/>
-      <c r="K444" s="16" t="n"/>
-      <c r="L444" s="13" t="n"/>
+      <c r="I444" s="14" t="n"/>
+      <c r="J444" s="15" t="n"/>
+      <c r="K444" s="14" t="n"/>
+      <c r="L444" s="16" t="n"/>
+      <c r="M444" s="13" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="11" t="n"/>
@@ -8180,10 +8701,11 @@
       <c r="F445" s="14" t="n"/>
       <c r="G445" s="14" t="n"/>
       <c r="H445" s="14" t="n"/>
-      <c r="I445" s="15" t="n"/>
-      <c r="J445" s="14" t="n"/>
-      <c r="K445" s="16" t="n"/>
-      <c r="L445" s="13" t="n"/>
+      <c r="I445" s="14" t="n"/>
+      <c r="J445" s="15" t="n"/>
+      <c r="K445" s="14" t="n"/>
+      <c r="L445" s="16" t="n"/>
+      <c r="M445" s="13" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="11" t="n"/>
@@ -8194,10 +8716,11 @@
       <c r="F446" s="14" t="n"/>
       <c r="G446" s="14" t="n"/>
       <c r="H446" s="14" t="n"/>
-      <c r="I446" s="15" t="n"/>
-      <c r="J446" s="14" t="n"/>
-      <c r="K446" s="16" t="n"/>
-      <c r="L446" s="13" t="n"/>
+      <c r="I446" s="14" t="n"/>
+      <c r="J446" s="15" t="n"/>
+      <c r="K446" s="14" t="n"/>
+      <c r="L446" s="16" t="n"/>
+      <c r="M446" s="13" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="11" t="n"/>
@@ -8208,10 +8731,11 @@
       <c r="F447" s="14" t="n"/>
       <c r="G447" s="14" t="n"/>
       <c r="H447" s="14" t="n"/>
-      <c r="I447" s="15" t="n"/>
-      <c r="J447" s="14" t="n"/>
-      <c r="K447" s="16" t="n"/>
-      <c r="L447" s="13" t="n"/>
+      <c r="I447" s="14" t="n"/>
+      <c r="J447" s="15" t="n"/>
+      <c r="K447" s="14" t="n"/>
+      <c r="L447" s="16" t="n"/>
+      <c r="M447" s="13" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="11" t="n"/>
@@ -8222,10 +8746,11 @@
       <c r="F448" s="14" t="n"/>
       <c r="G448" s="14" t="n"/>
       <c r="H448" s="14" t="n"/>
-      <c r="I448" s="15" t="n"/>
-      <c r="J448" s="14" t="n"/>
-      <c r="K448" s="16" t="n"/>
-      <c r="L448" s="13" t="n"/>
+      <c r="I448" s="14" t="n"/>
+      <c r="J448" s="15" t="n"/>
+      <c r="K448" s="14" t="n"/>
+      <c r="L448" s="16" t="n"/>
+      <c r="M448" s="13" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="11" t="n"/>
@@ -8236,10 +8761,11 @@
       <c r="F449" s="14" t="n"/>
       <c r="G449" s="14" t="n"/>
       <c r="H449" s="14" t="n"/>
-      <c r="I449" s="15" t="n"/>
-      <c r="J449" s="14" t="n"/>
-      <c r="K449" s="16" t="n"/>
-      <c r="L449" s="13" t="n"/>
+      <c r="I449" s="14" t="n"/>
+      <c r="J449" s="15" t="n"/>
+      <c r="K449" s="14" t="n"/>
+      <c r="L449" s="16" t="n"/>
+      <c r="M449" s="13" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="11" t="n"/>
@@ -8250,10 +8776,11 @@
       <c r="F450" s="14" t="n"/>
       <c r="G450" s="14" t="n"/>
       <c r="H450" s="14" t="n"/>
-      <c r="I450" s="15" t="n"/>
-      <c r="J450" s="14" t="n"/>
-      <c r="K450" s="16" t="n"/>
-      <c r="L450" s="13" t="n"/>
+      <c r="I450" s="14" t="n"/>
+      <c r="J450" s="15" t="n"/>
+      <c r="K450" s="14" t="n"/>
+      <c r="L450" s="16" t="n"/>
+      <c r="M450" s="13" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="11" t="n"/>
@@ -8264,10 +8791,11 @@
       <c r="F451" s="14" t="n"/>
       <c r="G451" s="14" t="n"/>
       <c r="H451" s="14" t="n"/>
-      <c r="I451" s="15" t="n"/>
-      <c r="J451" s="14" t="n"/>
-      <c r="K451" s="16" t="n"/>
-      <c r="L451" s="13" t="n"/>
+      <c r="I451" s="14" t="n"/>
+      <c r="J451" s="15" t="n"/>
+      <c r="K451" s="14" t="n"/>
+      <c r="L451" s="16" t="n"/>
+      <c r="M451" s="13" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="11" t="n"/>
@@ -8278,10 +8806,11 @@
       <c r="F452" s="14" t="n"/>
       <c r="G452" s="14" t="n"/>
       <c r="H452" s="14" t="n"/>
-      <c r="I452" s="15" t="n"/>
-      <c r="J452" s="14" t="n"/>
-      <c r="K452" s="16" t="n"/>
-      <c r="L452" s="13" t="n"/>
+      <c r="I452" s="14" t="n"/>
+      <c r="J452" s="15" t="n"/>
+      <c r="K452" s="14" t="n"/>
+      <c r="L452" s="16" t="n"/>
+      <c r="M452" s="13" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="11" t="n"/>
@@ -8292,10 +8821,11 @@
       <c r="F453" s="14" t="n"/>
       <c r="G453" s="14" t="n"/>
       <c r="H453" s="14" t="n"/>
-      <c r="I453" s="15" t="n"/>
-      <c r="J453" s="14" t="n"/>
-      <c r="K453" s="16" t="n"/>
-      <c r="L453" s="13" t="n"/>
+      <c r="I453" s="14" t="n"/>
+      <c r="J453" s="15" t="n"/>
+      <c r="K453" s="14" t="n"/>
+      <c r="L453" s="16" t="n"/>
+      <c r="M453" s="13" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="11" t="n"/>
@@ -8306,10 +8836,11 @@
       <c r="F454" s="14" t="n"/>
       <c r="G454" s="14" t="n"/>
       <c r="H454" s="14" t="n"/>
-      <c r="I454" s="15" t="n"/>
-      <c r="J454" s="14" t="n"/>
-      <c r="K454" s="16" t="n"/>
-      <c r="L454" s="13" t="n"/>
+      <c r="I454" s="14" t="n"/>
+      <c r="J454" s="15" t="n"/>
+      <c r="K454" s="14" t="n"/>
+      <c r="L454" s="16" t="n"/>
+      <c r="M454" s="13" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="11" t="n"/>
@@ -8320,10 +8851,11 @@
       <c r="F455" s="14" t="n"/>
       <c r="G455" s="14" t="n"/>
       <c r="H455" s="14" t="n"/>
-      <c r="I455" s="15" t="n"/>
-      <c r="J455" s="14" t="n"/>
-      <c r="K455" s="16" t="n"/>
-      <c r="L455" s="13" t="n"/>
+      <c r="I455" s="14" t="n"/>
+      <c r="J455" s="15" t="n"/>
+      <c r="K455" s="14" t="n"/>
+      <c r="L455" s="16" t="n"/>
+      <c r="M455" s="13" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="11" t="n"/>
@@ -8334,10 +8866,11 @@
       <c r="F456" s="14" t="n"/>
       <c r="G456" s="14" t="n"/>
       <c r="H456" s="14" t="n"/>
-      <c r="I456" s="15" t="n"/>
-      <c r="J456" s="14" t="n"/>
-      <c r="K456" s="16" t="n"/>
-      <c r="L456" s="13" t="n"/>
+      <c r="I456" s="14" t="n"/>
+      <c r="J456" s="15" t="n"/>
+      <c r="K456" s="14" t="n"/>
+      <c r="L456" s="16" t="n"/>
+      <c r="M456" s="13" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="11" t="n"/>
@@ -8348,10 +8881,11 @@
       <c r="F457" s="14" t="n"/>
       <c r="G457" s="14" t="n"/>
       <c r="H457" s="14" t="n"/>
-      <c r="I457" s="15" t="n"/>
-      <c r="J457" s="14" t="n"/>
-      <c r="K457" s="16" t="n"/>
-      <c r="L457" s="13" t="n"/>
+      <c r="I457" s="14" t="n"/>
+      <c r="J457" s="15" t="n"/>
+      <c r="K457" s="14" t="n"/>
+      <c r="L457" s="16" t="n"/>
+      <c r="M457" s="13" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="11" t="n"/>
@@ -8362,10 +8896,11 @@
       <c r="F458" s="14" t="n"/>
       <c r="G458" s="14" t="n"/>
       <c r="H458" s="14" t="n"/>
-      <c r="I458" s="15" t="n"/>
-      <c r="J458" s="14" t="n"/>
-      <c r="K458" s="16" t="n"/>
-      <c r="L458" s="13" t="n"/>
+      <c r="I458" s="14" t="n"/>
+      <c r="J458" s="15" t="n"/>
+      <c r="K458" s="14" t="n"/>
+      <c r="L458" s="16" t="n"/>
+      <c r="M458" s="13" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="11" t="n"/>
@@ -8376,10 +8911,11 @@
       <c r="F459" s="14" t="n"/>
       <c r="G459" s="14" t="n"/>
       <c r="H459" s="14" t="n"/>
-      <c r="I459" s="15" t="n"/>
-      <c r="J459" s="14" t="n"/>
-      <c r="K459" s="16" t="n"/>
-      <c r="L459" s="13" t="n"/>
+      <c r="I459" s="14" t="n"/>
+      <c r="J459" s="15" t="n"/>
+      <c r="K459" s="14" t="n"/>
+      <c r="L459" s="16" t="n"/>
+      <c r="M459" s="13" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="11" t="n"/>
@@ -8390,10 +8926,11 @@
       <c r="F460" s="14" t="n"/>
       <c r="G460" s="14" t="n"/>
       <c r="H460" s="14" t="n"/>
-      <c r="I460" s="15" t="n"/>
-      <c r="J460" s="14" t="n"/>
-      <c r="K460" s="16" t="n"/>
-      <c r="L460" s="13" t="n"/>
+      <c r="I460" s="14" t="n"/>
+      <c r="J460" s="15" t="n"/>
+      <c r="K460" s="14" t="n"/>
+      <c r="L460" s="16" t="n"/>
+      <c r="M460" s="13" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="11" t="n"/>
@@ -8404,10 +8941,11 @@
       <c r="F461" s="14" t="n"/>
       <c r="G461" s="14" t="n"/>
       <c r="H461" s="14" t="n"/>
-      <c r="I461" s="15" t="n"/>
-      <c r="J461" s="14" t="n"/>
-      <c r="K461" s="16" t="n"/>
-      <c r="L461" s="13" t="n"/>
+      <c r="I461" s="14" t="n"/>
+      <c r="J461" s="15" t="n"/>
+      <c r="K461" s="14" t="n"/>
+      <c r="L461" s="16" t="n"/>
+      <c r="M461" s="13" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="11" t="n"/>
@@ -8418,10 +8956,11 @@
       <c r="F462" s="14" t="n"/>
       <c r="G462" s="14" t="n"/>
       <c r="H462" s="14" t="n"/>
-      <c r="I462" s="15" t="n"/>
-      <c r="J462" s="14" t="n"/>
-      <c r="K462" s="16" t="n"/>
-      <c r="L462" s="13" t="n"/>
+      <c r="I462" s="14" t="n"/>
+      <c r="J462" s="15" t="n"/>
+      <c r="K462" s="14" t="n"/>
+      <c r="L462" s="16" t="n"/>
+      <c r="M462" s="13" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="11" t="n"/>
@@ -8432,10 +8971,11 @@
       <c r="F463" s="14" t="n"/>
       <c r="G463" s="14" t="n"/>
       <c r="H463" s="14" t="n"/>
-      <c r="I463" s="15" t="n"/>
-      <c r="J463" s="14" t="n"/>
-      <c r="K463" s="16" t="n"/>
-      <c r="L463" s="13" t="n"/>
+      <c r="I463" s="14" t="n"/>
+      <c r="J463" s="15" t="n"/>
+      <c r="K463" s="14" t="n"/>
+      <c r="L463" s="16" t="n"/>
+      <c r="M463" s="13" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="11" t="n"/>
@@ -8446,10 +8986,11 @@
       <c r="F464" s="14" t="n"/>
       <c r="G464" s="14" t="n"/>
       <c r="H464" s="14" t="n"/>
-      <c r="I464" s="15" t="n"/>
-      <c r="J464" s="14" t="n"/>
-      <c r="K464" s="16" t="n"/>
-      <c r="L464" s="13" t="n"/>
+      <c r="I464" s="14" t="n"/>
+      <c r="J464" s="15" t="n"/>
+      <c r="K464" s="14" t="n"/>
+      <c r="L464" s="16" t="n"/>
+      <c r="M464" s="13" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="11" t="n"/>
@@ -8460,10 +9001,11 @@
       <c r="F465" s="14" t="n"/>
       <c r="G465" s="14" t="n"/>
       <c r="H465" s="14" t="n"/>
-      <c r="I465" s="15" t="n"/>
-      <c r="J465" s="14" t="n"/>
-      <c r="K465" s="16" t="n"/>
-      <c r="L465" s="13" t="n"/>
+      <c r="I465" s="14" t="n"/>
+      <c r="J465" s="15" t="n"/>
+      <c r="K465" s="14" t="n"/>
+      <c r="L465" s="16" t="n"/>
+      <c r="M465" s="13" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="11" t="n"/>
@@ -8474,10 +9016,11 @@
       <c r="F466" s="14" t="n"/>
       <c r="G466" s="14" t="n"/>
       <c r="H466" s="14" t="n"/>
-      <c r="I466" s="15" t="n"/>
-      <c r="J466" s="14" t="n"/>
-      <c r="K466" s="16" t="n"/>
-      <c r="L466" s="13" t="n"/>
+      <c r="I466" s="14" t="n"/>
+      <c r="J466" s="15" t="n"/>
+      <c r="K466" s="14" t="n"/>
+      <c r="L466" s="16" t="n"/>
+      <c r="M466" s="13" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="11" t="n"/>
@@ -8488,10 +9031,11 @@
       <c r="F467" s="14" t="n"/>
       <c r="G467" s="14" t="n"/>
       <c r="H467" s="14" t="n"/>
-      <c r="I467" s="15" t="n"/>
-      <c r="J467" s="14" t="n"/>
-      <c r="K467" s="16" t="n"/>
-      <c r="L467" s="13" t="n"/>
+      <c r="I467" s="14" t="n"/>
+      <c r="J467" s="15" t="n"/>
+      <c r="K467" s="14" t="n"/>
+      <c r="L467" s="16" t="n"/>
+      <c r="M467" s="13" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="11" t="n"/>
@@ -8502,10 +9046,11 @@
       <c r="F468" s="14" t="n"/>
       <c r="G468" s="14" t="n"/>
       <c r="H468" s="14" t="n"/>
-      <c r="I468" s="15" t="n"/>
-      <c r="J468" s="14" t="n"/>
-      <c r="K468" s="16" t="n"/>
-      <c r="L468" s="13" t="n"/>
+      <c r="I468" s="14" t="n"/>
+      <c r="J468" s="15" t="n"/>
+      <c r="K468" s="14" t="n"/>
+      <c r="L468" s="16" t="n"/>
+      <c r="M468" s="13" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="11" t="n"/>
@@ -8516,10 +9061,11 @@
       <c r="F469" s="14" t="n"/>
       <c r="G469" s="14" t="n"/>
       <c r="H469" s="14" t="n"/>
-      <c r="I469" s="15" t="n"/>
-      <c r="J469" s="14" t="n"/>
-      <c r="K469" s="16" t="n"/>
-      <c r="L469" s="13" t="n"/>
+      <c r="I469" s="14" t="n"/>
+      <c r="J469" s="15" t="n"/>
+      <c r="K469" s="14" t="n"/>
+      <c r="L469" s="16" t="n"/>
+      <c r="M469" s="13" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="11" t="n"/>
@@ -8530,10 +9076,11 @@
       <c r="F470" s="14" t="n"/>
       <c r="G470" s="14" t="n"/>
       <c r="H470" s="14" t="n"/>
-      <c r="I470" s="15" t="n"/>
-      <c r="J470" s="14" t="n"/>
-      <c r="K470" s="16" t="n"/>
-      <c r="L470" s="13" t="n"/>
+      <c r="I470" s="14" t="n"/>
+      <c r="J470" s="15" t="n"/>
+      <c r="K470" s="14" t="n"/>
+      <c r="L470" s="16" t="n"/>
+      <c r="M470" s="13" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="11" t="n"/>
@@ -8544,10 +9091,11 @@
       <c r="F471" s="14" t="n"/>
       <c r="G471" s="14" t="n"/>
       <c r="H471" s="14" t="n"/>
-      <c r="I471" s="15" t="n"/>
-      <c r="J471" s="14" t="n"/>
-      <c r="K471" s="16" t="n"/>
-      <c r="L471" s="13" t="n"/>
+      <c r="I471" s="14" t="n"/>
+      <c r="J471" s="15" t="n"/>
+      <c r="K471" s="14" t="n"/>
+      <c r="L471" s="16" t="n"/>
+      <c r="M471" s="13" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="11" t="n"/>
@@ -8558,10 +9106,11 @@
       <c r="F472" s="14" t="n"/>
       <c r="G472" s="14" t="n"/>
       <c r="H472" s="14" t="n"/>
-      <c r="I472" s="15" t="n"/>
-      <c r="J472" s="14" t="n"/>
-      <c r="K472" s="16" t="n"/>
-      <c r="L472" s="13" t="n"/>
+      <c r="I472" s="14" t="n"/>
+      <c r="J472" s="15" t="n"/>
+      <c r="K472" s="14" t="n"/>
+      <c r="L472" s="16" t="n"/>
+      <c r="M472" s="13" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="11" t="n"/>
@@ -8572,10 +9121,11 @@
       <c r="F473" s="14" t="n"/>
       <c r="G473" s="14" t="n"/>
       <c r="H473" s="14" t="n"/>
-      <c r="I473" s="15" t="n"/>
-      <c r="J473" s="14" t="n"/>
-      <c r="K473" s="16" t="n"/>
-      <c r="L473" s="13" t="n"/>
+      <c r="I473" s="14" t="n"/>
+      <c r="J473" s="15" t="n"/>
+      <c r="K473" s="14" t="n"/>
+      <c r="L473" s="16" t="n"/>
+      <c r="M473" s="13" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="11" t="n"/>
@@ -8586,10 +9136,11 @@
       <c r="F474" s="14" t="n"/>
       <c r="G474" s="14" t="n"/>
       <c r="H474" s="14" t="n"/>
-      <c r="I474" s="15" t="n"/>
-      <c r="J474" s="14" t="n"/>
-      <c r="K474" s="16" t="n"/>
-      <c r="L474" s="13" t="n"/>
+      <c r="I474" s="14" t="n"/>
+      <c r="J474" s="15" t="n"/>
+      <c r="K474" s="14" t="n"/>
+      <c r="L474" s="16" t="n"/>
+      <c r="M474" s="13" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="11" t="n"/>
@@ -8600,10 +9151,11 @@
       <c r="F475" s="14" t="n"/>
       <c r="G475" s="14" t="n"/>
       <c r="H475" s="14" t="n"/>
-      <c r="I475" s="15" t="n"/>
-      <c r="J475" s="14" t="n"/>
-      <c r="K475" s="16" t="n"/>
-      <c r="L475" s="13" t="n"/>
+      <c r="I475" s="14" t="n"/>
+      <c r="J475" s="15" t="n"/>
+      <c r="K475" s="14" t="n"/>
+      <c r="L475" s="16" t="n"/>
+      <c r="M475" s="13" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="11" t="n"/>
@@ -8614,10 +9166,11 @@
       <c r="F476" s="14" t="n"/>
       <c r="G476" s="14" t="n"/>
       <c r="H476" s="14" t="n"/>
-      <c r="I476" s="15" t="n"/>
-      <c r="J476" s="14" t="n"/>
-      <c r="K476" s="16" t="n"/>
-      <c r="L476" s="13" t="n"/>
+      <c r="I476" s="14" t="n"/>
+      <c r="J476" s="15" t="n"/>
+      <c r="K476" s="14" t="n"/>
+      <c r="L476" s="16" t="n"/>
+      <c r="M476" s="13" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="11" t="n"/>
@@ -8628,10 +9181,11 @@
       <c r="F477" s="14" t="n"/>
       <c r="G477" s="14" t="n"/>
       <c r="H477" s="14" t="n"/>
-      <c r="I477" s="15" t="n"/>
-      <c r="J477" s="14" t="n"/>
-      <c r="K477" s="16" t="n"/>
-      <c r="L477" s="13" t="n"/>
+      <c r="I477" s="14" t="n"/>
+      <c r="J477" s="15" t="n"/>
+      <c r="K477" s="14" t="n"/>
+      <c r="L477" s="16" t="n"/>
+      <c r="M477" s="13" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="11" t="n"/>
@@ -8642,10 +9196,11 @@
       <c r="F478" s="14" t="n"/>
       <c r="G478" s="14" t="n"/>
       <c r="H478" s="14" t="n"/>
-      <c r="I478" s="15" t="n"/>
-      <c r="J478" s="14" t="n"/>
-      <c r="K478" s="16" t="n"/>
-      <c r="L478" s="13" t="n"/>
+      <c r="I478" s="14" t="n"/>
+      <c r="J478" s="15" t="n"/>
+      <c r="K478" s="14" t="n"/>
+      <c r="L478" s="16" t="n"/>
+      <c r="M478" s="13" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="11" t="n"/>
@@ -8656,10 +9211,11 @@
       <c r="F479" s="14" t="n"/>
       <c r="G479" s="14" t="n"/>
       <c r="H479" s="14" t="n"/>
-      <c r="I479" s="15" t="n"/>
-      <c r="J479" s="14" t="n"/>
-      <c r="K479" s="16" t="n"/>
-      <c r="L479" s="13" t="n"/>
+      <c r="I479" s="14" t="n"/>
+      <c r="J479" s="15" t="n"/>
+      <c r="K479" s="14" t="n"/>
+      <c r="L479" s="16" t="n"/>
+      <c r="M479" s="13" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="11" t="n"/>
@@ -8670,10 +9226,11 @@
       <c r="F480" s="14" t="n"/>
       <c r="G480" s="14" t="n"/>
       <c r="H480" s="14" t="n"/>
-      <c r="I480" s="15" t="n"/>
-      <c r="J480" s="14" t="n"/>
-      <c r="K480" s="16" t="n"/>
-      <c r="L480" s="13" t="n"/>
+      <c r="I480" s="14" t="n"/>
+      <c r="J480" s="15" t="n"/>
+      <c r="K480" s="14" t="n"/>
+      <c r="L480" s="16" t="n"/>
+      <c r="M480" s="13" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="11" t="n"/>
@@ -8684,10 +9241,11 @@
       <c r="F481" s="14" t="n"/>
       <c r="G481" s="14" t="n"/>
       <c r="H481" s="14" t="n"/>
-      <c r="I481" s="15" t="n"/>
-      <c r="J481" s="14" t="n"/>
-      <c r="K481" s="16" t="n"/>
-      <c r="L481" s="13" t="n"/>
+      <c r="I481" s="14" t="n"/>
+      <c r="J481" s="15" t="n"/>
+      <c r="K481" s="14" t="n"/>
+      <c r="L481" s="16" t="n"/>
+      <c r="M481" s="13" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="11" t="n"/>
@@ -8698,10 +9256,11 @@
       <c r="F482" s="14" t="n"/>
       <c r="G482" s="14" t="n"/>
       <c r="H482" s="14" t="n"/>
-      <c r="I482" s="15" t="n"/>
-      <c r="J482" s="14" t="n"/>
-      <c r="K482" s="16" t="n"/>
-      <c r="L482" s="13" t="n"/>
+      <c r="I482" s="14" t="n"/>
+      <c r="J482" s="15" t="n"/>
+      <c r="K482" s="14" t="n"/>
+      <c r="L482" s="16" t="n"/>
+      <c r="M482" s="13" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="11" t="n"/>
@@ -8712,10 +9271,11 @@
       <c r="F483" s="14" t="n"/>
       <c r="G483" s="14" t="n"/>
       <c r="H483" s="14" t="n"/>
-      <c r="I483" s="15" t="n"/>
-      <c r="J483" s="14" t="n"/>
-      <c r="K483" s="16" t="n"/>
-      <c r="L483" s="13" t="n"/>
+      <c r="I483" s="14" t="n"/>
+      <c r="J483" s="15" t="n"/>
+      <c r="K483" s="14" t="n"/>
+      <c r="L483" s="16" t="n"/>
+      <c r="M483" s="13" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="11" t="n"/>
@@ -8726,10 +9286,11 @@
       <c r="F484" s="14" t="n"/>
       <c r="G484" s="14" t="n"/>
       <c r="H484" s="14" t="n"/>
-      <c r="I484" s="15" t="n"/>
-      <c r="J484" s="14" t="n"/>
-      <c r="K484" s="16" t="n"/>
-      <c r="L484" s="13" t="n"/>
+      <c r="I484" s="14" t="n"/>
+      <c r="J484" s="15" t="n"/>
+      <c r="K484" s="14" t="n"/>
+      <c r="L484" s="16" t="n"/>
+      <c r="M484" s="13" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="11" t="n"/>
@@ -8740,10 +9301,11 @@
       <c r="F485" s="14" t="n"/>
       <c r="G485" s="14" t="n"/>
       <c r="H485" s="14" t="n"/>
-      <c r="I485" s="15" t="n"/>
-      <c r="J485" s="14" t="n"/>
-      <c r="K485" s="16" t="n"/>
-      <c r="L485" s="13" t="n"/>
+      <c r="I485" s="14" t="n"/>
+      <c r="J485" s="15" t="n"/>
+      <c r="K485" s="14" t="n"/>
+      <c r="L485" s="16" t="n"/>
+      <c r="M485" s="13" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="11" t="n"/>
@@ -8754,10 +9316,11 @@
       <c r="F486" s="14" t="n"/>
       <c r="G486" s="14" t="n"/>
       <c r="H486" s="14" t="n"/>
-      <c r="I486" s="15" t="n"/>
-      <c r="J486" s="14" t="n"/>
-      <c r="K486" s="16" t="n"/>
-      <c r="L486" s="13" t="n"/>
+      <c r="I486" s="14" t="n"/>
+      <c r="J486" s="15" t="n"/>
+      <c r="K486" s="14" t="n"/>
+      <c r="L486" s="16" t="n"/>
+      <c r="M486" s="13" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="11" t="n"/>
@@ -8768,10 +9331,11 @@
       <c r="F487" s="14" t="n"/>
       <c r="G487" s="14" t="n"/>
       <c r="H487" s="14" t="n"/>
-      <c r="I487" s="15" t="n"/>
-      <c r="J487" s="14" t="n"/>
-      <c r="K487" s="16" t="n"/>
-      <c r="L487" s="13" t="n"/>
+      <c r="I487" s="14" t="n"/>
+      <c r="J487" s="15" t="n"/>
+      <c r="K487" s="14" t="n"/>
+      <c r="L487" s="16" t="n"/>
+      <c r="M487" s="13" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="11" t="n"/>
@@ -8782,10 +9346,11 @@
       <c r="F488" s="14" t="n"/>
       <c r="G488" s="14" t="n"/>
       <c r="H488" s="14" t="n"/>
-      <c r="I488" s="15" t="n"/>
-      <c r="J488" s="14" t="n"/>
-      <c r="K488" s="16" t="n"/>
-      <c r="L488" s="13" t="n"/>
+      <c r="I488" s="14" t="n"/>
+      <c r="J488" s="15" t="n"/>
+      <c r="K488" s="14" t="n"/>
+      <c r="L488" s="16" t="n"/>
+      <c r="M488" s="13" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="11" t="n"/>
@@ -8796,10 +9361,11 @@
       <c r="F489" s="14" t="n"/>
       <c r="G489" s="14" t="n"/>
       <c r="H489" s="14" t="n"/>
-      <c r="I489" s="15" t="n"/>
-      <c r="J489" s="14" t="n"/>
-      <c r="K489" s="16" t="n"/>
-      <c r="L489" s="13" t="n"/>
+      <c r="I489" s="14" t="n"/>
+      <c r="J489" s="15" t="n"/>
+      <c r="K489" s="14" t="n"/>
+      <c r="L489" s="16" t="n"/>
+      <c r="M489" s="13" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="11" t="n"/>
@@ -8810,10 +9376,11 @@
       <c r="F490" s="14" t="n"/>
       <c r="G490" s="14" t="n"/>
       <c r="H490" s="14" t="n"/>
-      <c r="I490" s="15" t="n"/>
-      <c r="J490" s="14" t="n"/>
-      <c r="K490" s="16" t="n"/>
-      <c r="L490" s="13" t="n"/>
+      <c r="I490" s="14" t="n"/>
+      <c r="J490" s="15" t="n"/>
+      <c r="K490" s="14" t="n"/>
+      <c r="L490" s="16" t="n"/>
+      <c r="M490" s="13" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="11" t="n"/>
@@ -8824,10 +9391,11 @@
       <c r="F491" s="14" t="n"/>
       <c r="G491" s="14" t="n"/>
       <c r="H491" s="14" t="n"/>
-      <c r="I491" s="15" t="n"/>
-      <c r="J491" s="14" t="n"/>
-      <c r="K491" s="16" t="n"/>
-      <c r="L491" s="13" t="n"/>
+      <c r="I491" s="14" t="n"/>
+      <c r="J491" s="15" t="n"/>
+      <c r="K491" s="14" t="n"/>
+      <c r="L491" s="16" t="n"/>
+      <c r="M491" s="13" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="11" t="n"/>
@@ -8838,10 +9406,11 @@
       <c r="F492" s="14" t="n"/>
       <c r="G492" s="14" t="n"/>
       <c r="H492" s="14" t="n"/>
-      <c r="I492" s="15" t="n"/>
-      <c r="J492" s="14" t="n"/>
-      <c r="K492" s="16" t="n"/>
-      <c r="L492" s="13" t="n"/>
+      <c r="I492" s="14" t="n"/>
+      <c r="J492" s="15" t="n"/>
+      <c r="K492" s="14" t="n"/>
+      <c r="L492" s="16" t="n"/>
+      <c r="M492" s="13" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="11" t="n"/>
@@ -8852,10 +9421,11 @@
       <c r="F493" s="14" t="n"/>
       <c r="G493" s="14" t="n"/>
       <c r="H493" s="14" t="n"/>
-      <c r="I493" s="15" t="n"/>
-      <c r="J493" s="14" t="n"/>
-      <c r="K493" s="16" t="n"/>
-      <c r="L493" s="13" t="n"/>
+      <c r="I493" s="14" t="n"/>
+      <c r="J493" s="15" t="n"/>
+      <c r="K493" s="14" t="n"/>
+      <c r="L493" s="16" t="n"/>
+      <c r="M493" s="13" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="11" t="n"/>
@@ -8866,10 +9436,11 @@
       <c r="F494" s="14" t="n"/>
       <c r="G494" s="14" t="n"/>
       <c r="H494" s="14" t="n"/>
-      <c r="I494" s="15" t="n"/>
-      <c r="J494" s="14" t="n"/>
-      <c r="K494" s="16" t="n"/>
-      <c r="L494" s="13" t="n"/>
+      <c r="I494" s="14" t="n"/>
+      <c r="J494" s="15" t="n"/>
+      <c r="K494" s="14" t="n"/>
+      <c r="L494" s="16" t="n"/>
+      <c r="M494" s="13" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="11" t="n"/>
@@ -8880,10 +9451,11 @@
       <c r="F495" s="14" t="n"/>
       <c r="G495" s="14" t="n"/>
       <c r="H495" s="14" t="n"/>
-      <c r="I495" s="15" t="n"/>
-      <c r="J495" s="14" t="n"/>
-      <c r="K495" s="16" t="n"/>
-      <c r="L495" s="13" t="n"/>
+      <c r="I495" s="14" t="n"/>
+      <c r="J495" s="15" t="n"/>
+      <c r="K495" s="14" t="n"/>
+      <c r="L495" s="16" t="n"/>
+      <c r="M495" s="13" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="11" t="n"/>
@@ -8894,10 +9466,11 @@
       <c r="F496" s="14" t="n"/>
       <c r="G496" s="14" t="n"/>
       <c r="H496" s="14" t="n"/>
-      <c r="I496" s="15" t="n"/>
-      <c r="J496" s="14" t="n"/>
-      <c r="K496" s="16" t="n"/>
-      <c r="L496" s="13" t="n"/>
+      <c r="I496" s="14" t="n"/>
+      <c r="J496" s="15" t="n"/>
+      <c r="K496" s="14" t="n"/>
+      <c r="L496" s="16" t="n"/>
+      <c r="M496" s="13" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="11" t="n"/>
@@ -8908,10 +9481,11 @@
       <c r="F497" s="14" t="n"/>
       <c r="G497" s="14" t="n"/>
       <c r="H497" s="14" t="n"/>
-      <c r="I497" s="15" t="n"/>
-      <c r="J497" s="14" t="n"/>
-      <c r="K497" s="16" t="n"/>
-      <c r="L497" s="13" t="n"/>
+      <c r="I497" s="14" t="n"/>
+      <c r="J497" s="15" t="n"/>
+      <c r="K497" s="14" t="n"/>
+      <c r="L497" s="16" t="n"/>
+      <c r="M497" s="13" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="11" t="n"/>
@@ -8922,10 +9496,11 @@
       <c r="F498" s="14" t="n"/>
       <c r="G498" s="14" t="n"/>
       <c r="H498" s="14" t="n"/>
-      <c r="I498" s="15" t="n"/>
-      <c r="J498" s="14" t="n"/>
-      <c r="K498" s="16" t="n"/>
-      <c r="L498" s="13" t="n"/>
+      <c r="I498" s="14" t="n"/>
+      <c r="J498" s="15" t="n"/>
+      <c r="K498" s="14" t="n"/>
+      <c r="L498" s="16" t="n"/>
+      <c r="M498" s="13" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="11" t="n"/>
@@ -8936,10 +9511,11 @@
       <c r="F499" s="14" t="n"/>
       <c r="G499" s="14" t="n"/>
       <c r="H499" s="14" t="n"/>
-      <c r="I499" s="15" t="n"/>
-      <c r="J499" s="14" t="n"/>
-      <c r="K499" s="16" t="n"/>
-      <c r="L499" s="13" t="n"/>
+      <c r="I499" s="14" t="n"/>
+      <c r="J499" s="15" t="n"/>
+      <c r="K499" s="14" t="n"/>
+      <c r="L499" s="16" t="n"/>
+      <c r="M499" s="13" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="11" t="n"/>
@@ -8950,10 +9526,11 @@
       <c r="F500" s="14" t="n"/>
       <c r="G500" s="14" t="n"/>
       <c r="H500" s="14" t="n"/>
-      <c r="I500" s="15" t="n"/>
-      <c r="J500" s="14" t="n"/>
-      <c r="K500" s="16" t="n"/>
-      <c r="L500" s="13" t="n"/>
+      <c r="I500" s="14" t="n"/>
+      <c r="J500" s="15" t="n"/>
+      <c r="K500" s="14" t="n"/>
+      <c r="L500" s="16" t="n"/>
+      <c r="M500" s="13" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="11" t="n"/>
@@ -8964,31 +9541,35 @@
       <c r="F501" s="14" t="n"/>
       <c r="G501" s="14" t="n"/>
       <c r="H501" s="14" t="n"/>
-      <c r="I501" s="15" t="n"/>
-      <c r="J501" s="14" t="n"/>
-      <c r="K501" s="16" t="n"/>
-      <c r="L501" s="13" t="n"/>
+      <c r="I501" s="14" t="n"/>
+      <c r="J501" s="15" t="n"/>
+      <c r="K501" s="14" t="n"/>
+      <c r="L501" s="16" t="n"/>
+      <c r="M501" s="13" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:K1000">
+  <conditionalFormatting sqref="A2:L1000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$J2="Hủy"</formula>
+      <formula>$K2="Hủy"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn gói trong danh sách (để trống nếu khách chưa chọn 399/699)." type="list" errorStyle="warning">
       <formula1>"399,699,Couple 999,1499,2999,Team 349"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
-      <formula1>"HUY,CƯỜNG,TÍN"</formula1>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Ô TÔ / Ngoại Cảnh / Nhóm tại Stu / Sản Phẩm." type="list" errorStyle="warning">
+      <formula1>"Ô TÔ,Ngoại Cảnh,Nhóm tại Stu,Sản Phẩm"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
       <formula1>"HUY,CƯỜNG,TÍN"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Nam / Nữ / Làm Tóc." type="list" errorStyle="warning">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chọn tên thợ đã ghép trên web." type="list" errorStyle="warning">
+      <formula1>"HUY,CƯỜNG,TÍN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Nam / Nữ / Làm Tóc." type="list" errorStyle="warning">
       <formula1>"Nam,Nữ,Làm Tóc"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chỉ chọn Hủy khi khách hủy." type="list" errorStyle="warning">
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngoài danh sách" error="Chỉ chọn Hủy khi khách hủy." type="list" errorStyle="warning">
       <formula1>"Hủy"</formula1>
     </dataValidation>
   </dataValidations>
